--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B140" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C140" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D140" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E140" t="str">
-        <v>Attach label 2 sides</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L140">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M140">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N140">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="O140" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B141" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C141" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D141" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L141">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M141">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N141">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O141" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B142" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C142" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D142" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L142">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M142">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N142">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="O142" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B143" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C143" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D143" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L143">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M143">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N143">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O143" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B144" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C144" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D144" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L144">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M144">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N144">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O144" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B145" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C145" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D145" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L145">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M145">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N145">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O145" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B146" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C146" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D146" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L146">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M146">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N146">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O146" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B147" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C147" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D147" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F147" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G147" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L147">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M147">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N147">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="O147" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B148" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C148" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D148" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L148">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M148">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N148">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O148" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B149" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C149" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D149" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F149" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L149">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M149">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O149" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B150" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C150" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D150" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L150">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M150">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O150" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B151" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C151" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D151" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Final press full shirt</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F151" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L151">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M151">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="O151" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B152" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C152" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D152" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Label attach manual</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L152">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M152">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N152">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O152" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B153" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C153" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D153" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L153">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M153">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N153">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O153" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B154" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C154" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D154" t="str">
-        <v>SH::US RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F154" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G154" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,22 +7619,22 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L154">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M154">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N154">
-        <v>1.1</v>
+        <v>0.43</v>
       </c>
       <c r="O154" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="155">
@@ -7648,10 +7648,10 @@
         <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E155" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,10 +7666,10 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L155">
         <v>2190</v>
@@ -7678,7 +7678,7 @@
         <v>17.96</v>
       </c>
       <c r="N155">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O155" t="str">
         <v>mudithaj</v>
@@ -7695,10 +7695,10 @@
         <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach cuff</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F156" t="str">
         <v>SNL</v>
@@ -7713,10 +7713,10 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L156">
         <v>2190</v>
@@ -7725,7 +7725,7 @@
         <v>17.96</v>
       </c>
       <c r="N156">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O156" t="str">
         <v>mudithaj</v>
@@ -7742,10 +7742,10 @@
         <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F157" t="str">
         <v>SNL</v>
@@ -7760,10 +7760,10 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L157">
         <v>2190</v>
@@ -7772,7 +7772,7 @@
         <v>17.96</v>
       </c>
       <c r="N157">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="O157" t="str">
         <v>mudithaj</v>
@@ -7789,10 +7789,10 @@
         <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,10 +7807,10 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L158">
         <v>2190</v>
@@ -7819,7 +7819,7 @@
         <v>17.96</v>
       </c>
       <c r="N158">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O158" t="str">
         <v>mudithaj</v>
@@ -7836,10 +7836,10 @@
         <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F159" t="str">
         <v>SNL</v>
@@ -7854,10 +7854,10 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L159">
         <v>2190</v>
@@ -7866,7 +7866,7 @@
         <v>17.96</v>
       </c>
       <c r="N159">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O159" t="str">
         <v>mudithaj</v>
@@ -7883,13 +7883,13 @@
         <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F160" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G160" t="str">
         <v>Sewing</v>
@@ -7901,10 +7901,10 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L160">
         <v>2190</v>
@@ -7913,7 +7913,7 @@
         <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O160" t="str">
         <v>mudithaj</v>
@@ -7930,16 +7930,16 @@
         <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F161" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G161" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,10 +7948,10 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L161">
         <v>2190</v>
@@ -7960,7 +7960,7 @@
         <v>17.96</v>
       </c>
       <c r="N161">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O161" t="str">
         <v>mudithaj</v>
@@ -7977,10 +7977,10 @@
         <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F162" t="str">
         <v>SNL</v>
@@ -7995,10 +7995,10 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L162">
         <v>2190</v>
@@ -8007,7 +8007,7 @@
         <v>17.96</v>
       </c>
       <c r="N162">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O162" t="str">
         <v>mudithaj</v>
@@ -8024,13 +8024,13 @@
         <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F163" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,10 +8042,10 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L163">
         <v>2190</v>
@@ -8071,10 +8071,10 @@
         <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F164" t="str">
         <v>VIR</v>
@@ -8089,10 +8089,10 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L164">
         <v>2190</v>
@@ -8101,7 +8101,7 @@
         <v>17.96</v>
       </c>
       <c r="N164">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O164" t="str">
         <v>mudithaj</v>
@@ -8118,13 +8118,13 @@
         <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F165" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,10 +8136,10 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L165">
         <v>2190</v>
@@ -8148,7 +8148,7 @@
         <v>17.96</v>
       </c>
       <c r="N165">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="O165" t="str">
         <v>mudithaj</v>
@@ -8165,10 +8165,10 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F166" t="str">
         <v>HELP</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,10 +8212,10 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F167" t="str">
         <v>HELP</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F168" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G168" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8306,10 +8306,10 @@
         <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E169" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,10 +8324,10 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L169">
         <v>2190</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8353,10 +8353,10 @@
         <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach cuff</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,10 +8371,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L170">
         <v>2190</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8400,10 +8400,10 @@
         <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8418,10 +8418,10 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L171">
         <v>2190</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8447,10 +8447,10 @@
         <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F172" t="str">
         <v>SNL</v>
@@ -8465,10 +8465,10 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L172">
         <v>2190</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8494,10 +8494,10 @@
         <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
@@ -8512,10 +8512,10 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L173">
         <v>2190</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8541,13 +8541,13 @@
         <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F174" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G174" t="str">
         <v>Sewing</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L174">
         <v>2190</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8588,16 +8588,16 @@
         <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F175" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G175" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8606,10 +8606,10 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L175">
         <v>2190</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8635,10 +8635,10 @@
         <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F176" t="str">
         <v>SNL</v>
@@ -8653,10 +8653,10 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L176">
         <v>2190</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8682,13 +8682,13 @@
         <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F177" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,10 +8700,10 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L177">
         <v>2190</v>
@@ -8729,10 +8729,10 @@
         <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F178" t="str">
         <v>VIR</v>
@@ -8747,10 +8747,10 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L178">
         <v>2190</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8776,13 +8776,13 @@
         <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F179" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8794,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L179">
         <v>2190</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8823,10 +8823,10 @@
         <v>Blouse</v>
       </c>
       <c r="D180" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F180" t="str">
         <v>HELP</v>
@@ -8841,10 +8841,10 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L180">
         <v>2190</v>
@@ -8853,7 +8853,7 @@
         <v>17.96</v>
       </c>
       <c r="N180">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O180" t="str">
         <v>mudithaj</v>
@@ -8870,10 +8870,10 @@
         <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F181" t="str">
         <v>HELP</v>
@@ -8888,10 +8888,10 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L181">
         <v>2190</v>
@@ -8900,7 +8900,7 @@
         <v>17.96</v>
       </c>
       <c r="N181">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O181" t="str">
         <v>mudithaj</v>
@@ -8908,25 +8908,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B182" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C182" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D182" t="str">
-        <v>BL::MX RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E182" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F182" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G182" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L182">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M182">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N182">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="O182" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B183" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C183" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D183" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E183" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,39 +8982,39 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L183">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M183">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N183">
-        <v>0.43</v>
+        <v>0.56</v>
       </c>
       <c r="O183" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B184" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C184" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D184" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach cuff</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F184" t="str">
         <v>SNL</v>
@@ -9029,39 +9029,39 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L184">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M184">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N184">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="O184" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B185" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C185" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D185" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E185" t="str">
-        <v>Attach set band collar</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F185" t="str">
         <v>SNL</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L185">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M185">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N185">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="O185" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B186" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C186" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D186" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach sleeve</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F186" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L186">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M186">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N186">
-        <v>1.5</v>
+        <v>0.84</v>
       </c>
       <c r="O186" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B187" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C187" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D187" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E187" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F187" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,42 +9170,42 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L187">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M187">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N187">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="O187" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B188" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C188" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D188" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E188" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F188" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G188" t="str">
         <v>Sewing</v>
@@ -9217,42 +9217,42 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L188">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M188">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O188" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B189" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C189" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D189" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E189" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F189" t="str">
-        <v>SNLU</v>
+        <v>LDN</v>
       </c>
       <c r="G189" t="str">
         <v>Sewing</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L189">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M189">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N189">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="O189" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B190" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C190" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D190" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E190" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F190" t="str">
         <v>SNL</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L190">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M190">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N190">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O190" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B191" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C191" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D191" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E191" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F191" t="str">
         <v>SNL</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L191">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M191">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N191">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="O191" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B192" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C192" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D192" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E192" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F192" t="str">
         <v>VIR</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L192">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M192">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N192">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O192" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B193" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C193" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D193" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E193" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F193" t="str">
         <v>VIR</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L193">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M193">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N193">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O193" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B194" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C194" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D194" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E194" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,39 +9499,39 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L194">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M194">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N194">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O194" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B195" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C195" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E195" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F195" t="str">
         <v>HELP</v>
@@ -9546,39 +9546,39 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L195">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M195">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N195">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O195" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B196" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C196" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E196" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F196" t="str">
         <v>HELP</v>
@@ -9593,22 +9593,22 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L196">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M196">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N196">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O196" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="197">
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E197" t="str">
         <v>Attach back stitch</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E198" t="str">
         <v>Attach pocket bag</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E199" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E200" t="str">
         <v>Collar attach to body</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E201" t="str">
         <v>Collar attach lining</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E202" t="str">
         <v>Sleeve attach overlock</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E203" t="str">
         <v>Attach zipper front</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E204" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E205" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E206" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E207" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E208" t="str">
         <v>Final press full jacket</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E209" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E210" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E211" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E212" t="str">
         <v>Attach back stitch</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E213" t="str">
         <v>Attach pocket bag</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E214" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E215" t="str">
         <v>Collar attach to body</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E216" t="str">
         <v>Collar attach lining</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E217" t="str">
         <v>Sleeve attach overlock</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E218" t="str">
         <v>Attach zipper front</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E219" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E220" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E221" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E222" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E223" t="str">
         <v>Final press full jacket</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E224" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10938,7 +10938,7 @@
         <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E225" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10956,10 +10956,10 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L225">
         <v>500</v>
@@ -10985,7 +10985,7 @@
         <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E226" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -11003,10 +11003,10 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L226">
         <v>500</v>
@@ -11023,19 +11023,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B227" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C227" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D227" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,39 +11050,39 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L227">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M227">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N227">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O227" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B228" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C228" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D228" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E228" t="str">
-        <v>Attach pocket bag</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F228" t="str">
         <v>SNL</v>
@@ -11097,39 +11097,39 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L228">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M228">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N228">
-        <v>0.56</v>
+        <v>1.2</v>
       </c>
       <c r="O228" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B229" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C229" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D229" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E229" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L229">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M229">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N229">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="O229" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B230" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C230" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D230" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E230" t="str">
-        <v>Collar attach to body</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F230" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L230">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M230">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N230">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="O230" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B231" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C231" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D231" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E231" t="str">
-        <v>Collar attach lining</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F231" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,42 +11238,42 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L231">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M231">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N231">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="O231" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B232" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C232" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D232" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E232" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F232" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G232" t="str">
         <v>Sewing</v>
@@ -11285,42 +11285,42 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L232">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M232">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N232">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="O232" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B233" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C233" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D233" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E233" t="str">
-        <v>Attach zipper front</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F233" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G233" t="str">
         <v>Sewing</v>
@@ -11332,45 +11332,45 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L233">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M233">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N233">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="O233" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B234" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C234" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D234" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E234" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F234" t="str">
-        <v>LDN</v>
+        <v>SNL</v>
       </c>
       <c r="G234" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L234">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M234">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N234">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="O234" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B235" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C235" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D235" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E235" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F235" t="str">
         <v>SNL</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L235">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M235">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N235">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O235" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B236" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C236" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D236" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E236" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F236" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L236">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M236">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N236">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="O236" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B237" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C237" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D237" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E237" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F237" t="str">
         <v>VIR</v>
@@ -11520,42 +11520,42 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L237">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M237">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N237">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="O237" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B238" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C238" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D238" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E238" t="str">
-        <v>Final press full jacket</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F238" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11567,39 +11567,39 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L238">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M238">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N238">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="O238" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B239" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C239" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D239" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E239" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F239" t="str">
         <v>HELP</v>
@@ -11614,39 +11614,39 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L239">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M239">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N239">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O239" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B240" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C240" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F240" t="str">
         <v>HELP</v>
@@ -11661,45 +11661,45 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L240">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M240">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N240">
         <v>1.1</v>
       </c>
       <c r="O240" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B241" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C241" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F241" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G241" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,22 +11708,22 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L241">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M241">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N241">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O241" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="242">
@@ -11737,10 +11737,10 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F242" t="str">
         <v>SNL</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,10 +11784,10 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,13 +11831,13 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F244" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G244" t="str">
         <v>Sewing</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,13 +11878,13 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F245" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,10 +11925,10 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,16 +12019,16 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F248" t="str">
         <v>SNL</v>
       </c>
       <c r="G248" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F249" t="str">
         <v>SNL</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F250" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F251" t="str">
         <v>VIR</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,13 +12207,13 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F252" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,10 +12254,10 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F253" t="str">
         <v>HELP</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F254" t="str">
         <v>HELP</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F255" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G255" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12395,10 +12395,10 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F256" t="str">
         <v>SNL</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,10 +12442,10 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,13 +12489,13 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F258" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G258" t="str">
         <v>Sewing</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,13 +12536,13 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F259" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,10 +12583,10 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,16 +12677,16 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F262" t="str">
         <v>SNL</v>
       </c>
       <c r="G262" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F263" t="str">
         <v>SNL</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F264" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F265" t="str">
         <v>VIR</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,13 +12865,13 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F266" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12912,10 +12912,10 @@
         <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F267" t="str">
         <v>HELP</v>
@@ -12930,10 +12930,10 @@
         <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L267">
         <v>607</v>
@@ -12942,7 +12942,7 @@
         <v>19</v>
       </c>
       <c r="N267">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O267" t="str">
         <v>sasanthar</v>
@@ -12959,10 +12959,10 @@
         <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F268" t="str">
         <v>HELP</v>
@@ -12977,10 +12977,10 @@
         <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L268">
         <v>607</v>
@@ -12989,7 +12989,7 @@
         <v>19</v>
       </c>
       <c r="N268">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O268" t="str">
         <v>sasanthar</v>
@@ -12997,66 +12997,66 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B269" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C269" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D269" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F269" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G269" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L269">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M269">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N269">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="O269" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B270" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C270" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D270" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,42 +13068,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L270">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M270">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N270">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O270" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B271" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C271" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D271" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L271">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M271">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N271">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="O271" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B272" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C272" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D272" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,45 +13162,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L272">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M272">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N272">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O272" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B273" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C273" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D273" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F273" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13209,42 +13209,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L273">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M273">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N273">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="O273" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B274" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C274" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D274" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F274" t="str">
         <v>SNL</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L274">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M274">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N274">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="O274" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B275" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C275" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D275" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,45 +13303,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L275">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M275">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N275">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O275" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B276" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C276" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D276" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F276" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G276" t="str">
         <v>Sewing</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L276">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M276">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N276">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="O276" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B277" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C277" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D277" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Thread trim full garment</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F277" t="str">
         <v>SNL</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L277">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M277">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N277">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="O277" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B278" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C278" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D278" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F278" t="str">
         <v>SNL</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L278">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M278">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N278">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O278" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B279" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C279" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D279" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Full body pressing</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F279" t="str">
         <v>VIR</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
+        <v>3</v>
+      </c>
+      <c r="J279" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="K279" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="L279">
+        <v>646</v>
+      </c>
+      <c r="M279">
+        <v>15.28</v>
+      </c>
+      <c r="N279">
         <v>2</v>
       </c>
-      <c r="J279" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="K279" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="L279">
-        <v>607</v>
-      </c>
-      <c r="M279">
-        <v>19</v>
-      </c>
-      <c r="N279">
-        <v>3.2</v>
-      </c>
       <c r="O279" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B280" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C280" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D280" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F280" t="str">
         <v>VIR</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L280">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M280">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N280">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O280" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B281" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C281" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D281" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,42 +13585,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L281">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M281">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N281">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O281" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B282" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C282" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D282" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E282" t="str">
-        <v>Hang tag attach</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F282" t="str">
         <v>HELP</v>
@@ -13632,42 +13632,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L282">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M282">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N282">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O282" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B283" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C283" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D283" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F283" t="str">
         <v>HELP</v>
@@ -13679,25 +13679,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L283">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M283">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N283">
         <v>1.1</v>
       </c>
       <c r="O283" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="284">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B140" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C140" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D140" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E140" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L140">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M140">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N140">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="O140" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B141" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C141" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D141" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach cuff</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L141">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M141">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O141" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B142" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C142" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D142" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L142">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M142">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N142">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="O142" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B143" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C143" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D143" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L143">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M143">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O143" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B144" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C144" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D144" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L144">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M144">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="O144" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B145" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C145" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D145" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L145">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M145">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N145">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O145" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B146" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C146" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D146" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L146">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M146">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O146" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B147" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C147" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D147" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F147" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G147" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L147">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M147">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N147">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="O147" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B148" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C148" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D148" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L148">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M148">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O148" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B149" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C149" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D149" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F149" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L149">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M149">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N149">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O149" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B150" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C150" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D150" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L150">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M150">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N150">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O150" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B151" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C151" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D151" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F151" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L151">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M151">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N151">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="O151" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B152" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C152" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D152" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L152">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M152">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N152">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O152" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B153" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C153" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D153" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L153">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M153">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O153" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B154" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C154" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D154" t="str">
-        <v>BL::MX RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E154" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F154" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G154" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,22 +7619,22 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L154">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M154">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N154">
-        <v>0.43</v>
+        <v>1.1</v>
       </c>
       <c r="O154" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="155">
@@ -7648,10 +7648,10 @@
         <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E155" t="str">
-        <v>Attach cuff</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,10 +7666,10 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L155">
         <v>2190</v>
@@ -7678,7 +7678,7 @@
         <v>17.96</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O155" t="str">
         <v>mudithaj</v>
@@ -7695,10 +7695,10 @@
         <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F156" t="str">
         <v>SNL</v>
@@ -7713,10 +7713,10 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L156">
         <v>2190</v>
@@ -7725,7 +7725,7 @@
         <v>17.96</v>
       </c>
       <c r="N156">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O156" t="str">
         <v>mudithaj</v>
@@ -7742,10 +7742,10 @@
         <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F157" t="str">
         <v>SNL</v>
@@ -7760,10 +7760,10 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L157">
         <v>2190</v>
@@ -7772,7 +7772,7 @@
         <v>17.96</v>
       </c>
       <c r="N157">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O157" t="str">
         <v>mudithaj</v>
@@ -7789,10 +7789,10 @@
         <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,10 +7807,10 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L158">
         <v>2190</v>
@@ -7819,7 +7819,7 @@
         <v>17.96</v>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O158" t="str">
         <v>mudithaj</v>
@@ -7836,10 +7836,10 @@
         <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F159" t="str">
         <v>SNL</v>
@@ -7854,10 +7854,10 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L159">
         <v>2190</v>
@@ -7866,7 +7866,7 @@
         <v>17.96</v>
       </c>
       <c r="N159">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O159" t="str">
         <v>mudithaj</v>
@@ -7883,13 +7883,13 @@
         <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F160" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G160" t="str">
         <v>Sewing</v>
@@ -7901,10 +7901,10 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L160">
         <v>2190</v>
@@ -7913,7 +7913,7 @@
         <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O160" t="str">
         <v>mudithaj</v>
@@ -7930,16 +7930,16 @@
         <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F161" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G161" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,10 +7948,10 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L161">
         <v>2190</v>
@@ -7960,7 +7960,7 @@
         <v>17.96</v>
       </c>
       <c r="N161">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O161" t="str">
         <v>mudithaj</v>
@@ -7977,10 +7977,10 @@
         <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F162" t="str">
         <v>SNL</v>
@@ -7995,10 +7995,10 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L162">
         <v>2190</v>
@@ -8007,7 +8007,7 @@
         <v>17.96</v>
       </c>
       <c r="N162">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O162" t="str">
         <v>mudithaj</v>
@@ -8024,13 +8024,13 @@
         <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F163" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,10 +8042,10 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L163">
         <v>2190</v>
@@ -8071,10 +8071,10 @@
         <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F164" t="str">
         <v>VIR</v>
@@ -8089,10 +8089,10 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L164">
         <v>2190</v>
@@ -8101,7 +8101,7 @@
         <v>17.96</v>
       </c>
       <c r="N164">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O164" t="str">
         <v>mudithaj</v>
@@ -8118,13 +8118,13 @@
         <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F165" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,10 +8136,10 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L165">
         <v>2190</v>
@@ -8148,7 +8148,7 @@
         <v>17.96</v>
       </c>
       <c r="N165">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="O165" t="str">
         <v>mudithaj</v>
@@ -8165,10 +8165,10 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F166" t="str">
         <v>HELP</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,10 +8212,10 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F167" t="str">
         <v>HELP</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E168" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F168" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G168" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8306,10 +8306,10 @@
         <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E169" t="str">
-        <v>Attach cuff</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,10 +8324,10 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L169">
         <v>2190</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8353,10 +8353,10 @@
         <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,10 +8371,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L170">
         <v>2190</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8400,10 +8400,10 @@
         <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8418,10 +8418,10 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L171">
         <v>2190</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8447,10 +8447,10 @@
         <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F172" t="str">
         <v>SNL</v>
@@ -8465,10 +8465,10 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L172">
         <v>2190</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8494,10 +8494,10 @@
         <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
@@ -8512,10 +8512,10 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L173">
         <v>2190</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8541,13 +8541,13 @@
         <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F174" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G174" t="str">
         <v>Sewing</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L174">
         <v>2190</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8588,16 +8588,16 @@
         <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F175" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G175" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8606,10 +8606,10 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L175">
         <v>2190</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8635,10 +8635,10 @@
         <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F176" t="str">
         <v>SNL</v>
@@ -8653,10 +8653,10 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L176">
         <v>2190</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8682,13 +8682,13 @@
         <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F177" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,10 +8700,10 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L177">
         <v>2190</v>
@@ -8729,10 +8729,10 @@
         <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F178" t="str">
         <v>VIR</v>
@@ -8747,10 +8747,10 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L178">
         <v>2190</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8776,13 +8776,13 @@
         <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F179" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8794,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L179">
         <v>2190</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8823,10 +8823,10 @@
         <v>Blouse</v>
       </c>
       <c r="D180" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F180" t="str">
         <v>HELP</v>
@@ -8841,10 +8841,10 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L180">
         <v>2190</v>
@@ -8853,7 +8853,7 @@
         <v>17.96</v>
       </c>
       <c r="N180">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O180" t="str">
         <v>mudithaj</v>
@@ -8870,10 +8870,10 @@
         <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F181" t="str">
         <v>HELP</v>
@@ -8888,10 +8888,10 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L181">
         <v>2190</v>
@@ -8900,7 +8900,7 @@
         <v>17.96</v>
       </c>
       <c r="N181">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O181" t="str">
         <v>mudithaj</v>
@@ -8908,25 +8908,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B182" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C182" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D182" t="str">
-        <v>JK::B</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E182" t="str">
-        <v>Attach back stitch</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F182" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G182" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L182">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M182">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N182">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="O182" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B183" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C183" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D183" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E183" t="str">
-        <v>Attach pocket bag</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,39 +8982,39 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L183">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M183">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N183">
-        <v>0.56</v>
+        <v>0.43</v>
       </c>
       <c r="O183" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B184" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C184" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D184" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F184" t="str">
         <v>SNL</v>
@@ -9029,39 +9029,39 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L184">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M184">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N184">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="O184" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B185" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C185" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D185" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E185" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F185" t="str">
         <v>SNL</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L185">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M185">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N185">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="O185" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B186" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C186" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D186" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E186" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F186" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L186">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M186">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N186">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="O186" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B187" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C187" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D187" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E187" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F187" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,42 +9170,42 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L187">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M187">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N187">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="O187" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B188" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C188" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D188" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E188" t="str">
-        <v>Attach zipper front</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F188" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G188" t="str">
         <v>Sewing</v>
@@ -9217,42 +9217,42 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L188">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M188">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N188">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O188" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B189" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C189" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D189" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E189" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F189" t="str">
-        <v>LDN</v>
+        <v>SNLU</v>
       </c>
       <c r="G189" t="str">
         <v>Sewing</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L189">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M189">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N189">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="O189" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B190" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C190" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D190" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E190" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F190" t="str">
         <v>SNL</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L190">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M190">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N190">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O190" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B191" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C191" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D191" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E191" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F191" t="str">
         <v>SNL</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L191">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M191">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N191">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O191" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B192" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C192" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D192" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E192" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F192" t="str">
         <v>VIR</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L192">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M192">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N192">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O192" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B193" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C193" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D193" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E193" t="str">
-        <v>Final press full jacket</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F193" t="str">
         <v>VIR</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L193">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M193">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N193">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O193" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B194" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C194" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D194" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E194" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,39 +9499,39 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L194">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M194">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N194">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="O194" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B195" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C195" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D195" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E195" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F195" t="str">
         <v>HELP</v>
@@ -9546,39 +9546,39 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L195">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M195">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N195">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O195" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B196" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C196" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D196" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E196" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F196" t="str">
         <v>HELP</v>
@@ -9593,22 +9593,22 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L196">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M196">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N196">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O196" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="197">
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E197" t="str">
         <v>Attach back stitch</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E198" t="str">
         <v>Attach pocket bag</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E199" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E200" t="str">
         <v>Collar attach to body</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E201" t="str">
         <v>Collar attach lining</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E202" t="str">
         <v>Sleeve attach overlock</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E203" t="str">
         <v>Attach zipper front</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E204" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E205" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E206" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E207" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E208" t="str">
         <v>Final press full jacket</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E209" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E210" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E211" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E212" t="str">
         <v>Attach back stitch</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E213" t="str">
         <v>Attach pocket bag</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E214" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E215" t="str">
         <v>Collar attach to body</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E216" t="str">
         <v>Collar attach lining</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E217" t="str">
         <v>Sleeve attach overlock</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E218" t="str">
         <v>Attach zipper front</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E219" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E220" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E221" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E222" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E223" t="str">
         <v>Final press full jacket</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E224" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10938,7 +10938,7 @@
         <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E225" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10956,10 +10956,10 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L225">
         <v>500</v>
@@ -10985,7 +10985,7 @@
         <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E226" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -11003,10 +11003,10 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L226">
         <v>500</v>
@@ -11023,19 +11023,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B227" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C227" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D227" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,39 +11050,39 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L227">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M227">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N227">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O227" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B228" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C228" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D228" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E228" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F228" t="str">
         <v>SNL</v>
@@ -11097,39 +11097,39 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L228">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M228">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N228">
-        <v>1.2</v>
+        <v>0.56</v>
       </c>
       <c r="O228" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B229" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C229" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D229" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E229" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L229">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M229">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N229">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="O229" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B230" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C230" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D230" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E230" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F230" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L230">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M230">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N230">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O230" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B231" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C231" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D231" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E231" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F231" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,42 +11238,42 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L231">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M231">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N231">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="O231" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B232" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C232" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D232" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E232" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F232" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G232" t="str">
         <v>Sewing</v>
@@ -11285,42 +11285,42 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L232">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M232">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N232">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="O232" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B233" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C233" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D233" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E233" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F233" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G233" t="str">
         <v>Sewing</v>
@@ -11332,45 +11332,45 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L233">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M233">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N233">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="O233" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B234" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C234" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D234" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E234" t="str">
-        <v>Thread trim full garment</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F234" t="str">
-        <v>SNL</v>
+        <v>LDN</v>
       </c>
       <c r="G234" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L234">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M234">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N234">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="O234" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B235" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C235" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D235" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E235" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F235" t="str">
         <v>SNL</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L235">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M235">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N235">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O235" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B236" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C236" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D236" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E236" t="str">
-        <v>Full body pressing</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F236" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L236">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M236">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N236">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="O236" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B237" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C237" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D237" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E237" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F237" t="str">
         <v>VIR</v>
@@ -11520,42 +11520,42 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L237">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M237">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N237">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O237" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B238" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C238" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D238" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E238" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F238" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11567,39 +11567,39 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L238">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M238">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N238">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="O238" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B239" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C239" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D239" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E239" t="str">
-        <v>Hang tag attach</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F239" t="str">
         <v>HELP</v>
@@ -11614,39 +11614,39 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L239">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M239">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N239">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O239" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B240" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C240" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D240" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E240" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F240" t="str">
         <v>HELP</v>
@@ -11661,45 +11661,45 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L240">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M240">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N240">
         <v>1.1</v>
       </c>
       <c r="O240" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B241" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C241" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D241" t="str">
-        <v>BL::US RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E241" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F241" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G241" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,22 +11708,22 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L241">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M241">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N241">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O241" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="242">
@@ -11737,10 +11737,10 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F242" t="str">
         <v>SNL</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,10 +11784,10 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,13 +11831,13 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F244" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G244" t="str">
         <v>Sewing</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,13 +11878,13 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F245" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,10 +11925,10 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,16 +12019,16 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F248" t="str">
         <v>SNL</v>
       </c>
       <c r="G248" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F249" t="str">
         <v>SNL</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F250" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F251" t="str">
         <v>VIR</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,13 +12207,13 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F252" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,10 +12254,10 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F253" t="str">
         <v>HELP</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F254" t="str">
         <v>HELP</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F255" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G255" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12395,10 +12395,10 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F256" t="str">
         <v>SNL</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,10 +12442,10 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,13 +12489,13 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F258" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G258" t="str">
         <v>Sewing</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,13 +12536,13 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F259" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,10 +12583,10 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,16 +12677,16 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F262" t="str">
         <v>SNL</v>
       </c>
       <c r="G262" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F263" t="str">
         <v>SNL</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F264" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F265" t="str">
         <v>VIR</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,13 +12865,13 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F266" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12912,10 +12912,10 @@
         <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F267" t="str">
         <v>HELP</v>
@@ -12930,10 +12930,10 @@
         <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L267">
         <v>607</v>
@@ -12942,7 +12942,7 @@
         <v>19</v>
       </c>
       <c r="N267">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O267" t="str">
         <v>sasanthar</v>
@@ -12959,10 +12959,10 @@
         <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F268" t="str">
         <v>HELP</v>
@@ -12977,10 +12977,10 @@
         <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L268">
         <v>607</v>
@@ -12989,7 +12989,7 @@
         <v>19</v>
       </c>
       <c r="N268">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O268" t="str">
         <v>sasanthar</v>
@@ -12997,66 +12997,66 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B269" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C269" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D269" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Attach label 2 sides</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F269" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G269" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L269">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M269">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N269">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="O269" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B270" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C270" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D270" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,42 +13068,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L270">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M270">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N270">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="O270" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B271" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C271" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D271" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L271">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M271">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N271">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O271" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B272" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C272" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D272" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,45 +13162,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L272">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M272">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N272">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O272" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B273" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C273" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D273" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F273" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13209,42 +13209,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L273">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M273">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N273">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="O273" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B274" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C274" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D274" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F274" t="str">
         <v>SNL</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L274">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M274">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N274">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="O274" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B275" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C275" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D275" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,45 +13303,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L275">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M275">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N275">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O275" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B276" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C276" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D276" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F276" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G276" t="str">
         <v>Sewing</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L276">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M276">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N276">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="O276" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B277" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C277" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D277" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F277" t="str">
         <v>SNL</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L277">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M277">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N277">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O277" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B278" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C278" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D278" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F278" t="str">
         <v>SNL</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L278">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M278">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N278">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O278" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B279" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C279" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D279" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F279" t="str">
         <v>VIR</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L279">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M279">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N279">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O279" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B280" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C280" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D280" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Final press full shirt</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F280" t="str">
         <v>VIR</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L280">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M280">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N280">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O280" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B281" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C281" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D281" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Label attach manual</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,42 +13585,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L281">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M281">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N281">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O281" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B282" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C282" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D282" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E282" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F282" t="str">
         <v>HELP</v>
@@ -13632,42 +13632,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I282">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L282">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M282">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N282">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O282" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B283" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C283" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D283" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F283" t="str">
         <v>HELP</v>
@@ -13679,25 +13679,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I283">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-05-12</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L283">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M283">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N283">
         <v>1.1</v>
       </c>
       <c r="O283" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="284">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-12</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B140" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C140" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D140" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E140" t="str">
-        <v>Attach label 2 sides</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L140">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M140">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N140">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="O140" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B141" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C141" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D141" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L141">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M141">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N141">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O141" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B142" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C142" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D142" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L142">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M142">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N142">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="O142" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B143" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C143" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D143" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L143">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M143">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N143">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O143" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B144" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C144" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D144" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L144">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M144">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N144">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O144" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B145" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C145" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D145" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L145">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M145">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N145">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O145" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B146" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C146" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D146" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L146">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M146">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N146">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O146" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B147" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C147" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D147" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F147" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G147" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L147">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M147">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N147">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="O147" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B148" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C148" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D148" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L148">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M148">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N148">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O148" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B149" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C149" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D149" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F149" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L149">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M149">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O149" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B150" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C150" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D150" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L150">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M150">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O150" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B151" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C151" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D151" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Final press full shirt</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F151" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L151">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M151">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="O151" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B152" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C152" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D152" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Label attach manual</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L152">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M152">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N152">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O152" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B153" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C153" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D153" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L153">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M153">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N153">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O153" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B154" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C154" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D154" t="str">
-        <v>SH::US RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F154" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G154" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,22 +7619,22 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L154">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M154">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N154">
-        <v>1.1</v>
+        <v>0.43</v>
       </c>
       <c r="O154" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="155">
@@ -7648,10 +7648,10 @@
         <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E155" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,10 +7666,10 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L155">
         <v>2190</v>
@@ -7678,7 +7678,7 @@
         <v>17.96</v>
       </c>
       <c r="N155">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O155" t="str">
         <v>mudithaj</v>
@@ -7695,10 +7695,10 @@
         <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach cuff</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F156" t="str">
         <v>SNL</v>
@@ -7713,10 +7713,10 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L156">
         <v>2190</v>
@@ -7725,7 +7725,7 @@
         <v>17.96</v>
       </c>
       <c r="N156">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O156" t="str">
         <v>mudithaj</v>
@@ -7742,10 +7742,10 @@
         <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F157" t="str">
         <v>SNL</v>
@@ -7760,10 +7760,10 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L157">
         <v>2190</v>
@@ -7772,7 +7772,7 @@
         <v>17.96</v>
       </c>
       <c r="N157">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="O157" t="str">
         <v>mudithaj</v>
@@ -7789,10 +7789,10 @@
         <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,10 +7807,10 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L158">
         <v>2190</v>
@@ -7819,7 +7819,7 @@
         <v>17.96</v>
       </c>
       <c r="N158">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O158" t="str">
         <v>mudithaj</v>
@@ -7836,10 +7836,10 @@
         <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F159" t="str">
         <v>SNL</v>
@@ -7854,10 +7854,10 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L159">
         <v>2190</v>
@@ -7866,7 +7866,7 @@
         <v>17.96</v>
       </c>
       <c r="N159">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O159" t="str">
         <v>mudithaj</v>
@@ -7883,13 +7883,13 @@
         <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F160" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G160" t="str">
         <v>Sewing</v>
@@ -7901,10 +7901,10 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L160">
         <v>2190</v>
@@ -7913,7 +7913,7 @@
         <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O160" t="str">
         <v>mudithaj</v>
@@ -7930,16 +7930,16 @@
         <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F161" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G161" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,10 +7948,10 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L161">
         <v>2190</v>
@@ -7960,7 +7960,7 @@
         <v>17.96</v>
       </c>
       <c r="N161">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O161" t="str">
         <v>mudithaj</v>
@@ -7977,10 +7977,10 @@
         <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F162" t="str">
         <v>SNL</v>
@@ -7995,10 +7995,10 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L162">
         <v>2190</v>
@@ -8007,7 +8007,7 @@
         <v>17.96</v>
       </c>
       <c r="N162">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O162" t="str">
         <v>mudithaj</v>
@@ -8024,13 +8024,13 @@
         <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F163" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,10 +8042,10 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L163">
         <v>2190</v>
@@ -8071,10 +8071,10 @@
         <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F164" t="str">
         <v>VIR</v>
@@ -8089,10 +8089,10 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L164">
         <v>2190</v>
@@ -8101,7 +8101,7 @@
         <v>17.96</v>
       </c>
       <c r="N164">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O164" t="str">
         <v>mudithaj</v>
@@ -8118,13 +8118,13 @@
         <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F165" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,10 +8136,10 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L165">
         <v>2190</v>
@@ -8148,7 +8148,7 @@
         <v>17.96</v>
       </c>
       <c r="N165">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="O165" t="str">
         <v>mudithaj</v>
@@ -8165,10 +8165,10 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F166" t="str">
         <v>HELP</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,10 +8212,10 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F167" t="str">
         <v>HELP</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F168" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G168" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8306,10 +8306,10 @@
         <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E169" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,10 +8324,10 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L169">
         <v>2190</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8353,10 +8353,10 @@
         <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach cuff</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,10 +8371,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L170">
         <v>2190</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8400,10 +8400,10 @@
         <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8418,10 +8418,10 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L171">
         <v>2190</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8447,10 +8447,10 @@
         <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F172" t="str">
         <v>SNL</v>
@@ -8465,10 +8465,10 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L172">
         <v>2190</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8494,10 +8494,10 @@
         <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
@@ -8512,10 +8512,10 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L173">
         <v>2190</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8541,13 +8541,13 @@
         <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F174" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G174" t="str">
         <v>Sewing</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L174">
         <v>2190</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8588,16 +8588,16 @@
         <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F175" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G175" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8606,10 +8606,10 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L175">
         <v>2190</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8635,10 +8635,10 @@
         <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F176" t="str">
         <v>SNL</v>
@@ -8653,10 +8653,10 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L176">
         <v>2190</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8682,13 +8682,13 @@
         <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F177" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,10 +8700,10 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L177">
         <v>2190</v>
@@ -8729,10 +8729,10 @@
         <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F178" t="str">
         <v>VIR</v>
@@ -8747,10 +8747,10 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L178">
         <v>2190</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8776,13 +8776,13 @@
         <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F179" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8794,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L179">
         <v>2190</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>2.2</v>
+        <v>0.7</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8823,10 +8823,10 @@
         <v>Blouse</v>
       </c>
       <c r="D180" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F180" t="str">
         <v>HELP</v>
@@ -8841,10 +8841,10 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L180">
         <v>2190</v>
@@ -8853,7 +8853,7 @@
         <v>17.96</v>
       </c>
       <c r="N180">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O180" t="str">
         <v>mudithaj</v>
@@ -8870,10 +8870,10 @@
         <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F181" t="str">
         <v>HELP</v>
@@ -8888,10 +8888,10 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L181">
         <v>2190</v>
@@ -8900,7 +8900,7 @@
         <v>17.96</v>
       </c>
       <c r="N181">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O181" t="str">
         <v>mudithaj</v>
@@ -8908,25 +8908,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B182" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C182" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D182" t="str">
-        <v>BL::MX RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E182" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F182" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G182" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L182">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M182">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N182">
-        <v>1</v>
+        <v>1.26</v>
       </c>
       <c r="O182" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B183" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C183" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D183" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E183" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,39 +8982,39 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L183">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M183">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N183">
-        <v>0.43</v>
+        <v>0.56</v>
       </c>
       <c r="O183" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B184" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C184" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D184" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach cuff</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F184" t="str">
         <v>SNL</v>
@@ -9029,39 +9029,39 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L184">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M184">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N184">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="O184" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B185" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C185" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D185" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E185" t="str">
-        <v>Attach set band collar</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F185" t="str">
         <v>SNL</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L185">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M185">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N185">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="O185" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B186" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C186" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D186" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach sleeve</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F186" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L186">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M186">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N186">
-        <v>1.5</v>
+        <v>0.84</v>
       </c>
       <c r="O186" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B187" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C187" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D187" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E187" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F187" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,42 +9170,42 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L187">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M187">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N187">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="O187" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B188" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C188" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D188" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E188" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F188" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G188" t="str">
         <v>Sewing</v>
@@ -9217,42 +9217,42 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L188">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M188">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O188" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B189" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C189" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D189" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E189" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F189" t="str">
-        <v>SNLU</v>
+        <v>LDN</v>
       </c>
       <c r="G189" t="str">
         <v>Sewing</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L189">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M189">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N189">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="O189" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B190" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C190" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D190" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E190" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F190" t="str">
         <v>SNL</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L190">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M190">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N190">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O190" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B191" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C191" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D191" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E191" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F191" t="str">
         <v>SNL</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L191">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M191">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N191">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="O191" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B192" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C192" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D192" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E192" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F192" t="str">
         <v>VIR</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L192">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M192">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N192">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O192" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B193" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C193" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D193" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E193" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F193" t="str">
         <v>VIR</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L193">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M193">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N193">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O193" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B194" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C194" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D194" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E194" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,39 +9499,39 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L194">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M194">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N194">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O194" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B195" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C195" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E195" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F195" t="str">
         <v>HELP</v>
@@ -9546,39 +9546,39 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L195">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M195">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N195">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O195" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B196" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C196" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E196" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F196" t="str">
         <v>HELP</v>
@@ -9593,22 +9593,22 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L196">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M196">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N196">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O196" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="197">
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E197" t="str">
         <v>Attach back stitch</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E198" t="str">
         <v>Attach pocket bag</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E199" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E200" t="str">
         <v>Collar attach to body</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E201" t="str">
         <v>Collar attach lining</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E202" t="str">
         <v>Sleeve attach overlock</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E203" t="str">
         <v>Attach zipper front</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E204" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E205" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E206" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E207" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E208" t="str">
         <v>Final press full jacket</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E209" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E210" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E211" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E212" t="str">
         <v>Attach back stitch</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E213" t="str">
         <v>Attach pocket bag</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E214" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E215" t="str">
         <v>Collar attach to body</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E216" t="str">
         <v>Collar attach lining</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E217" t="str">
         <v>Sleeve attach overlock</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E218" t="str">
         <v>Attach zipper front</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E219" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E220" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E221" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E222" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E223" t="str">
         <v>Final press full jacket</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E224" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10938,7 +10938,7 @@
         <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E225" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10956,10 +10956,10 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L225">
         <v>500</v>
@@ -10985,7 +10985,7 @@
         <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E226" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -11003,10 +11003,10 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L226">
         <v>500</v>
@@ -11023,19 +11023,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B227" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C227" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D227" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,39 +11050,39 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L227">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M227">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N227">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O227" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B228" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C228" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D228" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E228" t="str">
-        <v>Attach pocket bag</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F228" t="str">
         <v>SNL</v>
@@ -11097,39 +11097,39 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L228">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M228">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N228">
-        <v>0.56</v>
+        <v>1.2</v>
       </c>
       <c r="O228" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B229" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C229" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D229" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E229" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L229">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M229">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N229">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="O229" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B230" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C230" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D230" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E230" t="str">
-        <v>Collar attach to body</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F230" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L230">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M230">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N230">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="O230" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B231" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C231" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D231" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E231" t="str">
-        <v>Collar attach lining</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F231" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,42 +11238,42 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L231">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M231">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N231">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="O231" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B232" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C232" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D232" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E232" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F232" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G232" t="str">
         <v>Sewing</v>
@@ -11285,42 +11285,42 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L232">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M232">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N232">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="O232" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B233" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C233" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D233" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E233" t="str">
-        <v>Attach zipper front</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F233" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G233" t="str">
         <v>Sewing</v>
@@ -11332,45 +11332,45 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L233">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M233">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N233">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="O233" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B234" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C234" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D234" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E234" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F234" t="str">
-        <v>LDN</v>
+        <v>SNL</v>
       </c>
       <c r="G234" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L234">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M234">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N234">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="O234" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B235" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C235" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D235" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E235" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F235" t="str">
         <v>SNL</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L235">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M235">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N235">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O235" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B236" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C236" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D236" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E236" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F236" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L236">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M236">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N236">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="O236" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B237" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C237" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D237" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E237" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F237" t="str">
         <v>VIR</v>
@@ -11520,42 +11520,42 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L237">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M237">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N237">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="O237" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B238" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C238" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D238" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E238" t="str">
-        <v>Final press full jacket</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F238" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11567,39 +11567,39 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L238">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M238">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N238">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="O238" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B239" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C239" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D239" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E239" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F239" t="str">
         <v>HELP</v>
@@ -11614,39 +11614,39 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L239">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M239">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N239">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O239" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B240" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C240" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F240" t="str">
         <v>HELP</v>
@@ -11661,45 +11661,45 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L240">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M240">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N240">
         <v>1.1</v>
       </c>
       <c r="O240" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B241" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C241" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F241" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G241" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,22 +11708,22 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L241">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M241">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N241">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O241" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="242">
@@ -11737,10 +11737,10 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F242" t="str">
         <v>SNL</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,10 +11784,10 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,13 +11831,13 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F244" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G244" t="str">
         <v>Sewing</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,13 +11878,13 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F245" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,10 +11925,10 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,16 +12019,16 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F248" t="str">
         <v>SNL</v>
       </c>
       <c r="G248" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F249" t="str">
         <v>SNL</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F250" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F251" t="str">
         <v>VIR</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,13 +12207,13 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F252" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,10 +12254,10 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F253" t="str">
         <v>HELP</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F254" t="str">
         <v>HELP</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F255" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G255" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12395,10 +12395,10 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F256" t="str">
         <v>SNL</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,10 +12442,10 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,13 +12489,13 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F258" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G258" t="str">
         <v>Sewing</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,13 +12536,13 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F259" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,10 +12583,10 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,16 +12677,16 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F262" t="str">
         <v>SNL</v>
       </c>
       <c r="G262" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F263" t="str">
         <v>SNL</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F264" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F265" t="str">
         <v>VIR</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,13 +12865,13 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F266" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12912,10 +12912,10 @@
         <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F267" t="str">
         <v>HELP</v>
@@ -12930,10 +12930,10 @@
         <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L267">
         <v>607</v>
@@ -12942,7 +12942,7 @@
         <v>19</v>
       </c>
       <c r="N267">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O267" t="str">
         <v>sasanthar</v>
@@ -12959,10 +12959,10 @@
         <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F268" t="str">
         <v>HELP</v>
@@ -12977,10 +12977,10 @@
         <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L268">
         <v>607</v>
@@ -12989,7 +12989,7 @@
         <v>19</v>
       </c>
       <c r="N268">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O268" t="str">
         <v>sasanthar</v>
@@ -12997,66 +12997,66 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B269" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C269" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D269" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F269" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G269" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L269">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M269">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N269">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="O269" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B270" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C270" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D270" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,42 +13068,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L270">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M270">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N270">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O270" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B271" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C271" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D271" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L271">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M271">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N271">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="O271" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B272" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C272" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D272" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,45 +13162,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L272">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M272">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N272">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O272" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B273" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C273" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D273" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F273" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13209,42 +13209,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L273">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M273">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N273">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="O273" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B274" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C274" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D274" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F274" t="str">
         <v>SNL</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L274">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M274">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N274">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="O274" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B275" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C275" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D275" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,45 +13303,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L275">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M275">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N275">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O275" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B276" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C276" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D276" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F276" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G276" t="str">
         <v>Sewing</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L276">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M276">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N276">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="O276" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B277" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C277" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D277" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Thread trim full garment</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F277" t="str">
         <v>SNL</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L277">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M277">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N277">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="O277" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B278" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C278" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D278" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F278" t="str">
         <v>SNL</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L278">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M278">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N278">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O278" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B279" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C279" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D279" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Full body pressing</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F279" t="str">
         <v>VIR</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
+        <v>3</v>
+      </c>
+      <c r="J279" t="str">
+        <v>2026-05-11</v>
+      </c>
+      <c r="K279" t="str">
+        <v>2026-05-13</v>
+      </c>
+      <c r="L279">
+        <v>646</v>
+      </c>
+      <c r="M279">
+        <v>15.28</v>
+      </c>
+      <c r="N279">
         <v>2</v>
       </c>
-      <c r="J279" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="K279" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="L279">
-        <v>607</v>
-      </c>
-      <c r="M279">
-        <v>19</v>
-      </c>
-      <c r="N279">
-        <v>3.2</v>
-      </c>
       <c r="O279" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B280" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C280" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D280" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F280" t="str">
         <v>VIR</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L280">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M280">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N280">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O280" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B281" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C281" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D281" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,42 +13585,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L281">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M281">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N281">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O281" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B282" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C282" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D282" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E282" t="str">
-        <v>Hang tag attach</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F282" t="str">
         <v>HELP</v>
@@ -13632,42 +13632,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L282">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M282">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N282">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O282" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B283" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C283" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D283" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F283" t="str">
         <v>HELP</v>
@@ -13679,25 +13679,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L283">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M283">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N283">
         <v>1.1</v>
       </c>
       <c r="O283" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="284">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -13024,10 +13024,10 @@
         <v>3</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L269">
         <v>646</v>
@@ -13071,10 +13071,10 @@
         <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L270">
         <v>646</v>
@@ -13118,10 +13118,10 @@
         <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L271">
         <v>646</v>
@@ -13165,10 +13165,10 @@
         <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L272">
         <v>646</v>
@@ -13212,10 +13212,10 @@
         <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L273">
         <v>646</v>
@@ -13259,10 +13259,10 @@
         <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L274">
         <v>646</v>
@@ -13306,10 +13306,10 @@
         <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L275">
         <v>646</v>
@@ -13353,10 +13353,10 @@
         <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L276">
         <v>646</v>
@@ -13400,10 +13400,10 @@
         <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L277">
         <v>646</v>
@@ -13447,10 +13447,10 @@
         <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L278">
         <v>646</v>
@@ -13494,10 +13494,10 @@
         <v>3</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L279">
         <v>646</v>
@@ -13541,10 +13541,10 @@
         <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L280">
         <v>646</v>
@@ -13588,10 +13588,10 @@
         <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L281">
         <v>646</v>
@@ -13635,10 +13635,10 @@
         <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L282">
         <v>646</v>
@@ -13682,10 +13682,10 @@
         <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L283">
         <v>646</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B140" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C140" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D140" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E140" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L140">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M140">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N140">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="O140" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B141" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C141" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D141" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach cuff</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L141">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M141">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O141" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B142" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C142" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D142" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L142">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M142">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N142">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="O142" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B143" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C143" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D143" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L143">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M143">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O143" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B144" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C144" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D144" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L144">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M144">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="O144" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B145" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C145" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D145" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L145">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M145">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N145">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O145" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B146" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C146" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D146" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L146">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M146">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O146" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B147" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C147" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D147" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F147" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G147" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L147">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M147">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N147">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="O147" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B148" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C148" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D148" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L148">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M148">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O148" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B149" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C149" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D149" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F149" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L149">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M149">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N149">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O149" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B150" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C150" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D150" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L150">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M150">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N150">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O150" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B151" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C151" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D151" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F151" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L151">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M151">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N151">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="O151" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B152" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C152" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D152" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L152">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M152">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N152">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O152" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B153" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C153" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D153" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L153">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M153">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O153" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B154" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C154" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D154" t="str">
-        <v>BL::MX RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E154" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F154" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G154" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,22 +7619,22 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L154">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M154">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N154">
-        <v>0.43</v>
+        <v>1.1</v>
       </c>
       <c r="O154" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="155">
@@ -7648,10 +7648,10 @@
         <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E155" t="str">
-        <v>Attach cuff</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,10 +7666,10 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L155">
         <v>2190</v>
@@ -7678,7 +7678,7 @@
         <v>17.96</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O155" t="str">
         <v>mudithaj</v>
@@ -7695,10 +7695,10 @@
         <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F156" t="str">
         <v>SNL</v>
@@ -7713,10 +7713,10 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L156">
         <v>2190</v>
@@ -7725,7 +7725,7 @@
         <v>17.96</v>
       </c>
       <c r="N156">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O156" t="str">
         <v>mudithaj</v>
@@ -7742,10 +7742,10 @@
         <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F157" t="str">
         <v>SNL</v>
@@ -7760,10 +7760,10 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L157">
         <v>2190</v>
@@ -7772,7 +7772,7 @@
         <v>17.96</v>
       </c>
       <c r="N157">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O157" t="str">
         <v>mudithaj</v>
@@ -7789,10 +7789,10 @@
         <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,10 +7807,10 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L158">
         <v>2190</v>
@@ -7819,7 +7819,7 @@
         <v>17.96</v>
       </c>
       <c r="N158">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O158" t="str">
         <v>mudithaj</v>
@@ -7836,10 +7836,10 @@
         <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F159" t="str">
         <v>SNL</v>
@@ -7854,10 +7854,10 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L159">
         <v>2190</v>
@@ -7866,7 +7866,7 @@
         <v>17.96</v>
       </c>
       <c r="N159">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O159" t="str">
         <v>mudithaj</v>
@@ -7883,13 +7883,13 @@
         <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F160" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G160" t="str">
         <v>Sewing</v>
@@ -7901,10 +7901,10 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L160">
         <v>2190</v>
@@ -7913,7 +7913,7 @@
         <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O160" t="str">
         <v>mudithaj</v>
@@ -7930,16 +7930,16 @@
         <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F161" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G161" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,10 +7948,10 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L161">
         <v>2190</v>
@@ -7960,7 +7960,7 @@
         <v>17.96</v>
       </c>
       <c r="N161">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O161" t="str">
         <v>mudithaj</v>
@@ -7977,10 +7977,10 @@
         <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F162" t="str">
         <v>SNL</v>
@@ -7995,10 +7995,10 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L162">
         <v>2190</v>
@@ -8007,7 +8007,7 @@
         <v>17.96</v>
       </c>
       <c r="N162">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O162" t="str">
         <v>mudithaj</v>
@@ -8024,13 +8024,13 @@
         <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F163" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,10 +8042,10 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L163">
         <v>2190</v>
@@ -8071,10 +8071,10 @@
         <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F164" t="str">
         <v>VIR</v>
@@ -8089,10 +8089,10 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L164">
         <v>2190</v>
@@ -8101,7 +8101,7 @@
         <v>17.96</v>
       </c>
       <c r="N164">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O164" t="str">
         <v>mudithaj</v>
@@ -8118,13 +8118,13 @@
         <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F165" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,10 +8136,10 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L165">
         <v>2190</v>
@@ -8148,7 +8148,7 @@
         <v>17.96</v>
       </c>
       <c r="N165">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="O165" t="str">
         <v>mudithaj</v>
@@ -8165,10 +8165,10 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F166" t="str">
         <v>HELP</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,10 +8212,10 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F167" t="str">
         <v>HELP</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E168" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F168" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G168" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8306,10 +8306,10 @@
         <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E169" t="str">
-        <v>Attach cuff</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,10 +8324,10 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L169">
         <v>2190</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8353,10 +8353,10 @@
         <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,10 +8371,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L170">
         <v>2190</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8400,10 +8400,10 @@
         <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8418,10 +8418,10 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L171">
         <v>2190</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8447,10 +8447,10 @@
         <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F172" t="str">
         <v>SNL</v>
@@ -8465,10 +8465,10 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L172">
         <v>2190</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8494,10 +8494,10 @@
         <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
@@ -8512,10 +8512,10 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L173">
         <v>2190</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8541,13 +8541,13 @@
         <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F174" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G174" t="str">
         <v>Sewing</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L174">
         <v>2190</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8588,16 +8588,16 @@
         <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F175" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G175" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8606,10 +8606,10 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L175">
         <v>2190</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8635,10 +8635,10 @@
         <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F176" t="str">
         <v>SNL</v>
@@ -8653,10 +8653,10 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L176">
         <v>2190</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8682,13 +8682,13 @@
         <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F177" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,10 +8700,10 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L177">
         <v>2190</v>
@@ -8729,10 +8729,10 @@
         <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F178" t="str">
         <v>VIR</v>
@@ -8747,10 +8747,10 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L178">
         <v>2190</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8776,13 +8776,13 @@
         <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F179" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8794,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L179">
         <v>2190</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8823,10 +8823,10 @@
         <v>Blouse</v>
       </c>
       <c r="D180" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F180" t="str">
         <v>HELP</v>
@@ -8841,10 +8841,10 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L180">
         <v>2190</v>
@@ -8853,7 +8853,7 @@
         <v>17.96</v>
       </c>
       <c r="N180">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O180" t="str">
         <v>mudithaj</v>
@@ -8870,10 +8870,10 @@
         <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F181" t="str">
         <v>HELP</v>
@@ -8888,10 +8888,10 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L181">
         <v>2190</v>
@@ -8900,7 +8900,7 @@
         <v>17.96</v>
       </c>
       <c r="N181">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O181" t="str">
         <v>mudithaj</v>
@@ -8908,25 +8908,25 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B182" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C182" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D182" t="str">
-        <v>JK::B</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E182" t="str">
-        <v>Attach back stitch</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F182" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G182" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L182">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M182">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N182">
-        <v>1.26</v>
+        <v>1</v>
       </c>
       <c r="O182" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B183" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C183" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D183" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E183" t="str">
-        <v>Attach pocket bag</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,39 +8982,39 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L183">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M183">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N183">
-        <v>0.56</v>
+        <v>0.43</v>
       </c>
       <c r="O183" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B184" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C184" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D184" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F184" t="str">
         <v>SNL</v>
@@ -9029,39 +9029,39 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L184">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M184">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N184">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="O184" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B185" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C185" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D185" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E185" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F185" t="str">
         <v>SNL</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L185">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M185">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N185">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="O185" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B186" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C186" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D186" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E186" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F186" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L186">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M186">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N186">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="O186" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B187" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C187" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D187" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E187" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F187" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,42 +9170,42 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L187">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M187">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N187">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="O187" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B188" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C188" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D188" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E188" t="str">
-        <v>Attach zipper front</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F188" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G188" t="str">
         <v>Sewing</v>
@@ -9217,42 +9217,42 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L188">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M188">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N188">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O188" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B189" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C189" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D189" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E189" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F189" t="str">
-        <v>LDN</v>
+        <v>SNLU</v>
       </c>
       <c r="G189" t="str">
         <v>Sewing</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L189">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M189">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N189">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="O189" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B190" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C190" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D190" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E190" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F190" t="str">
         <v>SNL</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L190">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M190">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N190">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O190" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B191" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C191" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D191" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E191" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F191" t="str">
         <v>SNL</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L191">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M191">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N191">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O191" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B192" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C192" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D192" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E192" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F192" t="str">
         <v>VIR</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L192">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M192">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N192">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O192" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B193" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C193" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D193" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E193" t="str">
-        <v>Final press full jacket</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F193" t="str">
         <v>VIR</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L193">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M193">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N193">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O193" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B194" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C194" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D194" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E194" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,39 +9499,39 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L194">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M194">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N194">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="O194" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B195" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C195" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D195" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E195" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F195" t="str">
         <v>HELP</v>
@@ -9546,39 +9546,39 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L195">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M195">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N195">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O195" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B196" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C196" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D196" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E196" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F196" t="str">
         <v>HELP</v>
@@ -9593,22 +9593,22 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L196">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M196">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N196">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O196" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="197">
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E197" t="str">
         <v>Attach back stitch</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E198" t="str">
         <v>Attach pocket bag</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E199" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E200" t="str">
         <v>Collar attach to body</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E201" t="str">
         <v>Collar attach lining</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E202" t="str">
         <v>Sleeve attach overlock</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E203" t="str">
         <v>Attach zipper front</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E204" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E205" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E206" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E207" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E208" t="str">
         <v>Final press full jacket</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E209" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E210" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E211" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E212" t="str">
         <v>Attach back stitch</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E213" t="str">
         <v>Attach pocket bag</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E214" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E215" t="str">
         <v>Collar attach to body</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E216" t="str">
         <v>Collar attach lining</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E217" t="str">
         <v>Sleeve attach overlock</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E218" t="str">
         <v>Attach zipper front</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E219" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E220" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E221" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E222" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E223" t="str">
         <v>Final press full jacket</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E224" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10938,7 +10938,7 @@
         <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E225" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10956,10 +10956,10 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L225">
         <v>500</v>
@@ -10985,7 +10985,7 @@
         <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E226" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -11003,10 +11003,10 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L226">
         <v>500</v>
@@ -11023,19 +11023,19 @@
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B227" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C227" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D227" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,39 +11050,39 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L227">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M227">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N227">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O227" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B228" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C228" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D228" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E228" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F228" t="str">
         <v>SNL</v>
@@ -11097,39 +11097,39 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L228">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M228">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N228">
-        <v>1.2</v>
+        <v>0.56</v>
       </c>
       <c r="O228" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B229" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C229" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D229" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E229" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L229">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M229">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N229">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="O229" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B230" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C230" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D230" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E230" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F230" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L230">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M230">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N230">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O230" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B231" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C231" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D231" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E231" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F231" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,42 +11238,42 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L231">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M231">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N231">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="O231" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B232" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C232" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D232" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E232" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F232" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G232" t="str">
         <v>Sewing</v>
@@ -11285,42 +11285,42 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L232">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M232">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N232">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="O232" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B233" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C233" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D233" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E233" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F233" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G233" t="str">
         <v>Sewing</v>
@@ -11332,45 +11332,45 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L233">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M233">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N233">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="O233" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B234" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C234" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D234" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E234" t="str">
-        <v>Thread trim full garment</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F234" t="str">
-        <v>SNL</v>
+        <v>LDN</v>
       </c>
       <c r="G234" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L234">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M234">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N234">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="O234" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B235" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C235" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D235" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E235" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F235" t="str">
         <v>SNL</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L235">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M235">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N235">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O235" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B236" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C236" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D236" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E236" t="str">
-        <v>Full body pressing</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F236" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L236">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M236">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N236">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="O236" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B237" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C237" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D237" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E237" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F237" t="str">
         <v>VIR</v>
@@ -11520,42 +11520,42 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L237">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M237">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N237">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O237" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B238" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C238" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D238" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E238" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F238" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11567,39 +11567,39 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L238">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M238">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N238">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="O238" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B239" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C239" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D239" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E239" t="str">
-        <v>Hang tag attach</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F239" t="str">
         <v>HELP</v>
@@ -11614,39 +11614,39 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L239">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M239">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N239">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O239" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B240" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C240" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D240" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E240" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F240" t="str">
         <v>HELP</v>
@@ -11661,45 +11661,45 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L240">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M240">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N240">
         <v>1.1</v>
       </c>
       <c r="O240" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B241" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C241" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D241" t="str">
-        <v>BL::US RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E241" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F241" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G241" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,22 +11708,22 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L241">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M241">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N241">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O241" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="242">
@@ -11737,10 +11737,10 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F242" t="str">
         <v>SNL</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,10 +11784,10 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,13 +11831,13 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F244" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G244" t="str">
         <v>Sewing</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,13 +11878,13 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F245" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,10 +11925,10 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,16 +12019,16 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F248" t="str">
         <v>SNL</v>
       </c>
       <c r="G248" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F249" t="str">
         <v>SNL</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F250" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F251" t="str">
         <v>VIR</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,13 +12207,13 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F252" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,10 +12254,10 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F253" t="str">
         <v>HELP</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F254" t="str">
         <v>HELP</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F255" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G255" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12395,10 +12395,10 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F256" t="str">
         <v>SNL</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,10 +12442,10 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,13 +12489,13 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F258" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G258" t="str">
         <v>Sewing</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,13 +12536,13 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F259" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,10 +12583,10 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,16 +12677,16 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F262" t="str">
         <v>SNL</v>
       </c>
       <c r="G262" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F263" t="str">
         <v>SNL</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F264" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F265" t="str">
         <v>VIR</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,13 +12865,13 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F266" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12912,10 +12912,10 @@
         <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F267" t="str">
         <v>HELP</v>
@@ -12930,10 +12930,10 @@
         <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L267">
         <v>607</v>
@@ -12942,7 +12942,7 @@
         <v>19</v>
       </c>
       <c r="N267">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O267" t="str">
         <v>sasanthar</v>
@@ -12959,10 +12959,10 @@
         <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F268" t="str">
         <v>HELP</v>
@@ -12977,10 +12977,10 @@
         <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L268">
         <v>607</v>
@@ -12989,7 +12989,7 @@
         <v>19</v>
       </c>
       <c r="N268">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O268" t="str">
         <v>sasanthar</v>
@@ -12997,66 +12997,66 @@
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B269" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C269" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D269" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Attach label 2 sides</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F269" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G269" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L269">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M269">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N269">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="O269" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B270" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C270" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D270" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,42 +13068,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L270">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M270">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N270">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="O270" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B271" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C271" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D271" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L271">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M271">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N271">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O271" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B272" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C272" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D272" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,45 +13162,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L272">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M272">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N272">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O272" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B273" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C273" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D273" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F273" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13209,42 +13209,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L273">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M273">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N273">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="O273" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B274" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C274" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D274" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F274" t="str">
         <v>SNL</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L274">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M274">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N274">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="O274" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B275" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C275" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D275" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,45 +13303,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L275">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M275">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N275">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O275" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B276" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C276" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D276" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F276" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G276" t="str">
         <v>Sewing</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L276">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M276">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N276">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="O276" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B277" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C277" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D277" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F277" t="str">
         <v>SNL</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L277">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M277">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N277">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O277" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B278" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C278" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D278" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F278" t="str">
         <v>SNL</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L278">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M278">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N278">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O278" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B279" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C279" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D279" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F279" t="str">
         <v>VIR</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L279">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M279">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N279">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O279" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B280" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C280" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D280" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Final press full shirt</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F280" t="str">
         <v>VIR</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L280">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M280">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N280">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O280" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B281" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C281" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D281" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Label attach manual</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,42 +13585,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L281">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M281">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N281">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O281" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B282" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C282" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D282" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E282" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F282" t="str">
         <v>HELP</v>
@@ -13632,42 +13632,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I282">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L282">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M282">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N282">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O282" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B283" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C283" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D283" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F283" t="str">
         <v>HELP</v>
@@ -13679,25 +13679,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I283">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L283">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M283">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N283">
         <v>1.1</v>
       </c>
       <c r="O283" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="284">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B140" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C140" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D140" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E140" t="str">
-        <v>Attach label 2 sides</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L140">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M140">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N140">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="O140" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B141" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C141" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D141" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L141">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M141">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N141">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O141" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B142" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C142" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D142" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L142">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M142">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N142">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="O142" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B143" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C143" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D143" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L143">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M143">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N143">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O143" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B144" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C144" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D144" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L144">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M144">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N144">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O144" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B145" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C145" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D145" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L145">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M145">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N145">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O145" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B146" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C146" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D146" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L146">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M146">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N146">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O146" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B147" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C147" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D147" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F147" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G147" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L147">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M147">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N147">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="O147" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B148" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C148" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D148" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L148">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M148">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N148">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O148" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B149" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C149" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D149" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F149" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L149">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M149">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O149" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B150" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C150" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D150" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L150">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M150">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O150" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B151" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C151" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D151" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Final press full shirt</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F151" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L151">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M151">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="O151" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B152" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C152" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D152" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Label attach manual</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L152">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M152">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N152">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O152" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B153" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C153" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D153" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L153">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M153">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N153">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O153" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>935</v>
+        <v>910</v>
       </c>
       <c r="B154" t="str">
-        <v>4462A::SH</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C154" t="str">
-        <v>Shirt</v>
+        <v>Pant</v>
       </c>
       <c r="D154" t="str">
-        <v>SH::US RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Attach waistband - curved</v>
       </c>
       <c r="F154" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G154" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,19 +7619,19 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L154">
-        <v>646</v>
+        <v>1890</v>
       </c>
       <c r="M154">
-        <v>15.28</v>
+        <v>14</v>
       </c>
       <c r="N154">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O154" t="str">
         <v>priyanthi</v>
@@ -7639,19 +7639,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B155" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C155" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E155" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Join inseam double stitch</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,42 +7666,42 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L155">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M155">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N155">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O155" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B156" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C156" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach cuff</v>
+        <v>Outseam overlock &amp; topstitch</v>
       </c>
       <c r="F156" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G156" t="str">
         <v>Sewing</v>
@@ -7713,42 +7713,42 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L156">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M156">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N156">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O156" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B157" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C157" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach zipper to fly</v>
       </c>
       <c r="F157" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G157" t="str">
         <v>Sewing</v>
@@ -7760,39 +7760,39 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L157">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M157">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N157">
-        <v>0.68</v>
+        <v>1.1</v>
       </c>
       <c r="O157" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B158" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C158" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach sleeve</v>
+        <v>Hem bottom with blind stitch</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,42 +7807,42 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L158">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M158">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N158">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O158" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B159" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C159" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Bartack pocket corners</v>
       </c>
       <c r="F159" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G159" t="str">
         <v>Sewing</v>
@@ -7854,45 +7854,45 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L159">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M159">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N159">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="O159" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B160" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C160" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F160" t="str">
         <v>SNL</v>
       </c>
       <c r="G160" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H160" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7901,45 +7901,45 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L160">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M160">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N160">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O160" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B161" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C161" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Press leg crease both sides</v>
       </c>
       <c r="F161" t="str">
-        <v>SNLU</v>
+        <v>VIR</v>
       </c>
       <c r="G161" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,42 +7948,42 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L161">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M161">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N161">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="O161" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B162" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C162" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Final press &amp; steam waistband</v>
       </c>
       <c r="F162" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G162" t="str">
         <v>Finishing</v>
@@ -7995,42 +7995,42 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L162">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M162">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N162">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O162" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B163" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C163" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Attach main &amp; care label</v>
       </c>
       <c r="F163" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,42 +8042,42 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L163">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M163">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N163">
-        <v>1.8</v>
+        <v>0.75</v>
       </c>
       <c r="O163" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B164" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C164" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F164" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G164" t="str">
         <v>Finishing</v>
@@ -8089,42 +8089,42 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L164">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M164">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N164">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="O164" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B165" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C165" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Fold, board insert &amp; poly bag</v>
       </c>
       <c r="F165" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,22 +8136,22 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L165">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M165">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N165">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="O165" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="166">
@@ -8165,16 +8165,16 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F166" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G166" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H166" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,16 +8212,16 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F167" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G167" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H167" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F168" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G168" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8306,10 +8306,10 @@
         <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E169" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,10 +8324,10 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L169">
         <v>2190</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>0.43</v>
+        <v>1.5</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8353,10 +8353,10 @@
         <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach cuff</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,10 +8371,10 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L170">
         <v>2190</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8400,10 +8400,10 @@
         <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8418,10 +8418,10 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L171">
         <v>2190</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>0.68</v>
+        <v>1.5</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8447,13 +8447,13 @@
         <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach sleeve</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F172" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G172" t="str">
         <v>Sewing</v>
@@ -8465,10 +8465,10 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L172">
         <v>2190</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8494,16 +8494,16 @@
         <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
       </c>
       <c r="G173" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H173" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8512,10 +8512,10 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L173">
         <v>2190</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8541,16 +8541,16 @@
         <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F174" t="str">
         <v>SNL</v>
       </c>
       <c r="G174" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H174" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8559,10 +8559,10 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L174">
         <v>2190</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8588,16 +8588,16 @@
         <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F175" t="str">
-        <v>SNLU</v>
+        <v>VIR</v>
       </c>
       <c r="G175" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8606,10 +8606,10 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L175">
         <v>2190</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8635,13 +8635,13 @@
         <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F176" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G176" t="str">
         <v>Finishing</v>
@@ -8653,10 +8653,10 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L176">
         <v>2190</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8682,13 +8682,13 @@
         <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F177" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,10 +8700,10 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L177">
         <v>2190</v>
@@ -8712,7 +8712,7 @@
         <v>17.96</v>
       </c>
       <c r="N177">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="O177" t="str">
         <v>mudithaj</v>
@@ -8729,13 +8729,13 @@
         <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F178" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G178" t="str">
         <v>Finishing</v>
@@ -8747,10 +8747,10 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L178">
         <v>2190</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>1.8</v>
+        <v>0.85</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8776,13 +8776,13 @@
         <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F179" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8794,10 +8794,10 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L179">
         <v>2190</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8814,25 +8814,25 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B180" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C180" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D180" t="str">
-        <v>BL::MX RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E180" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F180" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G180" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H180" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8841,45 +8841,45 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L180">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M180">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N180">
-        <v>0.7</v>
+        <v>1.26</v>
       </c>
       <c r="O180" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B181" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C181" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::MX RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E181" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F181" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G181" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H181" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8888,45 +8888,45 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L181">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M181">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N181">
-        <v>0.85</v>
+        <v>0.56</v>
       </c>
       <c r="O181" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B182" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C182" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D182" t="str">
-        <v>BL::MX RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E182" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F182" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G182" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L182">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M182">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N182">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="O182" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B183" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C183" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D183" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E183" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,42 +8982,42 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L183">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M183">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N183">
-        <v>0.43</v>
+        <v>0.77</v>
       </c>
       <c r="O183" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B184" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C184" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D184" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach cuff</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F184" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G184" t="str">
         <v>Sewing</v>
@@ -9029,42 +9029,42 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L184">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M184">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N184">
-        <v>1</v>
+        <v>0.84</v>
       </c>
       <c r="O184" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B185" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C185" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D185" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E185" t="str">
-        <v>Attach set band collar</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F185" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G185" t="str">
         <v>Sewing</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L185">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M185">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N185">
-        <v>0.68</v>
+        <v>1.34</v>
       </c>
       <c r="O185" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B186" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C186" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D186" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F186" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L186">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M186">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N186">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O186" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B187" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C187" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D187" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E187" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F187" t="str">
-        <v>SNL</v>
+        <v>LDN</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,45 +9170,45 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L187">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M187">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N187">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="O187" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B188" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C188" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D188" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E188" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F188" t="str">
         <v>SNL</v>
       </c>
       <c r="G188" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H188" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9217,45 +9217,45 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L188">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M188">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O188" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B189" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C189" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D189" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E189" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F189" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G189" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H189" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9264,42 +9264,42 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L189">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M189">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N189">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="O189" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B190" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C190" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D190" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E190" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F190" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G190" t="str">
         <v>Finishing</v>
@@ -9311,42 +9311,42 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L190">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M190">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N190">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O190" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B191" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C191" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D191" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E191" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F191" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G191" t="str">
         <v>Finishing</v>
@@ -9358,42 +9358,42 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L191">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M191">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N191">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="O191" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B192" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C192" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D192" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E192" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F192" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G192" t="str">
         <v>Finishing</v>
@@ -9405,42 +9405,42 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L192">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M192">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N192">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="O192" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B193" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C193" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D193" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E193" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F193" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G193" t="str">
         <v>Finishing</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L193">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M193">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N193">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="O193" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B194" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C194" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D194" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E194" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,45 +9499,45 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L194">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M194">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N194">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="O194" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B195" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C195" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::G</v>
       </c>
       <c r="E195" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F195" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G195" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H195" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9546,45 +9546,45 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L195">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M195">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N195">
-        <v>0.85</v>
+        <v>1.26</v>
       </c>
       <c r="O195" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B196" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C196" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::G</v>
       </c>
       <c r="E196" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F196" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G196" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H196" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9593,22 +9593,22 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L196">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M196">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N196">
-        <v>1</v>
+        <v>0.56</v>
       </c>
       <c r="O196" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="197">
@@ -9622,10 +9622,10 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E197" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F197" t="str">
         <v>SNL</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9652,7 +9652,7 @@
         <v>22.22</v>
       </c>
       <c r="N197">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="O197" t="str">
         <v>kamalag</v>
@@ -9669,10 +9669,10 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E198" t="str">
-        <v>Attach pocket bag</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F198" t="str">
         <v>SNL</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9699,7 +9699,7 @@
         <v>22.22</v>
       </c>
       <c r="N198">
-        <v>0.56</v>
+        <v>0.77</v>
       </c>
       <c r="O198" t="str">
         <v>kamalag</v>
@@ -9716,13 +9716,13 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E199" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F199" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G199" t="str">
         <v>Sewing</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9746,7 +9746,7 @@
         <v>22.22</v>
       </c>
       <c r="N199">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="O199" t="str">
         <v>kamalag</v>
@@ -9763,13 +9763,13 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E200" t="str">
-        <v>Collar attach to body</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F200" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G200" t="str">
         <v>Sewing</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9793,7 +9793,7 @@
         <v>22.22</v>
       </c>
       <c r="N200">
-        <v>0.77</v>
+        <v>1.34</v>
       </c>
       <c r="O200" t="str">
         <v>kamalag</v>
@@ -9810,13 +9810,13 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E201" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F201" t="str">
-        <v>4O/L</v>
+        <v>SNNF</v>
       </c>
       <c r="G201" t="str">
         <v>Sewing</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9840,7 +9840,7 @@
         <v>22.22</v>
       </c>
       <c r="N201">
-        <v>0.84</v>
+        <v>2.48</v>
       </c>
       <c r="O201" t="str">
         <v>kamalag</v>
@@ -9857,13 +9857,13 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E202" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F202" t="str">
-        <v>4O/L</v>
+        <v>LDN</v>
       </c>
       <c r="G202" t="str">
         <v>Sewing</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9887,7 +9887,7 @@
         <v>22.22</v>
       </c>
       <c r="N202">
-        <v>1.34</v>
+        <v>0.63</v>
       </c>
       <c r="O202" t="str">
         <v>kamalag</v>
@@ -9904,16 +9904,16 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E203" t="str">
-        <v>Attach zipper front</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F203" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G203" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H203" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9934,7 +9934,7 @@
         <v>22.22</v>
       </c>
       <c r="N203">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O203" t="str">
         <v>kamalag</v>
@@ -9951,16 +9951,16 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E204" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F204" t="str">
-        <v>LDN</v>
+        <v>SNL</v>
       </c>
       <c r="G204" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H204" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9981,7 +9981,7 @@
         <v>22.22</v>
       </c>
       <c r="N204">
-        <v>0.63</v>
+        <v>1.2</v>
       </c>
       <c r="O204" t="str">
         <v>kamalag</v>
@@ -9998,13 +9998,13 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E205" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F205" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G205" t="str">
         <v>Finishing</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10028,7 +10028,7 @@
         <v>22.22</v>
       </c>
       <c r="N205">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O205" t="str">
         <v>kamalag</v>
@@ -10045,13 +10045,13 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E206" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F206" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G206" t="str">
         <v>Finishing</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10075,7 +10075,7 @@
         <v>22.22</v>
       </c>
       <c r="N206">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="O206" t="str">
         <v>kamalag</v>
@@ -10092,13 +10092,13 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E207" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F207" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G207" t="str">
         <v>Finishing</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10122,7 +10122,7 @@
         <v>22.22</v>
       </c>
       <c r="N207">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="O207" t="str">
         <v>kamalag</v>
@@ -10139,13 +10139,13 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E208" t="str">
-        <v>Final press full jacket</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F208" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G208" t="str">
         <v>Finishing</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10169,7 +10169,7 @@
         <v>22.22</v>
       </c>
       <c r="N208">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="O208" t="str">
         <v>kamalag</v>
@@ -10186,10 +10186,10 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E209" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F209" t="str">
         <v>HELP</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10216,7 +10216,7 @@
         <v>22.22</v>
       </c>
       <c r="N209">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="O209" t="str">
         <v>kamalag</v>
@@ -10233,16 +10233,16 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::B</v>
+        <v>JK::W</v>
       </c>
       <c r="E210" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F210" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G210" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H210" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-25</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10263,7 +10263,7 @@
         <v>22.22</v>
       </c>
       <c r="N210">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O210" t="str">
         <v>kamalag</v>
@@ -10280,16 +10280,16 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::B</v>
+        <v>JK::W</v>
       </c>
       <c r="E211" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F211" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G211" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H211" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-25</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-28</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10310,7 +10310,7 @@
         <v>22.22</v>
       </c>
       <c r="N211">
-        <v>1.3</v>
+        <v>0.56</v>
       </c>
       <c r="O211" t="str">
         <v>kamalag</v>
@@ -10327,10 +10327,10 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E212" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F212" t="str">
         <v>SNL</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10357,7 +10357,7 @@
         <v>22.22</v>
       </c>
       <c r="N212">
-        <v>1.26</v>
+        <v>1.04</v>
       </c>
       <c r="O212" t="str">
         <v>kamalag</v>
@@ -10374,10 +10374,10 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E213" t="str">
-        <v>Attach pocket bag</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F213" t="str">
         <v>SNL</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10404,7 +10404,7 @@
         <v>22.22</v>
       </c>
       <c r="N213">
-        <v>0.56</v>
+        <v>0.77</v>
       </c>
       <c r="O213" t="str">
         <v>kamalag</v>
@@ -10421,13 +10421,13 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E214" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F214" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G214" t="str">
         <v>Sewing</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10451,7 +10451,7 @@
         <v>22.22</v>
       </c>
       <c r="N214">
-        <v>1.04</v>
+        <v>0.84</v>
       </c>
       <c r="O214" t="str">
         <v>kamalag</v>
@@ -10468,13 +10468,13 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E215" t="str">
-        <v>Collar attach to body</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F215" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G215" t="str">
         <v>Sewing</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10498,7 +10498,7 @@
         <v>22.22</v>
       </c>
       <c r="N215">
-        <v>0.77</v>
+        <v>1.34</v>
       </c>
       <c r="O215" t="str">
         <v>kamalag</v>
@@ -10515,13 +10515,13 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E216" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F216" t="str">
-        <v>4O/L</v>
+        <v>SNNF</v>
       </c>
       <c r="G216" t="str">
         <v>Sewing</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10545,7 +10545,7 @@
         <v>22.22</v>
       </c>
       <c r="N216">
-        <v>0.84</v>
+        <v>2.48</v>
       </c>
       <c r="O216" t="str">
         <v>kamalag</v>
@@ -10562,13 +10562,13 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E217" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F217" t="str">
-        <v>4O/L</v>
+        <v>LDN</v>
       </c>
       <c r="G217" t="str">
         <v>Sewing</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10592,7 +10592,7 @@
         <v>22.22</v>
       </c>
       <c r="N217">
-        <v>1.34</v>
+        <v>0.63</v>
       </c>
       <c r="O217" t="str">
         <v>kamalag</v>
@@ -10609,16 +10609,16 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E218" t="str">
-        <v>Attach zipper front</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F218" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G218" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H218" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10639,7 +10639,7 @@
         <v>22.22</v>
       </c>
       <c r="N218">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O218" t="str">
         <v>kamalag</v>
@@ -10656,16 +10656,16 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E219" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F219" t="str">
-        <v>LDN</v>
+        <v>SNL</v>
       </c>
       <c r="G219" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H219" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10686,7 +10686,7 @@
         <v>22.22</v>
       </c>
       <c r="N219">
-        <v>0.63</v>
+        <v>1.2</v>
       </c>
       <c r="O219" t="str">
         <v>kamalag</v>
@@ -10703,13 +10703,13 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E220" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F220" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G220" t="str">
         <v>Finishing</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10733,7 +10733,7 @@
         <v>22.22</v>
       </c>
       <c r="N220">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="O220" t="str">
         <v>kamalag</v>
@@ -10750,13 +10750,13 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E221" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F221" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G221" t="str">
         <v>Finishing</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10780,7 +10780,7 @@
         <v>22.22</v>
       </c>
       <c r="N221">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="O221" t="str">
         <v>kamalag</v>
@@ -10797,13 +10797,13 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E222" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F222" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G222" t="str">
         <v>Finishing</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10827,7 +10827,7 @@
         <v>22.22</v>
       </c>
       <c r="N222">
-        <v>2.8</v>
+        <v>0.9</v>
       </c>
       <c r="O222" t="str">
         <v>kamalag</v>
@@ -10844,13 +10844,13 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E223" t="str">
-        <v>Final press full jacket</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F223" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G223" t="str">
         <v>Finishing</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10874,7 +10874,7 @@
         <v>22.22</v>
       </c>
       <c r="N223">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="O223" t="str">
         <v>kamalag</v>
@@ -10891,10 +10891,10 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E224" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F224" t="str">
         <v>HELP</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10921,7 +10921,7 @@
         <v>22.22</v>
       </c>
       <c r="N224">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
       <c r="O224" t="str">
         <v>kamalag</v>
@@ -10929,25 +10929,25 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B225" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C225" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::G</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E225" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F225" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G225" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H225" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10956,45 +10956,45 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L225">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M225">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N225">
         <v>1.1</v>
       </c>
       <c r="O225" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B226" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C226" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::G</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E226" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F226" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G226" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H226" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11003,39 +11003,39 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L226">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M226">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N226">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="O226" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B227" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C227" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D227" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,42 +11050,42 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L227">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M227">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N227">
-        <v>1.26</v>
+        <v>1.6</v>
       </c>
       <c r="O227" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B228" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C228" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D228" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E228" t="str">
-        <v>Attach pocket bag</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F228" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G228" t="str">
         <v>Sewing</v>
@@ -11097,39 +11097,39 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L228">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M228">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N228">
-        <v>0.56</v>
+        <v>0.75</v>
       </c>
       <c r="O228" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B229" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C229" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D229" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E229" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11144,39 +11144,39 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L229">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M229">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N229">
-        <v>1.04</v>
+        <v>0.7</v>
       </c>
       <c r="O229" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B230" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C230" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D230" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E230" t="str">
-        <v>Collar attach to body</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F230" t="str">
         <v>SNL</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L230">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M230">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N230">
-        <v>0.77</v>
+        <v>1</v>
       </c>
       <c r="O230" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B231" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C231" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D231" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E231" t="str">
-        <v>Collar attach lining</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F231" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,45 +11238,45 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L231">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M231">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N231">
-        <v>0.84</v>
+        <v>1.3</v>
       </c>
       <c r="O231" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B232" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C232" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D232" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E232" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F232" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G232" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H232" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11285,45 +11285,45 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L232">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M232">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N232">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="O232" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B233" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C233" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D233" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E233" t="str">
-        <v>Attach zipper front</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F233" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G233" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H233" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11332,45 +11332,45 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L233">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M233">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N233">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="O233" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B234" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C234" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D234" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E234" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F234" t="str">
-        <v>LDN</v>
+        <v>VIR</v>
       </c>
       <c r="G234" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11379,42 +11379,42 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L234">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M234">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N234">
-        <v>0.63</v>
+        <v>3.2</v>
       </c>
       <c r="O234" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B235" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C235" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D235" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E235" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F235" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G235" t="str">
         <v>Finishing</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L235">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M235">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N235">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O235" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B236" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C236" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D236" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E236" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F236" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,42 +11473,42 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L236">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M236">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N236">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="O236" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B237" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C237" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D237" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E237" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F237" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G237" t="str">
         <v>Finishing</v>
@@ -11520,42 +11520,42 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L237">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M237">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N237">
-        <v>2.8</v>
+        <v>0.85</v>
       </c>
       <c r="O237" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B238" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C238" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D238" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E238" t="str">
-        <v>Final press full jacket</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F238" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11567,45 +11567,45 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L238">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M238">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N238">
-        <v>3.5</v>
+        <v>1.1</v>
       </c>
       <c r="O238" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B239" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C239" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D239" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E239" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F239" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G239" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H239" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11614,45 +11614,45 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L239">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M239">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N239">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="O239" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B240" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C240" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F240" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G240" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H240" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11661,45 +11661,45 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L240">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M240">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N240">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O240" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B241" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C241" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F241" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G241" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,22 +11708,22 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L241">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M241">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N241">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="O241" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="242">
@@ -11737,13 +11737,13 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach back panel to front</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F242" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G242" t="str">
         <v>Sewing</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,10 +11784,10 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Attach collar to body</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,10 +11831,10 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F244" t="str">
         <v>SNL</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,13 +11878,13 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F245" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,16 +11925,16 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
       </c>
       <c r="G246" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H246" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,16 +11972,16 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
       </c>
       <c r="G247" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H247" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,16 +12019,16 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F248" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G248" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,13 +12066,13 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Thread trim full garment</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F249" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G249" t="str">
         <v>Finishing</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F250" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,13 +12160,13 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Full body pressing</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F251" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G251" t="str">
         <v>Finishing</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>3.2</v>
+        <v>0.85</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,13 +12207,13 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F252" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,16 +12254,16 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F253" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G253" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H253" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,16 +12301,16 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Hang tag attach</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F254" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G254" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H254" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>0.85</v>
+        <v>1.2</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F255" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G255" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12378,7 +12378,7 @@
         <v>19</v>
       </c>
       <c r="N255">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="O255" t="str">
         <v>sasanthar</v>
@@ -12395,13 +12395,13 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach back panel to front</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F256" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G256" t="str">
         <v>Sewing</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,10 +12442,10 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Attach collar to body</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,10 +12489,10 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F258" t="str">
         <v>SNL</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,13 +12536,13 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F259" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>0.75</v>
+        <v>1.3</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,16 +12583,16 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
       </c>
       <c r="G260" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H260" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,16 +12630,16 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
       </c>
       <c r="G261" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H261" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,16 +12677,16 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F262" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G262" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,13 +12724,13 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Thread trim full garment</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F263" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G263" t="str">
         <v>Finishing</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F264" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>1.9</v>
+        <v>0.8</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,13 +12818,13 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Full body pressing</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F265" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G265" t="str">
         <v>Finishing</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>3.2</v>
+        <v>0.85</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,13 +12865,13 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F266" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12903,160 +12903,160 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B267" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C267" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F267" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G267" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H267" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L267">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M267">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N267">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="O267" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B268" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C268" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Hang tag attach</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F268" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G268" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H268" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I268">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L268">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M268">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N268">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O268" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B269" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C269" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D269" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F269" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G269" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L269">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M269">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N269">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="O269" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B270" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C270" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D270" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,42 +13068,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L270">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M270">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N270">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O270" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B271" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C271" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D271" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L271">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M271">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N271">
-        <v>1.2</v>
+        <v>0.45</v>
       </c>
       <c r="O271" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B272" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C272" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D272" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,45 +13162,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L272">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M272">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N272">
         <v>1.6</v>
       </c>
       <c r="O272" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B273" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C273" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D273" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F273" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13209,45 +13209,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L273">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M273">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N273">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="O273" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B274" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C274" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D274" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F274" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G274" t="str">
         <v>Sewing</v>
@@ -13256,139 +13256,139 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L274">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M274">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N274">
-        <v>0.7</v>
+        <v>0.42</v>
       </c>
       <c r="O274" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B275" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C275" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D275" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
       </c>
       <c r="G275" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H275" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L275">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M275">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N275">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O275" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B276" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C276" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D276" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F276" t="str">
         <v>SNL</v>
       </c>
       <c r="G276" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H276" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L276">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M276">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N276">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O276" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B277" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C277" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D277" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Thread trim full garment</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F277" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G277" t="str">
         <v>Finishing</v>
@@ -13397,45 +13397,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L277">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M277">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N277">
         <v>2</v>
       </c>
       <c r="O277" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B278" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C278" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D278" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F278" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G278" t="str">
         <v>Finishing</v>
@@ -13444,45 +13444,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L278">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M278">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N278">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O278" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B279" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C279" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D279" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Full body pressing</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F279" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G279" t="str">
         <v>Finishing</v>
@@ -13491,45 +13491,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L279">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M279">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N279">
-        <v>3.2</v>
+        <v>0.75</v>
       </c>
       <c r="O279" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B280" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C280" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D280" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F280" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G280" t="str">
         <v>Finishing</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L280">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M280">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N280">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="O280" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B281" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C281" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D281" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,25 +13585,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-14</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L281">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M281">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N281">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="O281" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="282">
@@ -13611,46 +13611,46 @@
         <v>847</v>
       </c>
       <c r="B282" t="str">
-        <v>8774T::BL</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C282" t="str">
         <v>Blouse</v>
       </c>
       <c r="D282" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E282" t="str">
-        <v>Hang tag attach</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F282" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G282" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H282" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I282">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-20</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L282">
-        <v>607</v>
+        <v>2190</v>
       </c>
       <c r="M282">
-        <v>19</v>
+        <v>17.96</v>
       </c>
       <c r="N282">
-        <v>0.85</v>
+        <v>0.43</v>
       </c>
       <c r="O282" t="str">
-        <v>sasanthar</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="283">
@@ -13658,63 +13658,63 @@
         <v>847</v>
       </c>
       <c r="B283" t="str">
-        <v>8774T::BL</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C283" t="str">
         <v>Blouse</v>
       </c>
       <c r="D283" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F283" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G283" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H283" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I283">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-20</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L283">
-        <v>607</v>
+        <v>2190</v>
       </c>
       <c r="M283">
-        <v>19</v>
+        <v>17.96</v>
       </c>
       <c r="N283">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O283" t="str">
-        <v>sasanthar</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B284" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C284" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D284" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E284" t="str">
-        <v>Attach waistband - curved</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F284" t="str">
         <v>SNL</v>
@@ -13735,33 +13735,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L284">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M284">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N284">
-        <v>1.2</v>
+        <v>0.68</v>
       </c>
       <c r="O284" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B285" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C285" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D285" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E285" t="str">
-        <v>Join inseam double stitch</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F285" t="str">
         <v>SNL</v>
@@ -13782,36 +13782,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L285">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M285">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N285">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O285" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B286" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C286" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D286" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E286" t="str">
-        <v>Outseam overlock &amp; topstitch</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F286" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G286" t="str">
         <v>Sewing</v>
@@ -13829,36 +13829,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L286">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M286">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N286">
-        <v>0.85</v>
+        <v>2</v>
       </c>
       <c r="O286" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B287" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C287" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D287" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E287" t="str">
-        <v>Attach zipper to fly</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F287" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G287" t="str">
         <v>Sewing</v>
@@ -13876,36 +13876,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L287">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M287">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N287">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O287" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B288" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C288" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D288" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E288" t="str">
-        <v>Hem bottom with blind stitch</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F288" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G288" t="str">
         <v>Sewing</v>
@@ -13923,39 +13923,39 @@
         <v>2026-05-22</v>
       </c>
       <c r="L288">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M288">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N288">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O288" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B289" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C289" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D289" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E289" t="str">
-        <v>Bartack pocket corners</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F289" t="str">
-        <v>ASNL</v>
+        <v>SNL</v>
       </c>
       <c r="G289" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H289" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13970,33 +13970,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L289">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M289">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N289">
-        <v>0.45</v>
+        <v>1.5</v>
       </c>
       <c r="O289" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B290" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C290" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D290" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E290" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F290" t="str">
         <v>SNL</v>
@@ -14017,33 +14017,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L290">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M290">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N290">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O290" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B291" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C291" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D291" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E291" t="str">
-        <v>Press leg crease both sides</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F291" t="str">
         <v>VIR</v>
@@ -14064,33 +14064,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L291">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M291">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N291">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O291" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B292" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C292" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D292" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E292" t="str">
-        <v>Final press &amp; steam waistband</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F292" t="str">
         <v>VIR</v>
@@ -14111,33 +14111,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L292">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M292">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N292">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O292" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B293" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C293" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D293" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E293" t="str">
-        <v>Attach main &amp; care label</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F293" t="str">
         <v>HELP</v>
@@ -14158,33 +14158,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L293">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M293">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N293">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O293" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B294" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C294" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D294" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E294" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F294" t="str">
         <v>HELP</v>
@@ -14205,33 +14205,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L294">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M294">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N294">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O294" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B295" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C295" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D295" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E295" t="str">
-        <v>Fold, board insert &amp; poly bag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F295" t="str">
         <v>HELP</v>
@@ -14252,16 +14252,16 @@
         <v>2026-05-22</v>
       </c>
       <c r="L295">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M295">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N295">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="O295" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="296">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-11</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B140" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C140" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D140" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E140" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L140">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M140">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N140">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="O140" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B141" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C141" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D141" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach cuff</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L141">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M141">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O141" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B142" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C142" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D142" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L142">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M142">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N142">
-        <v>0.68</v>
+        <v>0.5</v>
       </c>
       <c r="O142" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B143" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C143" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D143" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L143">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M143">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O143" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B144" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C144" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D144" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L144">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M144">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="O144" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B145" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C145" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D145" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L145">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M145">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N145">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O145" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B146" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C146" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D146" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L146">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M146">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O146" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B147" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C147" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D147" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F147" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G147" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L147">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M147">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N147">
-        <v>1.5</v>
+        <v>0.42</v>
       </c>
       <c r="O147" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B148" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C148" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D148" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L148">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M148">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="O148" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B149" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C149" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D149" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F149" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L149">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M149">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N149">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O149" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B150" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C150" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D150" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L150">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M150">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N150">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O150" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B151" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C151" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D151" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F151" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L151">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M151">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N151">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="O151" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B152" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C152" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D152" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L152">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M152">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N152">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O152" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B153" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C153" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D153" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L153">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M153">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O153" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B154" t="str">
-        <v>3524P::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C154" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D154" t="str">
-        <v>PN::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Attach waistband - curved</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F154" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G154" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,19 +7619,19 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L154">
-        <v>1890</v>
+        <v>646</v>
       </c>
       <c r="M154">
-        <v>14</v>
+        <v>15.28</v>
       </c>
       <c r="N154">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O154" t="str">
         <v>priyanthi</v>
@@ -7639,19 +7639,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B155" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C155" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E155" t="str">
-        <v>Join inseam double stitch</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,42 +7666,42 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L155">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M155">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O155" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B156" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C156" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Outseam overlock &amp; topstitch</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F156" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G156" t="str">
         <v>Sewing</v>
@@ -7713,42 +7713,42 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L156">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M156">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N156">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O156" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B157" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C157" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach zipper to fly</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F157" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G157" t="str">
         <v>Sewing</v>
@@ -7760,39 +7760,39 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L157">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M157">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N157">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="O157" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B158" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C158" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Hem bottom with blind stitch</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,42 +7807,42 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L158">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M158">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N158">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O158" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B159" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C159" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Bartack pocket corners</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F159" t="str">
-        <v>ASNL</v>
+        <v>SNL</v>
       </c>
       <c r="G159" t="str">
         <v>Sewing</v>
@@ -7854,45 +7854,45 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L159">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M159">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N159">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O159" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B160" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C160" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F160" t="str">
         <v>SNL</v>
       </c>
       <c r="G160" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H160" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7901,45 +7901,45 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L160">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M160">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O160" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B161" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C161" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Press leg crease both sides</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F161" t="str">
-        <v>VIR</v>
+        <v>SNLU</v>
       </c>
       <c r="G161" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,42 +7948,42 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L161">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M161">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N161">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="O161" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B162" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C162" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Final press &amp; steam waistband</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F162" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G162" t="str">
         <v>Finishing</v>
@@ -7995,42 +7995,42 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L162">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M162">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N162">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O162" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B163" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C163" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Attach main &amp; care label</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F163" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,42 +8042,42 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L163">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M163">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N163">
-        <v>0.75</v>
+        <v>1.8</v>
       </c>
       <c r="O163" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B164" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C164" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F164" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G164" t="str">
         <v>Finishing</v>
@@ -8089,42 +8089,42 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L164">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M164">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N164">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="O164" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B165" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C165" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Fold, board insert &amp; poly bag</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F165" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,22 +8136,22 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L165">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M165">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N165">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="O165" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="166">
@@ -8165,16 +8165,16 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E166" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F166" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G166" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H166" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,16 +8212,16 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Attach cuff</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F167" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G167" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H167" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Attach set band collar</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F168" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G168" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8297,19 +8297,19 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B169" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C169" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D169" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E169" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach waistband - curved</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,39 +8324,39 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L169">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M169">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N169">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="O169" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B170" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C170" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D170" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Join inseam double stitch</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,42 +8371,42 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L170">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M170">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O170" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B171" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C171" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D171" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Outseam overlock &amp; topstitch</v>
       </c>
       <c r="F171" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G171" t="str">
         <v>Sewing</v>
@@ -8418,42 +8418,42 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L171">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M171">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>0.85</v>
       </c>
       <c r="O171" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B172" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C172" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D172" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach zipper to fly</v>
       </c>
       <c r="F172" t="str">
-        <v>SNLU</v>
+        <v>SNNF</v>
       </c>
       <c r="G172" t="str">
         <v>Sewing</v>
@@ -8465,45 +8465,45 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L172">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M172">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N172">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O172" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B173" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C173" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D173" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Hem bottom with blind stitch</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
       </c>
       <c r="G173" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H173" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8512,45 +8512,45 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L173">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M173">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N173">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O173" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B174" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C174" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D174" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Bartack pocket corners</v>
       </c>
       <c r="F174" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G174" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H174" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8559,42 +8559,42 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L174">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M174">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N174">
-        <v>1.8</v>
+        <v>0.45</v>
       </c>
       <c r="O174" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B175" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C175" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D175" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F175" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G175" t="str">
         <v>Finishing</v>
@@ -8606,39 +8606,39 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L175">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M175">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N175">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O175" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B176" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C176" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D176" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Press leg crease both sides</v>
       </c>
       <c r="F176" t="str">
         <v>VIR</v>
@@ -8653,42 +8653,42 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L176">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M176">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N176">
         <v>2.2</v>
       </c>
       <c r="O176" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B177" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C177" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D177" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press &amp; steam waistband</v>
       </c>
       <c r="F177" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,39 +8700,39 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L177">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M177">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N177">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="O177" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B178" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C178" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D178" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach main &amp; care label</v>
       </c>
       <c r="F178" t="str">
         <v>HELP</v>
@@ -8747,39 +8747,39 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L178">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M178">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N178">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O178" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B179" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C179" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D179" t="str">
-        <v>BL::UK RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F179" t="str">
         <v>HELP</v>
@@ -8794,45 +8794,45 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L179">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M179">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N179">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O179" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>920</v>
+        <v>910</v>
       </c>
       <c r="B180" t="str">
-        <v>GOT12524N::JK</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C180" t="str">
-        <v>Jacket</v>
+        <v>Pant</v>
       </c>
       <c r="D180" t="str">
-        <v>JK::B</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Attach back stitch</v>
+        <v>Fold, board insert &amp; poly bag</v>
       </c>
       <c r="F180" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G180" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H180" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8841,39 +8841,39 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L180">
-        <v>500</v>
+        <v>1890</v>
       </c>
       <c r="M180">
-        <v>22.22</v>
+        <v>14</v>
       </c>
       <c r="N180">
-        <v>1.26</v>
+        <v>1.05</v>
       </c>
       <c r="O180" t="str">
-        <v>kamalag</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B181" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C181" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Attach pocket bag</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F181" t="str">
         <v>SNL</v>
@@ -8888,39 +8888,39 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L181">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M181">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N181">
-        <v>0.56</v>
+        <v>0.43</v>
       </c>
       <c r="O181" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B182" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C182" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D182" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E182" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F182" t="str">
         <v>SNL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L182">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M182">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N182">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="O182" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B183" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C183" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D183" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E183" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,42 +8982,42 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L183">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M183">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N183">
-        <v>0.77</v>
+        <v>0.68</v>
       </c>
       <c r="O183" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B184" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C184" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D184" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E184" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F184" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G184" t="str">
         <v>Sewing</v>
@@ -9029,42 +9029,42 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L184">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M184">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N184">
-        <v>0.84</v>
+        <v>1.5</v>
       </c>
       <c r="O184" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B185" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C185" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D185" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E185" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F185" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G185" t="str">
         <v>Sewing</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L185">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M185">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N185">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="O185" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B186" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C186" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D186" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach zipper front</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F186" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L186">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M186">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N186">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="O186" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B187" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C187" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D187" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E187" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F187" t="str">
-        <v>LDN</v>
+        <v>SNLU</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,39 +9170,39 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L187">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M187">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N187">
-        <v>0.63</v>
+        <v>1</v>
       </c>
       <c r="O187" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B188" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C188" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D188" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E188" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F188" t="str">
         <v>SNL</v>
@@ -9217,39 +9217,39 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L188">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M188">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N188">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O188" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B189" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C189" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D189" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E189" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F189" t="str">
         <v>SNL</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L189">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M189">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N189">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
       <c r="O189" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B190" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C190" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D190" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E190" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F190" t="str">
         <v>VIR</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L190">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M190">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N190">
-        <v>2.8</v>
+        <v>1.8</v>
       </c>
       <c r="O190" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B191" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C191" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D191" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E191" t="str">
-        <v>Final press full jacket</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F191" t="str">
         <v>VIR</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L191">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M191">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N191">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="O191" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B192" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C192" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D192" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E192" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F192" t="str">
         <v>HELP</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L192">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M192">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N192">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="O192" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B193" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C193" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D193" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E193" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F193" t="str">
         <v>HELP</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L193">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M193">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N193">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O193" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B194" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C194" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D194" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E194" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,22 +9499,22 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L194">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M194">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N194">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O194" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="195">
@@ -9528,7 +9528,7 @@
         <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E195" t="str">
         <v>Attach back stitch</v>
@@ -9546,10 +9546,10 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L195">
         <v>500</v>
@@ -9575,7 +9575,7 @@
         <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E196" t="str">
         <v>Attach pocket bag</v>
@@ -9593,10 +9593,10 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L196">
         <v>500</v>
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E197" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E198" t="str">
         <v>Collar attach to body</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E199" t="str">
         <v>Collar attach lining</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E200" t="str">
         <v>Sleeve attach overlock</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E201" t="str">
         <v>Attach zipper front</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E202" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E203" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E204" t="str">
         <v>Button attach (2 buttons)</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E205" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E206" t="str">
         <v>Final press full jacket</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E207" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E208" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E209" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E210" t="str">
         <v>Attach back stitch</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E211" t="str">
         <v>Attach pocket bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E212" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E213" t="str">
         <v>Collar attach to body</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E214" t="str">
         <v>Collar attach lining</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E215" t="str">
         <v>Sleeve attach overlock</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E216" t="str">
         <v>Attach zipper front</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E217" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E218" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E219" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E220" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E221" t="str">
         <v>Final press full jacket</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E222" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E223" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E224" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10929,19 +10929,19 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B225" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C225" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E225" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F225" t="str">
         <v>SNL</v>
@@ -10956,39 +10956,39 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L225">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M225">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N225">
-        <v>1.1</v>
+        <v>1.26</v>
       </c>
       <c r="O225" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B226" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C226" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E226" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F226" t="str">
         <v>SNL</v>
@@ -11003,39 +11003,39 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L226">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M226">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N226">
-        <v>1.2</v>
+        <v>0.56</v>
       </c>
       <c r="O226" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B227" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C227" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D227" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,42 +11050,42 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L227">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M227">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N227">
-        <v>1.6</v>
+        <v>1.04</v>
       </c>
       <c r="O227" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B228" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C228" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D228" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E228" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F228" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G228" t="str">
         <v>Sewing</v>
@@ -11097,42 +11097,42 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L228">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M228">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N228">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O228" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B229" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C229" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D229" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E229" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F229" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G229" t="str">
         <v>Sewing</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L229">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M229">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N229">
-        <v>0.7</v>
+        <v>0.84</v>
       </c>
       <c r="O229" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B230" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C230" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D230" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E230" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F230" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L230">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M230">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N230">
-        <v>1</v>
+        <v>1.34</v>
       </c>
       <c r="O230" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B231" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C231" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D231" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E231" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F231" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,45 +11238,45 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L231">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M231">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N231">
-        <v>1.3</v>
+        <v>2.48</v>
       </c>
       <c r="O231" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B232" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C232" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D232" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E232" t="str">
-        <v>Thread trim full garment</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F232" t="str">
-        <v>SNL</v>
+        <v>LDN</v>
       </c>
       <c r="G232" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H232" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11285,39 +11285,39 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L232">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M232">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N232">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="O232" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B233" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C233" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D233" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E233" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F233" t="str">
         <v>SNL</v>
@@ -11332,42 +11332,42 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L233">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M233">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N233">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="O233" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B234" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C234" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D234" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E234" t="str">
-        <v>Full body pressing</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F234" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G234" t="str">
         <v>Finishing</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L234">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M234">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N234">
-        <v>3.2</v>
+        <v>1.2</v>
       </c>
       <c r="O234" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B235" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C235" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D235" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E235" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F235" t="str">
         <v>VIR</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L235">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M235">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N235">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="O235" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B236" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C236" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D236" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E236" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F236" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L236">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M236">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N236">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="O236" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B237" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C237" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D237" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E237" t="str">
-        <v>Hang tag attach</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F237" t="str">
         <v>HELP</v>
@@ -11520,39 +11520,39 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L237">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M237">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N237">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O237" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B238" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C238" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D238" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E238" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F238" t="str">
         <v>HELP</v>
@@ -11567,45 +11567,45 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L238">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M238">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N238">
         <v>1.1</v>
       </c>
       <c r="O238" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B239" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C239" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D239" t="str">
-        <v>BL::US RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E239" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F239" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G239" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H239" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11614,22 +11614,22 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L239">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M239">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N239">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="O239" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="240">
@@ -11643,10 +11643,10 @@
         <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F240" t="str">
         <v>SNL</v>
@@ -11661,10 +11661,10 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L240">
         <v>607</v>
@@ -11673,7 +11673,7 @@
         <v>19</v>
       </c>
       <c r="N240">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O240" t="str">
         <v>sasanthar</v>
@@ -11690,10 +11690,10 @@
         <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F241" t="str">
         <v>SNL</v>
@@ -11708,10 +11708,10 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L241">
         <v>607</v>
@@ -11720,7 +11720,7 @@
         <v>19</v>
       </c>
       <c r="N241">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O241" t="str">
         <v>sasanthar</v>
@@ -11737,13 +11737,13 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F242" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G242" t="str">
         <v>Sewing</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,13 +11784,13 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F243" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G243" t="str">
         <v>Sewing</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,10 +11831,10 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F244" t="str">
         <v>SNL</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,10 +11878,10 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F245" t="str">
         <v>SNL</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,16 +11925,16 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
       </c>
       <c r="G246" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H246" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,13 +12019,13 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F248" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G248" t="str">
         <v>Finishing</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F249" t="str">
         <v>VIR</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F250" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F251" t="str">
         <v>HELP</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,10 +12207,10 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F252" t="str">
         <v>HELP</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,16 +12254,16 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Attach back panel to front</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F253" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G253" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H253" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F254" t="str">
         <v>SNL</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,10 +12348,10 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F255" t="str">
         <v>SNL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12378,7 +12378,7 @@
         <v>19</v>
       </c>
       <c r="N255">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="O255" t="str">
         <v>sasanthar</v>
@@ -12395,13 +12395,13 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F256" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G256" t="str">
         <v>Sewing</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>0.75</v>
+        <v>1.6</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,13 +12442,13 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F257" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G257" t="str">
         <v>Sewing</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,10 +12489,10 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F258" t="str">
         <v>SNL</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,10 +12536,10 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F259" t="str">
         <v>SNL</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,16 +12583,16 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Thread trim full garment</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
       </c>
       <c r="G260" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H260" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,13 +12677,13 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Full body pressing</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F262" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G262" t="str">
         <v>Finishing</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F263" t="str">
         <v>VIR</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>1.5</v>
+        <v>3.2</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F264" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Hang tag attach</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F265" t="str">
         <v>HELP</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,10 +12865,10 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F266" t="str">
         <v>HELP</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>1.1</v>
+        <v>0.85</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12903,66 +12903,66 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B267" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C267" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Attach label 2 sides</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F267" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G267" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H267" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L267">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M267">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N267">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="O267" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B268" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C268" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F268" t="str">
         <v>SNL</v>
@@ -12974,42 +12974,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L268">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M268">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N268">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="O268" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B269" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C269" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D269" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F269" t="str">
         <v>SNL</v>
@@ -13021,42 +13021,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L269">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M269">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N269">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="O269" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B270" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C270" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D270" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,45 +13068,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L270">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M270">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N270">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="O270" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B271" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C271" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D271" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F271" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G271" t="str">
         <v>Sewing</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L271">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M271">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N271">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="O271" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B272" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C272" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D272" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,42 +13162,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L272">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M272">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N272">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="O272" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B273" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C273" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D273" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F273" t="str">
         <v>SNL</v>
@@ -13209,45 +13209,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L273">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M273">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N273">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O273" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B274" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C274" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D274" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F274" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G274" t="str">
         <v>Sewing</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L274">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M274">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N274">
-        <v>0.42</v>
+        <v>1.3</v>
       </c>
       <c r="O274" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B275" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C275" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D275" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,42 +13303,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L275">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M275">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N275">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O275" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B276" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C276" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D276" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F276" t="str">
         <v>SNL</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L276">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M276">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N276">
-        <v>1</v>
+        <v>1.9</v>
       </c>
       <c r="O276" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B277" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C277" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D277" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F277" t="str">
         <v>VIR</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L277">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M277">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N277">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="O277" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B278" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C278" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D278" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Final press full shirt</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F278" t="str">
         <v>VIR</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L278">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M278">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N278">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="O278" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B279" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C279" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D279" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Label attach manual</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F279" t="str">
         <v>HELP</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L279">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M279">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N279">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O279" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B280" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C280" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D280" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F280" t="str">
         <v>HELP</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L280">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M280">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N280">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O280" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B281" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C281" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D281" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,25 +13585,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-14</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L281">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M281">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N281">
         <v>1.1</v>
       </c>
       <c r="O281" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="282">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6238,7 +6238,7 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E125" t="str">
         <v>Attach label 2 sides</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6285,7 +6285,7 @@
         <v>Shirt</v>
       </c>
       <c r="D126" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E126" t="str">
         <v>Attach binding @ in seam 2x2</v>
@@ -6303,10 +6303,10 @@
         <v>2</v>
       </c>
       <c r="J126" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K126" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L126">
         <v>646</v>
@@ -6332,7 +6332,7 @@
         <v>Shirt</v>
       </c>
       <c r="D127" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E127" t="str">
         <v>Attach bottom triangle</v>
@@ -6350,10 +6350,10 @@
         <v>2</v>
       </c>
       <c r="J127" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K127" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L127">
         <v>646</v>
@@ -6379,7 +6379,7 @@
         <v>Shirt</v>
       </c>
       <c r="D128" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E128" t="str">
         <v>Attach curve contour w/b</v>
@@ -6397,10 +6397,10 @@
         <v>2</v>
       </c>
       <c r="J128" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K128" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L128">
         <v>646</v>
@@ -6426,7 +6426,7 @@
         <v>Shirt</v>
       </c>
       <c r="D129" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E129" t="str">
         <v>Attach FLAP pocket</v>
@@ -6444,10 +6444,10 @@
         <v>2</v>
       </c>
       <c r="J129" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K129" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L129">
         <v>646</v>
@@ -6473,7 +6473,7 @@
         <v>Shirt</v>
       </c>
       <c r="D130" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E130" t="str">
         <v>Attach hem facing to btm leg</v>
@@ -6491,10 +6491,10 @@
         <v>2</v>
       </c>
       <c r="J130" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K130" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L130">
         <v>646</v>
@@ -6520,7 +6520,7 @@
         <v>Shirt</v>
       </c>
       <c r="D131" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E131" t="str">
         <v>Join zip nip + fly attach</v>
@@ -6538,10 +6538,10 @@
         <v>2</v>
       </c>
       <c r="J131" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K131" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L131">
         <v>646</v>
@@ -6567,7 +6567,7 @@
         <v>Shirt</v>
       </c>
       <c r="D132" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E132" t="str">
         <v>Mark &amp; attach bar to w/b</v>
@@ -6585,10 +6585,10 @@
         <v>2</v>
       </c>
       <c r="J132" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K132" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L132">
         <v>646</v>
@@ -6614,7 +6614,7 @@
         <v>Shirt</v>
       </c>
       <c r="D133" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E133" t="str">
         <v>Thread trimming full garment</v>
@@ -6632,10 +6632,10 @@
         <v>2</v>
       </c>
       <c r="J133" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K133" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L133">
         <v>646</v>
@@ -6661,7 +6661,7 @@
         <v>Shirt</v>
       </c>
       <c r="D134" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E134" t="str">
         <v>Button attach (2 buttons)</v>
@@ -6679,10 +6679,10 @@
         <v>2</v>
       </c>
       <c r="J134" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K134" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L134">
         <v>646</v>
@@ -6708,7 +6708,7 @@
         <v>Shirt</v>
       </c>
       <c r="D135" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E135" t="str">
         <v>Press waistband &amp; seam</v>
@@ -6726,10 +6726,10 @@
         <v>2</v>
       </c>
       <c r="J135" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K135" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L135">
         <v>646</v>
@@ -6755,7 +6755,7 @@
         <v>Shirt</v>
       </c>
       <c r="D136" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E136" t="str">
         <v>Final press full shirt</v>
@@ -6773,10 +6773,10 @@
         <v>2</v>
       </c>
       <c r="J136" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K136" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L136">
         <v>646</v>
@@ -6802,7 +6802,7 @@
         <v>Shirt</v>
       </c>
       <c r="D137" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E137" t="str">
         <v>Label attach manual</v>
@@ -6820,10 +6820,10 @@
         <v>2</v>
       </c>
       <c r="J137" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K137" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L137">
         <v>646</v>
@@ -6849,7 +6849,7 @@
         <v>Shirt</v>
       </c>
       <c r="D138" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E138" t="str">
         <v>Measurement check &amp; hang tag</v>
@@ -6867,10 +6867,10 @@
         <v>2</v>
       </c>
       <c r="J138" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K138" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L138">
         <v>646</v>
@@ -6896,7 +6896,7 @@
         <v>Shirt</v>
       </c>
       <c r="D139" t="str">
-        <v>SH::EU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E139" t="str">
         <v>Fold, bag &amp; carton pack</v>
@@ -6914,10 +6914,10 @@
         <v>2</v>
       </c>
       <c r="J139" t="str">
-        <v>2026-05-11</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K139" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L139">
         <v>646</v>
@@ -6934,19 +6934,19 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B140" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C140" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D140" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E140" t="str">
-        <v>Attach label 2 sides</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F140" t="str">
         <v>SNL</v>
@@ -6961,39 +6961,39 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L140">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M140">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N140">
-        <v>0.25</v>
+        <v>0.43</v>
       </c>
       <c r="O140" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B141" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C141" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D141" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7008,39 +7008,39 @@
         <v>2</v>
       </c>
       <c r="J141" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K141" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L141">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M141">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N141">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="O141" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B142" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C142" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D142" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7055,39 +7055,39 @@
         <v>2</v>
       </c>
       <c r="J142" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K142" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L142">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M142">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N142">
-        <v>0.5</v>
+        <v>0.68</v>
       </c>
       <c r="O142" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B143" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C143" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D143" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7102,39 +7102,39 @@
         <v>2</v>
       </c>
       <c r="J143" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K143" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L143">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M143">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N143">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O143" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B144" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C144" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D144" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7149,39 +7149,39 @@
         <v>2</v>
       </c>
       <c r="J144" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K144" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L144">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M144">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N144">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O144" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B145" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C145" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D145" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7196,42 +7196,42 @@
         <v>2</v>
       </c>
       <c r="J145" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K145" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L145">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M145">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N145">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O145" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B146" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C146" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D146" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F146" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7243,45 +7243,45 @@
         <v>2</v>
       </c>
       <c r="J146" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K146" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L146">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M146">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N146">
-        <v>0.61</v>
+        <v>1</v>
       </c>
       <c r="O146" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B147" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C147" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D147" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F147" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G147" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7290,39 +7290,39 @@
         <v>2</v>
       </c>
       <c r="J147" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K147" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L147">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M147">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N147">
-        <v>0.42</v>
+        <v>1.5</v>
       </c>
       <c r="O147" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B148" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C148" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D148" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7337,42 +7337,42 @@
         <v>2</v>
       </c>
       <c r="J148" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K148" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L148">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M148">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N148">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="O148" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B149" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C149" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D149" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F149" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7384,39 +7384,39 @@
         <v>2</v>
       </c>
       <c r="J149" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K149" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L149">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M149">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>1.8</v>
       </c>
       <c r="O149" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B150" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C150" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D150" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7431,42 +7431,42 @@
         <v>2</v>
       </c>
       <c r="J150" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K150" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L150">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M150">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N150">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="O150" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B151" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C151" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D151" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Final press full shirt</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F151" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7478,39 +7478,39 @@
         <v>2</v>
       </c>
       <c r="J151" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K151" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L151">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M151">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N151">
-        <v>2.5</v>
+        <v>0.7</v>
       </c>
       <c r="O151" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B152" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C152" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D152" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Label attach manual</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7525,39 +7525,39 @@
         <v>2</v>
       </c>
       <c r="J152" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K152" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L152">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M152">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N152">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O152" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B153" t="str">
-        <v>4462A::SH</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C153" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D153" t="str">
-        <v>SH::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7572,45 +7572,45 @@
         <v>2</v>
       </c>
       <c r="J153" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K153" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L153">
-        <v>646</v>
+        <v>2190</v>
       </c>
       <c r="M153">
-        <v>15.28</v>
+        <v>17.96</v>
       </c>
       <c r="N153">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O153" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>935</v>
+        <v>910</v>
       </c>
       <c r="B154" t="str">
-        <v>4462A::SH</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C154" t="str">
-        <v>Shirt</v>
+        <v>Pant</v>
       </c>
       <c r="D154" t="str">
-        <v>SH::US RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Attach waistband - curved</v>
       </c>
       <c r="F154" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G154" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,19 +7619,19 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L154">
-        <v>646</v>
+        <v>1890</v>
       </c>
       <c r="M154">
-        <v>15.28</v>
+        <v>14</v>
       </c>
       <c r="N154">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O154" t="str">
         <v>priyanthi</v>
@@ -7639,19 +7639,19 @@
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B155" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C155" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D155" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E155" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Join inseam double stitch</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7666,42 +7666,42 @@
         <v>2</v>
       </c>
       <c r="J155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K155" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L155">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M155">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N155">
-        <v>0.43</v>
+        <v>1</v>
       </c>
       <c r="O155" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B156" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C156" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D156" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Attach cuff</v>
+        <v>Outseam overlock &amp; topstitch</v>
       </c>
       <c r="F156" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G156" t="str">
         <v>Sewing</v>
@@ -7713,42 +7713,42 @@
         <v>2</v>
       </c>
       <c r="J156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K156" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L156">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M156">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N156">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O156" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B157" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C157" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D157" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach zipper to fly</v>
       </c>
       <c r="F157" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G157" t="str">
         <v>Sewing</v>
@@ -7760,39 +7760,39 @@
         <v>2</v>
       </c>
       <c r="J157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K157" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L157">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M157">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N157">
-        <v>0.68</v>
+        <v>1.1</v>
       </c>
       <c r="O157" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B158" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C158" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D158" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Attach sleeve</v>
+        <v>Hem bottom with blind stitch</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7807,42 +7807,42 @@
         <v>2</v>
       </c>
       <c r="J158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K158" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L158">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M158">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N158">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O158" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B159" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C159" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D159" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Bartack pocket corners</v>
       </c>
       <c r="F159" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G159" t="str">
         <v>Sewing</v>
@@ -7854,45 +7854,45 @@
         <v>2</v>
       </c>
       <c r="J159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K159" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L159">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M159">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N159">
-        <v>2</v>
+        <v>0.45</v>
       </c>
       <c r="O159" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B160" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C160" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D160" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F160" t="str">
         <v>SNL</v>
       </c>
       <c r="G160" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H160" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7901,45 +7901,45 @@
         <v>2</v>
       </c>
       <c r="J160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K160" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L160">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M160">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N160">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="O160" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B161" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C161" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D161" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Press leg crease both sides</v>
       </c>
       <c r="F161" t="str">
-        <v>SNLU</v>
+        <v>VIR</v>
       </c>
       <c r="G161" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7948,42 +7948,42 @@
         <v>2</v>
       </c>
       <c r="J161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K161" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L161">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M161">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N161">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="O161" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B162" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C162" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D162" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Final press &amp; steam waistband</v>
       </c>
       <c r="F162" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G162" t="str">
         <v>Finishing</v>
@@ -7995,42 +7995,42 @@
         <v>2</v>
       </c>
       <c r="J162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K162" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L162">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M162">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N162">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O162" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B163" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C163" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D163" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Attach main &amp; care label</v>
       </c>
       <c r="F163" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8042,42 +8042,42 @@
         <v>2</v>
       </c>
       <c r="J163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K163" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L163">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M163">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N163">
-        <v>1.8</v>
+        <v>0.75</v>
       </c>
       <c r="O163" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B164" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C164" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D164" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F164" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G164" t="str">
         <v>Finishing</v>
@@ -8089,42 +8089,42 @@
         <v>2</v>
       </c>
       <c r="J164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K164" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L164">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M164">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N164">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="O164" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B165" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C165" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D165" t="str">
-        <v>BL::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Fold, board insert &amp; poly bag</v>
       </c>
       <c r="F165" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8136,22 +8136,22 @@
         <v>2</v>
       </c>
       <c r="J165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K165" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L165">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M165">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N165">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="O165" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="166">
@@ -8165,16 +8165,16 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E166" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F166" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G166" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H166" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.7</v>
+        <v>0.43</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,16 +8212,16 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F167" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G167" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H167" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F168" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G168" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>1</v>
+        <v>0.68</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8297,19 +8297,19 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B169" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C169" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D169" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E169" t="str">
-        <v>Attach waistband - curved</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8324,39 +8324,39 @@
         <v>2</v>
       </c>
       <c r="J169" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K169" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L169">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M169">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N169">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="O169" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B170" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C170" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D170" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Join inseam double stitch</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8371,42 +8371,42 @@
         <v>2</v>
       </c>
       <c r="J170" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K170" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L170">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M170">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O170" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B171" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C171" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D171" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Outseam overlock &amp; topstitch</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F171" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G171" t="str">
         <v>Sewing</v>
@@ -8418,42 +8418,42 @@
         <v>2</v>
       </c>
       <c r="J171" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K171" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L171">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M171">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N171">
-        <v>0.85</v>
+        <v>1.5</v>
       </c>
       <c r="O171" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B172" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C172" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D172" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Attach zipper to fly</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F172" t="str">
-        <v>SNNF</v>
+        <v>SNLU</v>
       </c>
       <c r="G172" t="str">
         <v>Sewing</v>
@@ -8465,45 +8465,45 @@
         <v>2</v>
       </c>
       <c r="J172" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K172" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L172">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M172">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N172">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O172" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B173" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C173" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D173" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Hem bottom with blind stitch</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
       </c>
       <c r="G173" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H173" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8512,45 +8512,45 @@
         <v>2</v>
       </c>
       <c r="J173" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K173" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L173">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M173">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N173">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O173" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B174" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C174" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D174" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Bartack pocket corners</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F174" t="str">
-        <v>ASNL</v>
+        <v>SNL</v>
       </c>
       <c r="G174" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H174" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8559,42 +8559,42 @@
         <v>2</v>
       </c>
       <c r="J174" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K174" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L174">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M174">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N174">
-        <v>0.45</v>
+        <v>1.8</v>
       </c>
       <c r="O174" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B175" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C175" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D175" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F175" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G175" t="str">
         <v>Finishing</v>
@@ -8606,39 +8606,39 @@
         <v>2</v>
       </c>
       <c r="J175" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K175" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L175">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M175">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="O175" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B176" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C176" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D176" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Press leg crease both sides</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F176" t="str">
         <v>VIR</v>
@@ -8653,42 +8653,42 @@
         <v>2</v>
       </c>
       <c r="J176" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K176" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L176">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M176">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N176">
         <v>2.2</v>
       </c>
       <c r="O176" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B177" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C177" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D177" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Final press &amp; steam waistband</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F177" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8700,39 +8700,39 @@
         <v>2</v>
       </c>
       <c r="J177" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K177" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L177">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M177">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N177">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="O177" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B178" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C178" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D178" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Attach main &amp; care label</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F178" t="str">
         <v>HELP</v>
@@ -8747,39 +8747,39 @@
         <v>2</v>
       </c>
       <c r="J178" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K178" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L178">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M178">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N178">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O178" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B179" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C179" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D179" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F179" t="str">
         <v>HELP</v>
@@ -8794,45 +8794,45 @@
         <v>2</v>
       </c>
       <c r="J179" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K179" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L179">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M179">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N179">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O179" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>910</v>
+        <v>920</v>
       </c>
       <c r="B180" t="str">
-        <v>3524P::PN</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C180" t="str">
-        <v>Pant</v>
+        <v>Jacket</v>
       </c>
       <c r="D180" t="str">
-        <v>PN::EU RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E180" t="str">
-        <v>Fold, board insert &amp; poly bag</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F180" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G180" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H180" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8841,39 +8841,39 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L180">
-        <v>1890</v>
+        <v>500</v>
       </c>
       <c r="M180">
-        <v>14</v>
+        <v>22.22</v>
       </c>
       <c r="N180">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
       <c r="O180" t="str">
-        <v>priyanthi</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B181" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C181" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D181" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E181" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F181" t="str">
         <v>SNL</v>
@@ -8888,39 +8888,39 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L181">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M181">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N181">
-        <v>0.43</v>
+        <v>0.56</v>
       </c>
       <c r="O181" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B182" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C182" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D182" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E182" t="str">
-        <v>Attach cuff</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F182" t="str">
         <v>SNL</v>
@@ -8935,39 +8935,39 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L182">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M182">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N182">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="O182" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B183" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C183" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D183" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E183" t="str">
-        <v>Attach set band collar</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8982,42 +8982,42 @@
         <v>2</v>
       </c>
       <c r="J183" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K183" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L183">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M183">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N183">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="O183" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B184" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C184" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D184" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E184" t="str">
-        <v>Attach sleeve</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F184" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G184" t="str">
         <v>Sewing</v>
@@ -9029,42 +9029,42 @@
         <v>2</v>
       </c>
       <c r="J184" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K184" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L184">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M184">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N184">
-        <v>1.5</v>
+        <v>0.84</v>
       </c>
       <c r="O184" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B185" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C185" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D185" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E185" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F185" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G185" t="str">
         <v>Sewing</v>
@@ -9076,42 +9076,42 @@
         <v>2</v>
       </c>
       <c r="J185" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K185" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L185">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M185">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N185">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="O185" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B186" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C186" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D186" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F186" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9123,42 +9123,42 @@
         <v>2</v>
       </c>
       <c r="J186" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K186" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L186">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M186">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N186">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="O186" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B187" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C187" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D187" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E187" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F187" t="str">
-        <v>SNLU</v>
+        <v>LDN</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9170,39 +9170,39 @@
         <v>2</v>
       </c>
       <c r="J187" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K187" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L187">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M187">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N187">
-        <v>1</v>
+        <v>0.63</v>
       </c>
       <c r="O187" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B188" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C188" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D188" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E188" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F188" t="str">
         <v>SNL</v>
@@ -9217,39 +9217,39 @@
         <v>2</v>
       </c>
       <c r="J188" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K188" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L188">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M188">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N188">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O188" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B189" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C189" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D189" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E189" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F189" t="str">
         <v>SNL</v>
@@ -9264,39 +9264,39 @@
         <v>2</v>
       </c>
       <c r="J189" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K189" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L189">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M189">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N189">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="O189" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B190" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C190" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D190" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E190" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F190" t="str">
         <v>VIR</v>
@@ -9311,39 +9311,39 @@
         <v>2</v>
       </c>
       <c r="J190" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K190" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L190">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M190">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N190">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="O190" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B191" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C191" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D191" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E191" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F191" t="str">
         <v>VIR</v>
@@ -9358,39 +9358,39 @@
         <v>2</v>
       </c>
       <c r="J191" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K191" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L191">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M191">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N191">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="O191" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B192" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C192" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D192" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E192" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F192" t="str">
         <v>HELP</v>
@@ -9405,39 +9405,39 @@
         <v>2</v>
       </c>
       <c r="J192" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K192" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L192">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M192">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N192">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="O192" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B193" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C193" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D193" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E193" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F193" t="str">
         <v>HELP</v>
@@ -9452,39 +9452,39 @@
         <v>2</v>
       </c>
       <c r="J193" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K193" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L193">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M193">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N193">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O193" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B194" t="str">
-        <v>6882T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C194" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D194" t="str">
-        <v>BL::UK RT</v>
+        <v>JK::B</v>
       </c>
       <c r="E194" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F194" t="str">
         <v>HELP</v>
@@ -9499,22 +9499,22 @@
         <v>2</v>
       </c>
       <c r="J194" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K194" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L194">
-        <v>2190</v>
+        <v>500</v>
       </c>
       <c r="M194">
-        <v>17.96</v>
+        <v>22.22</v>
       </c>
       <c r="N194">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O194" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="195">
@@ -9528,7 +9528,7 @@
         <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E195" t="str">
         <v>Attach back stitch</v>
@@ -9546,10 +9546,10 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L195">
         <v>500</v>
@@ -9575,7 +9575,7 @@
         <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E196" t="str">
         <v>Attach pocket bag</v>
@@ -9593,10 +9593,10 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L196">
         <v>500</v>
@@ -9622,7 +9622,7 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E197" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9669,7 +9669,7 @@
         <v>Jacket</v>
       </c>
       <c r="D198" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E198" t="str">
         <v>Collar attach to body</v>
@@ -9687,10 +9687,10 @@
         <v>2</v>
       </c>
       <c r="J198" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K198" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L198">
         <v>500</v>
@@ -9716,7 +9716,7 @@
         <v>Jacket</v>
       </c>
       <c r="D199" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E199" t="str">
         <v>Collar attach lining</v>
@@ -9734,10 +9734,10 @@
         <v>2</v>
       </c>
       <c r="J199" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K199" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L199">
         <v>500</v>
@@ -9763,7 +9763,7 @@
         <v>Jacket</v>
       </c>
       <c r="D200" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E200" t="str">
         <v>Sleeve attach overlock</v>
@@ -9781,10 +9781,10 @@
         <v>2</v>
       </c>
       <c r="J200" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K200" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L200">
         <v>500</v>
@@ -9810,7 +9810,7 @@
         <v>Jacket</v>
       </c>
       <c r="D201" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E201" t="str">
         <v>Attach zipper front</v>
@@ -9828,10 +9828,10 @@
         <v>2</v>
       </c>
       <c r="J201" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K201" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L201">
         <v>500</v>
@@ -9857,7 +9857,7 @@
         <v>Jacket</v>
       </c>
       <c r="D202" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E202" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -9875,10 +9875,10 @@
         <v>2</v>
       </c>
       <c r="J202" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K202" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L202">
         <v>500</v>
@@ -9904,7 +9904,7 @@
         <v>Jacket</v>
       </c>
       <c r="D203" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E203" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -9922,10 +9922,10 @@
         <v>2</v>
       </c>
       <c r="J203" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K203" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L203">
         <v>500</v>
@@ -9951,7 +9951,7 @@
         <v>Jacket</v>
       </c>
       <c r="D204" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E204" t="str">
         <v>Button attach (2 buttons)</v>
@@ -9969,10 +9969,10 @@
         <v>2</v>
       </c>
       <c r="J204" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K204" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L204">
         <v>500</v>
@@ -9998,7 +9998,7 @@
         <v>Jacket</v>
       </c>
       <c r="D205" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E205" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10016,10 +10016,10 @@
         <v>2</v>
       </c>
       <c r="J205" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K205" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L205">
         <v>500</v>
@@ -10045,7 +10045,7 @@
         <v>Jacket</v>
       </c>
       <c r="D206" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E206" t="str">
         <v>Final press full jacket</v>
@@ -10063,10 +10063,10 @@
         <v>2</v>
       </c>
       <c r="J206" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K206" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L206">
         <v>500</v>
@@ -10092,7 +10092,7 @@
         <v>Jacket</v>
       </c>
       <c r="D207" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E207" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10110,10 +10110,10 @@
         <v>2</v>
       </c>
       <c r="J207" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K207" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L207">
         <v>500</v>
@@ -10139,7 +10139,7 @@
         <v>Jacket</v>
       </c>
       <c r="D208" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E208" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10157,10 +10157,10 @@
         <v>2</v>
       </c>
       <c r="J208" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K208" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L208">
         <v>500</v>
@@ -10186,7 +10186,7 @@
         <v>Jacket</v>
       </c>
       <c r="D209" t="str">
-        <v>JK::B</v>
+        <v>JK::G</v>
       </c>
       <c r="E209" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10204,10 +10204,10 @@
         <v>2</v>
       </c>
       <c r="J209" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K209" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L209">
         <v>500</v>
@@ -10233,7 +10233,7 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E210" t="str">
         <v>Attach back stitch</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10280,7 +10280,7 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E211" t="str">
         <v>Attach pocket bag</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10327,7 +10327,7 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E212" t="str">
         <v>Attach self &amp; lining sleeve</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10374,7 +10374,7 @@
         <v>Jacket</v>
       </c>
       <c r="D213" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E213" t="str">
         <v>Collar attach to body</v>
@@ -10392,10 +10392,10 @@
         <v>2</v>
       </c>
       <c r="J213" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K213" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L213">
         <v>500</v>
@@ -10421,7 +10421,7 @@
         <v>Jacket</v>
       </c>
       <c r="D214" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E214" t="str">
         <v>Collar attach lining</v>
@@ -10439,10 +10439,10 @@
         <v>2</v>
       </c>
       <c r="J214" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K214" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L214">
         <v>500</v>
@@ -10468,7 +10468,7 @@
         <v>Jacket</v>
       </c>
       <c r="D215" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E215" t="str">
         <v>Sleeve attach overlock</v>
@@ -10486,10 +10486,10 @@
         <v>2</v>
       </c>
       <c r="J215" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K215" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L215">
         <v>500</v>
@@ -10515,7 +10515,7 @@
         <v>Jacket</v>
       </c>
       <c r="D216" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E216" t="str">
         <v>Attach zipper front</v>
@@ -10533,10 +10533,10 @@
         <v>2</v>
       </c>
       <c r="J216" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K216" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L216">
         <v>500</v>
@@ -10562,7 +10562,7 @@
         <v>Jacket</v>
       </c>
       <c r="D217" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E217" t="str">
         <v>Attach welt pocket by D/N</v>
@@ -10580,10 +10580,10 @@
         <v>2</v>
       </c>
       <c r="J217" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K217" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L217">
         <v>500</v>
@@ -10609,7 +10609,7 @@
         <v>Jacket</v>
       </c>
       <c r="D218" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E218" t="str">
         <v>Thread trim &amp; broken check</v>
@@ -10627,10 +10627,10 @@
         <v>2</v>
       </c>
       <c r="J218" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K218" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L218">
         <v>500</v>
@@ -10656,7 +10656,7 @@
         <v>Jacket</v>
       </c>
       <c r="D219" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E219" t="str">
         <v>Button attach (2 buttons)</v>
@@ -10674,10 +10674,10 @@
         <v>2</v>
       </c>
       <c r="J219" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K219" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L219">
         <v>500</v>
@@ -10703,7 +10703,7 @@
         <v>Jacket</v>
       </c>
       <c r="D220" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E220" t="str">
         <v>Press collar &amp; lapel area</v>
@@ -10721,10 +10721,10 @@
         <v>2</v>
       </c>
       <c r="J220" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K220" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L220">
         <v>500</v>
@@ -10750,7 +10750,7 @@
         <v>Jacket</v>
       </c>
       <c r="D221" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E221" t="str">
         <v>Final press full jacket</v>
@@ -10768,10 +10768,10 @@
         <v>2</v>
       </c>
       <c r="J221" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K221" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L221">
         <v>500</v>
@@ -10797,7 +10797,7 @@
         <v>Jacket</v>
       </c>
       <c r="D222" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E222" t="str">
         <v>Label attach - main &amp; care</v>
@@ -10815,10 +10815,10 @@
         <v>2</v>
       </c>
       <c r="J222" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K222" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L222">
         <v>500</v>
@@ -10844,7 +10844,7 @@
         <v>Jacket</v>
       </c>
       <c r="D223" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E223" t="str">
         <v>Hang tag attach &amp; measurement check</v>
@@ -10862,10 +10862,10 @@
         <v>2</v>
       </c>
       <c r="J223" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K223" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L223">
         <v>500</v>
@@ -10891,7 +10891,7 @@
         <v>Jacket</v>
       </c>
       <c r="D224" t="str">
-        <v>JK::G</v>
+        <v>JK::W</v>
       </c>
       <c r="E224" t="str">
         <v>Fold on hanger &amp; poly bag</v>
@@ -10909,10 +10909,10 @@
         <v>2</v>
       </c>
       <c r="J224" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K224" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L224">
         <v>500</v>
@@ -10929,19 +10929,19 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B225" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C225" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D225" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E225" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F225" t="str">
         <v>SNL</v>
@@ -10956,39 +10956,39 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L225">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M225">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N225">
-        <v>1.26</v>
+        <v>1.1</v>
       </c>
       <c r="O225" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B226" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C226" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D226" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E226" t="str">
-        <v>Attach pocket bag</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F226" t="str">
         <v>SNL</v>
@@ -11003,39 +11003,39 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L226">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M226">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N226">
-        <v>0.56</v>
+        <v>1.2</v>
       </c>
       <c r="O226" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B227" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C227" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D227" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F227" t="str">
         <v>SNL</v>
@@ -11050,42 +11050,42 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L227">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M227">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N227">
-        <v>1.04</v>
+        <v>1.6</v>
       </c>
       <c r="O227" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B228" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C228" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D228" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E228" t="str">
-        <v>Collar attach to body</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F228" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G228" t="str">
         <v>Sewing</v>
@@ -11097,42 +11097,42 @@
         <v>2</v>
       </c>
       <c r="J228" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K228" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L228">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M228">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N228">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="O228" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B229" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C229" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D229" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E229" t="str">
-        <v>Collar attach lining</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F229" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G229" t="str">
         <v>Sewing</v>
@@ -11144,42 +11144,42 @@
         <v>2</v>
       </c>
       <c r="J229" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K229" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L229">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M229">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N229">
-        <v>0.84</v>
+        <v>0.7</v>
       </c>
       <c r="O229" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B230" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C230" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D230" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E230" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F230" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G230" t="str">
         <v>Sewing</v>
@@ -11191,42 +11191,42 @@
         <v>2</v>
       </c>
       <c r="J230" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K230" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L230">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M230">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N230">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="O230" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B231" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C231" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D231" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E231" t="str">
-        <v>Attach zipper front</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F231" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11238,45 +11238,45 @@
         <v>2</v>
       </c>
       <c r="J231" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K231" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L231">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M231">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N231">
-        <v>2.48</v>
+        <v>1.3</v>
       </c>
       <c r="O231" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B232" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C232" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D232" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E232" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F232" t="str">
-        <v>LDN</v>
+        <v>SNL</v>
       </c>
       <c r="G232" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H232" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11285,39 +11285,39 @@
         <v>2</v>
       </c>
       <c r="J232" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K232" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L232">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M232">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N232">
-        <v>0.63</v>
+        <v>2</v>
       </c>
       <c r="O232" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B233" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C233" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D233" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E233" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F233" t="str">
         <v>SNL</v>
@@ -11332,42 +11332,42 @@
         <v>2</v>
       </c>
       <c r="J233" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K233" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L233">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M233">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N233">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="O233" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B234" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C234" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D234" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E234" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F234" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G234" t="str">
         <v>Finishing</v>
@@ -11379,39 +11379,39 @@
         <v>2</v>
       </c>
       <c r="J234" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K234" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L234">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M234">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N234">
-        <v>1.2</v>
+        <v>3.2</v>
       </c>
       <c r="O234" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B235" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C235" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D235" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E235" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F235" t="str">
         <v>VIR</v>
@@ -11426,42 +11426,42 @@
         <v>2</v>
       </c>
       <c r="J235" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K235" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L235">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M235">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N235">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="O235" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B236" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C236" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D236" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E236" t="str">
-        <v>Final press full jacket</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F236" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11473,39 +11473,39 @@
         <v>2</v>
       </c>
       <c r="J236" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K236" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L236">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M236">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N236">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="O236" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B237" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C237" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D237" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E237" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F237" t="str">
         <v>HELP</v>
@@ -11520,39 +11520,39 @@
         <v>2</v>
       </c>
       <c r="J237" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K237" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L237">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M237">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N237">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O237" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B238" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C238" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D238" t="str">
-        <v>JK::W</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E238" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F238" t="str">
         <v>HELP</v>
@@ -11567,45 +11567,45 @@
         <v>2</v>
       </c>
       <c r="J238" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K238" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L238">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M238">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N238">
         <v>1.1</v>
       </c>
       <c r="O238" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B239" t="str">
-        <v>GOT12524N::JK</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C239" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D239" t="str">
-        <v>JK::W</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E239" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F239" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G239" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H239" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11614,22 +11614,22 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L239">
-        <v>500</v>
+        <v>607</v>
       </c>
       <c r="M239">
-        <v>22.22</v>
+        <v>19</v>
       </c>
       <c r="N239">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O239" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="240">
@@ -11643,10 +11643,10 @@
         <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F240" t="str">
         <v>SNL</v>
@@ -11661,10 +11661,10 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L240">
         <v>607</v>
@@ -11673,7 +11673,7 @@
         <v>19</v>
       </c>
       <c r="N240">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O240" t="str">
         <v>sasanthar</v>
@@ -11690,10 +11690,10 @@
         <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F241" t="str">
         <v>SNL</v>
@@ -11708,10 +11708,10 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L241">
         <v>607</v>
@@ -11720,7 +11720,7 @@
         <v>19</v>
       </c>
       <c r="N241">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O241" t="str">
         <v>sasanthar</v>
@@ -11737,13 +11737,13 @@
         <v>Blouse</v>
       </c>
       <c r="D242" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F242" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G242" t="str">
         <v>Sewing</v>
@@ -11755,10 +11755,10 @@
         <v>2</v>
       </c>
       <c r="J242" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K242" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L242">
         <v>607</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11784,13 +11784,13 @@
         <v>Blouse</v>
       </c>
       <c r="D243" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F243" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G243" t="str">
         <v>Sewing</v>
@@ -11802,10 +11802,10 @@
         <v>2</v>
       </c>
       <c r="J243" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K243" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L243">
         <v>607</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11831,10 +11831,10 @@
         <v>Blouse</v>
       </c>
       <c r="D244" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F244" t="str">
         <v>SNL</v>
@@ -11849,10 +11849,10 @@
         <v>2</v>
       </c>
       <c r="J244" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K244" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L244">
         <v>607</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11878,10 +11878,10 @@
         <v>Blouse</v>
       </c>
       <c r="D245" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F245" t="str">
         <v>SNL</v>
@@ -11896,10 +11896,10 @@
         <v>2</v>
       </c>
       <c r="J245" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K245" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L245">
         <v>607</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11925,16 +11925,16 @@
         <v>Blouse</v>
       </c>
       <c r="D246" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
       </c>
       <c r="G246" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H246" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11943,10 +11943,10 @@
         <v>2</v>
       </c>
       <c r="J246" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K246" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L246">
         <v>607</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11972,10 +11972,10 @@
         <v>Blouse</v>
       </c>
       <c r="D247" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
@@ -11990,10 +11990,10 @@
         <v>2</v>
       </c>
       <c r="J247" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K247" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L247">
         <v>607</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12019,13 +12019,13 @@
         <v>Blouse</v>
       </c>
       <c r="D248" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F248" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G248" t="str">
         <v>Finishing</v>
@@ -12037,10 +12037,10 @@
         <v>2</v>
       </c>
       <c r="J248" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K248" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L248">
         <v>607</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12066,10 +12066,10 @@
         <v>Blouse</v>
       </c>
       <c r="D249" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F249" t="str">
         <v>VIR</v>
@@ -12084,10 +12084,10 @@
         <v>2</v>
       </c>
       <c r="J249" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K249" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L249">
         <v>607</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12113,13 +12113,13 @@
         <v>Blouse</v>
       </c>
       <c r="D250" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F250" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12131,10 +12131,10 @@
         <v>2</v>
       </c>
       <c r="J250" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K250" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L250">
         <v>607</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12160,10 +12160,10 @@
         <v>Blouse</v>
       </c>
       <c r="D251" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F251" t="str">
         <v>HELP</v>
@@ -12178,10 +12178,10 @@
         <v>2</v>
       </c>
       <c r="J251" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K251" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L251">
         <v>607</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12207,10 +12207,10 @@
         <v>Blouse</v>
       </c>
       <c r="D252" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F252" t="str">
         <v>HELP</v>
@@ -12225,10 +12225,10 @@
         <v>2</v>
       </c>
       <c r="J252" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K252" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L252">
         <v>607</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,16 +12254,16 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F253" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G253" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H253" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12301,10 +12301,10 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F254" t="str">
         <v>SNL</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,10 +12348,10 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F255" t="str">
         <v>SNL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12378,7 +12378,7 @@
         <v>19</v>
       </c>
       <c r="N255">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O255" t="str">
         <v>sasanthar</v>
@@ -12395,13 +12395,13 @@
         <v>Blouse</v>
       </c>
       <c r="D256" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F256" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G256" t="str">
         <v>Sewing</v>
@@ -12413,10 +12413,10 @@
         <v>2</v>
       </c>
       <c r="J256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K256" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L256">
         <v>607</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>1.6</v>
+        <v>0.75</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12442,13 +12442,13 @@
         <v>Blouse</v>
       </c>
       <c r="D257" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F257" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G257" t="str">
         <v>Sewing</v>
@@ -12460,10 +12460,10 @@
         <v>2</v>
       </c>
       <c r="J257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K257" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L257">
         <v>607</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>0.75</v>
+        <v>0.7</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12489,10 +12489,10 @@
         <v>Blouse</v>
       </c>
       <c r="D258" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F258" t="str">
         <v>SNL</v>
@@ -12507,10 +12507,10 @@
         <v>2</v>
       </c>
       <c r="J258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K258" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L258">
         <v>607</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12536,10 +12536,10 @@
         <v>Blouse</v>
       </c>
       <c r="D259" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F259" t="str">
         <v>SNL</v>
@@ -12554,10 +12554,10 @@
         <v>2</v>
       </c>
       <c r="J259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K259" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L259">
         <v>607</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12583,16 +12583,16 @@
         <v>Blouse</v>
       </c>
       <c r="D260" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
       </c>
       <c r="G260" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H260" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12601,10 +12601,10 @@
         <v>2</v>
       </c>
       <c r="J260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K260" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L260">
         <v>607</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12630,10 +12630,10 @@
         <v>Blouse</v>
       </c>
       <c r="D261" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Thread trim full garment</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
@@ -12648,10 +12648,10 @@
         <v>2</v>
       </c>
       <c r="J261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K261" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L261">
         <v>607</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12677,13 +12677,13 @@
         <v>Blouse</v>
       </c>
       <c r="D262" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F262" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G262" t="str">
         <v>Finishing</v>
@@ -12695,10 +12695,10 @@
         <v>2</v>
       </c>
       <c r="J262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K262" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L262">
         <v>607</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>1.9</v>
+        <v>3.2</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12724,10 +12724,10 @@
         <v>Blouse</v>
       </c>
       <c r="D263" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Full body pressing</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F263" t="str">
         <v>VIR</v>
@@ -12742,10 +12742,10 @@
         <v>2</v>
       </c>
       <c r="J263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K263" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L263">
         <v>607</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12771,13 +12771,13 @@
         <v>Blouse</v>
       </c>
       <c r="D264" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F264" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12789,10 +12789,10 @@
         <v>2</v>
       </c>
       <c r="J264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K264" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L264">
         <v>607</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12818,10 +12818,10 @@
         <v>Blouse</v>
       </c>
       <c r="D265" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F265" t="str">
         <v>HELP</v>
@@ -12836,10 +12836,10 @@
         <v>2</v>
       </c>
       <c r="J265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K265" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L265">
         <v>607</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12865,10 +12865,10 @@
         <v>Blouse</v>
       </c>
       <c r="D266" t="str">
-        <v>BL::US RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Hang tag attach</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F266" t="str">
         <v>HELP</v>
@@ -12883,10 +12883,10 @@
         <v>2</v>
       </c>
       <c r="J266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K266" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L266">
         <v>607</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>0.85</v>
+        <v>1.1</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12903,66 +12903,66 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B267" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C267" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D267" t="str">
-        <v>BL::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F267" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G267" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H267" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I267">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L267">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M267">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N267">
-        <v>1.1</v>
+        <v>0.25</v>
       </c>
       <c r="O267" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B268" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C268" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D268" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Attach back panel to front</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F268" t="str">
         <v>SNL</v>
@@ -12974,42 +12974,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I268">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L268">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M268">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N268">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O268" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B269" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C269" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D269" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Attach collar to body</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F269" t="str">
         <v>SNL</v>
@@ -13021,42 +13021,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L269">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M269">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N269">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="O269" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B270" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C270" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D270" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13068,45 +13068,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I270">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L270">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M270">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N270">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="O270" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B271" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C271" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D271" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F271" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G271" t="str">
         <v>Sewing</v>
@@ -13115,42 +13115,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I271">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L271">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M271">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N271">
-        <v>0.75</v>
+        <v>0.45</v>
       </c>
       <c r="O271" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B272" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C272" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D272" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13162,42 +13162,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I272">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L272">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M272">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N272">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="O272" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B273" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C273" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D273" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F273" t="str">
         <v>SNL</v>
@@ -13209,45 +13209,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I273">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L273">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M273">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N273">
-        <v>1</v>
+        <v>0.61</v>
       </c>
       <c r="O273" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B274" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C274" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D274" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F274" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G274" t="str">
         <v>Sewing</v>
@@ -13256,42 +13256,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I274">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L274">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M274">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N274">
-        <v>1.3</v>
+        <v>0.42</v>
       </c>
       <c r="O274" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B275" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C275" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D275" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Thread trim full garment</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
@@ -13303,42 +13303,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L275">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M275">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N275">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="O275" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B276" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C276" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D276" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F276" t="str">
         <v>SNL</v>
@@ -13350,42 +13350,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I276">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L276">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M276">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N276">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O276" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B277" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C277" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D277" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Full body pressing</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F277" t="str">
         <v>VIR</v>
@@ -13397,42 +13397,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I277">
+        <v>3</v>
+      </c>
+      <c r="J277" t="str">
+        <v>2026-05-16</v>
+      </c>
+      <c r="K277" t="str">
+        <v>2026-05-19</v>
+      </c>
+      <c r="L277">
+        <v>646</v>
+      </c>
+      <c r="M277">
+        <v>15.28</v>
+      </c>
+      <c r="N277">
         <v>2</v>
       </c>
-      <c r="J277" t="str">
-        <v>2026-06-08</v>
-      </c>
-      <c r="K277" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="L277">
-        <v>607</v>
-      </c>
-      <c r="M277">
-        <v>19</v>
-      </c>
-      <c r="N277">
-        <v>3.2</v>
-      </c>
       <c r="O277" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B278" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C278" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D278" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F278" t="str">
         <v>VIR</v>
@@ -13444,42 +13444,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I278">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L278">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M278">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N278">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="O278" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B279" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C279" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D279" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F279" t="str">
         <v>HELP</v>
@@ -13491,42 +13491,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I279">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L279">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M279">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N279">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="O279" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B280" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C280" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D280" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Hang tag attach</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F280" t="str">
         <v>HELP</v>
@@ -13538,42 +13538,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I280">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L280">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M280">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N280">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O280" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B281" t="str">
-        <v>8774T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C281" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D281" t="str">
-        <v>BL::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13585,25 +13585,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I281">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-06-08</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-19</v>
       </c>
       <c r="L281">
-        <v>607</v>
+        <v>646</v>
       </c>
       <c r="M281">
-        <v>19</v>
+        <v>15.28</v>
       </c>
       <c r="N281">
         <v>1.1</v>
       </c>
       <c r="O281" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="282">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -475,7 +475,7 @@
         <v>1</v>
       </c>
       <c r="J2" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K2" t="str">
         <v>2026-05-13</v>
@@ -522,7 +522,7 @@
         <v>1</v>
       </c>
       <c r="J3" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K3" t="str">
         <v>2026-05-13</v>
@@ -569,7 +569,7 @@
         <v>1</v>
       </c>
       <c r="J4" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K4" t="str">
         <v>2026-05-13</v>
@@ -616,7 +616,7 @@
         <v>1</v>
       </c>
       <c r="J5" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K5" t="str">
         <v>2026-05-13</v>
@@ -663,7 +663,7 @@
         <v>1</v>
       </c>
       <c r="J6" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K6" t="str">
         <v>2026-05-13</v>
@@ -710,7 +710,7 @@
         <v>1</v>
       </c>
       <c r="J7" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K7" t="str">
         <v>2026-05-13</v>
@@ -757,7 +757,7 @@
         <v>1</v>
       </c>
       <c r="J8" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K8" t="str">
         <v>2026-05-13</v>
@@ -804,7 +804,7 @@
         <v>1</v>
       </c>
       <c r="J9" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K9" t="str">
         <v>2026-05-13</v>
@@ -851,7 +851,7 @@
         <v>1</v>
       </c>
       <c r="J10" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K10" t="str">
         <v>2026-05-13</v>
@@ -898,7 +898,7 @@
         <v>1</v>
       </c>
       <c r="J11" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K11" t="str">
         <v>2026-05-13</v>
@@ -945,7 +945,7 @@
         <v>1</v>
       </c>
       <c r="J12" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K12" t="str">
         <v>2026-05-13</v>
@@ -992,7 +992,7 @@
         <v>1</v>
       </c>
       <c r="J13" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K13" t="str">
         <v>2026-05-13</v>
@@ -1039,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="J14" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K14" t="str">
         <v>2026-05-13</v>
@@ -1086,7 +1086,7 @@
         <v>1</v>
       </c>
       <c r="J15" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K15" t="str">
         <v>2026-05-13</v>
@@ -1115,7 +1115,7 @@
         <v>Blouse</v>
       </c>
       <c r="D16" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E16" t="str">
         <v>Attach front placket</v>
@@ -1133,10 +1133,10 @@
         <v>1</v>
       </c>
       <c r="J16" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K16" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L16">
         <v>646</v>
@@ -1162,7 +1162,7 @@
         <v>Blouse</v>
       </c>
       <c r="D17" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E17" t="str">
         <v>Attach collar to neckline</v>
@@ -1180,10 +1180,10 @@
         <v>1</v>
       </c>
       <c r="J17" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K17" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L17">
         <v>646</v>
@@ -1209,7 +1209,7 @@
         <v>Blouse</v>
       </c>
       <c r="D18" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E18" t="str">
         <v>Attach sleeve to body</v>
@@ -1227,10 +1227,10 @@
         <v>1</v>
       </c>
       <c r="J18" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K18" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L18">
         <v>646</v>
@@ -1256,7 +1256,7 @@
         <v>Blouse</v>
       </c>
       <c r="D19" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E19" t="str">
         <v>Join side seams</v>
@@ -1274,10 +1274,10 @@
         <v>1</v>
       </c>
       <c r="J19" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K19" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L19">
         <v>646</v>
@@ -1303,7 +1303,7 @@
         <v>Blouse</v>
       </c>
       <c r="D20" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E20" t="str">
         <v>Hem bottom edge</v>
@@ -1321,10 +1321,10 @@
         <v>1</v>
       </c>
       <c r="J20" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K20" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L20">
         <v>646</v>
@@ -1350,7 +1350,7 @@
         <v>Blouse</v>
       </c>
       <c r="D21" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E21" t="str">
         <v>Attach cuff to sleeve</v>
@@ -1368,10 +1368,10 @@
         <v>1</v>
       </c>
       <c r="J21" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K21" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L21">
         <v>646</v>
@@ -1397,7 +1397,7 @@
         <v>Blouse</v>
       </c>
       <c r="D22" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E22" t="str">
         <v>Overlock neckline edge</v>
@@ -1415,10 +1415,10 @@
         <v>1</v>
       </c>
       <c r="J22" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K22" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L22">
         <v>646</v>
@@ -1444,7 +1444,7 @@
         <v>Blouse</v>
       </c>
       <c r="D23" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E23" t="str">
         <v>Thread trimming full garment</v>
@@ -1462,10 +1462,10 @@
         <v>1</v>
       </c>
       <c r="J23" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K23" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L23">
         <v>646</v>
@@ -1491,7 +1491,7 @@
         <v>Blouse</v>
       </c>
       <c r="D24" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E24" t="str">
         <v>Button attach (3 buttons)</v>
@@ -1509,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="J24" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K24" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L24">
         <v>646</v>
@@ -1538,7 +1538,7 @@
         <v>Blouse</v>
       </c>
       <c r="D25" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E25" t="str">
         <v>Final pressing body</v>
@@ -1556,10 +1556,10 @@
         <v>1</v>
       </c>
       <c r="J25" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K25" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L25">
         <v>646</v>
@@ -1585,7 +1585,7 @@
         <v>Blouse</v>
       </c>
       <c r="D26" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E26" t="str">
         <v>Press collar &amp; cuff</v>
@@ -1603,10 +1603,10 @@
         <v>1</v>
       </c>
       <c r="J26" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K26" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L26">
         <v>646</v>
@@ -1632,7 +1632,7 @@
         <v>Blouse</v>
       </c>
       <c r="D27" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E27" t="str">
         <v>Attach main label manual</v>
@@ -1650,10 +1650,10 @@
         <v>1</v>
       </c>
       <c r="J27" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K27" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L27">
         <v>646</v>
@@ -1679,7 +1679,7 @@
         <v>Blouse</v>
       </c>
       <c r="D28" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E28" t="str">
         <v>Hang tag attach &amp; fold</v>
@@ -1697,10 +1697,10 @@
         <v>1</v>
       </c>
       <c r="J28" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K28" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L28">
         <v>646</v>
@@ -1726,7 +1726,7 @@
         <v>Blouse</v>
       </c>
       <c r="D29" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E29" t="str">
         <v>Poly bag &amp; pack into carton</v>
@@ -1744,10 +1744,10 @@
         <v>1</v>
       </c>
       <c r="J29" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-16</v>
       </c>
       <c r="K29" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L29">
         <v>646</v>
@@ -1767,16 +1767,16 @@
         <v>847</v>
       </c>
       <c r="B30" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C30" t="str">
         <v>Blouse</v>
       </c>
       <c r="D30" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E30" t="str">
-        <v>Attach front placket</v>
+        <v>Attach front yoke to body</v>
       </c>
       <c r="F30" t="str">
         <v>SNL</v>
@@ -1791,22 +1791,22 @@
         <v>1</v>
       </c>
       <c r="J30" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K30" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L30">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M30">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N30">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="O30" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="31">
@@ -1814,16 +1814,16 @@
         <v>847</v>
       </c>
       <c r="B31" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C31" t="str">
         <v>Blouse</v>
       </c>
       <c r="D31" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E31" t="str">
-        <v>Attach collar to neckline</v>
+        <v>Attach collar band</v>
       </c>
       <c r="F31" t="str">
         <v>SNL</v>
@@ -1838,22 +1838,22 @@
         <v>1</v>
       </c>
       <c r="J31" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K31" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L31">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M31">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N31">
-        <v>0.95</v>
+        <v>1.1</v>
       </c>
       <c r="O31" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="32">
@@ -1861,16 +1861,16 @@
         <v>847</v>
       </c>
       <c r="B32" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C32" t="str">
         <v>Blouse</v>
       </c>
       <c r="D32" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E32" t="str">
-        <v>Attach sleeve to body</v>
+        <v>Set sleeve with easing</v>
       </c>
       <c r="F32" t="str">
         <v>SNL</v>
@@ -1885,22 +1885,22 @@
         <v>1</v>
       </c>
       <c r="J32" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K32" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L32">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M32">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N32">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
       <c r="O32" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="33">
@@ -1908,19 +1908,19 @@
         <v>847</v>
       </c>
       <c r="B33" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C33" t="str">
         <v>Blouse</v>
       </c>
       <c r="D33" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E33" t="str">
-        <v>Join side seams</v>
+        <v>Join underarm seam</v>
       </c>
       <c r="F33" t="str">
-        <v>3O/L</v>
+        <v>SNL-SS</v>
       </c>
       <c r="G33" t="str">
         <v>Sewing</v>
@@ -1932,22 +1932,22 @@
         <v>1</v>
       </c>
       <c r="J33" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K33" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L33">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M33">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N33">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="O33" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="34">
@@ -1955,19 +1955,19 @@
         <v>847</v>
       </c>
       <c r="B34" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C34" t="str">
         <v>Blouse</v>
       </c>
       <c r="D34" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E34" t="str">
-        <v>Hem bottom edge</v>
+        <v>Overlock armhole edge</v>
       </c>
       <c r="F34" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G34" t="str">
         <v>Sewing</v>
@@ -1979,22 +1979,22 @@
         <v>1</v>
       </c>
       <c r="J34" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K34" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L34">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M34">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N34">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="O34" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="35">
@@ -2002,16 +2002,16 @@
         <v>847</v>
       </c>
       <c r="B35" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C35" t="str">
         <v>Blouse</v>
       </c>
       <c r="D35" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E35" t="str">
-        <v>Attach cuff to sleeve</v>
+        <v>Hem sleeve &amp; body</v>
       </c>
       <c r="F35" t="str">
         <v>SNL</v>
@@ -2026,22 +2026,22 @@
         <v>1</v>
       </c>
       <c r="J35" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K35" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L35">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M35">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O35" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="36">
@@ -2049,19 +2049,19 @@
         <v>847</v>
       </c>
       <c r="B36" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C36" t="str">
         <v>Blouse</v>
       </c>
       <c r="D36" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E36" t="str">
-        <v>Overlock neckline edge</v>
+        <v>Attach lining to facing</v>
       </c>
       <c r="F36" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G36" t="str">
         <v>Sewing</v>
@@ -2073,22 +2073,22 @@
         <v>1</v>
       </c>
       <c r="J36" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K36" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L36">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M36">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N36">
-        <v>0.55</v>
+        <v>1.05</v>
       </c>
       <c r="O36" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="37">
@@ -2096,16 +2096,16 @@
         <v>847</v>
       </c>
       <c r="B37" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C37" t="str">
         <v>Blouse</v>
       </c>
       <c r="D37" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E37" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Thread trimming &amp; spot cleaning</v>
       </c>
       <c r="F37" t="str">
         <v>SNL</v>
@@ -2120,22 +2120,22 @@
         <v>1</v>
       </c>
       <c r="J37" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K37" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L37">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M37">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N37">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
       <c r="O37" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="38">
@@ -2143,16 +2143,16 @@
         <v>847</v>
       </c>
       <c r="B38" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C38" t="str">
         <v>Blouse</v>
       </c>
       <c r="D38" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E38" t="str">
-        <v>Button attach (3 buttons)</v>
+        <v>Button hole marking &amp; sewing</v>
       </c>
       <c r="F38" t="str">
         <v>SNL</v>
@@ -2167,22 +2167,22 @@
         <v>1</v>
       </c>
       <c r="J38" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K38" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L38">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M38">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N38">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O38" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="39">
@@ -2190,16 +2190,16 @@
         <v>847</v>
       </c>
       <c r="B39" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C39" t="str">
         <v>Blouse</v>
       </c>
       <c r="D39" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E39" t="str">
-        <v>Final pressing body</v>
+        <v>Top pressing full garment</v>
       </c>
       <c r="F39" t="str">
         <v>VIR</v>
@@ -2214,22 +2214,22 @@
         <v>1</v>
       </c>
       <c r="J39" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K39" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L39">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M39">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N39">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="O39" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="40">
@@ -2237,16 +2237,16 @@
         <v>847</v>
       </c>
       <c r="B40" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C40" t="str">
         <v>Blouse</v>
       </c>
       <c r="D40" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E40" t="str">
-        <v>Press collar &amp; cuff</v>
+        <v>Press yoke &amp; collar area</v>
       </c>
       <c r="F40" t="str">
         <v>VIR</v>
@@ -2261,22 +2261,22 @@
         <v>1</v>
       </c>
       <c r="J40" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K40" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L40">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M40">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N40">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="O40" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="41">
@@ -2284,16 +2284,16 @@
         <v>847</v>
       </c>
       <c r="B41" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C41" t="str">
         <v>Blouse</v>
       </c>
       <c r="D41" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E41" t="str">
-        <v>Attach main label manual</v>
+        <v>Label attach &amp; size sticker</v>
       </c>
       <c r="F41" t="str">
         <v>HELP</v>
@@ -2308,22 +2308,22 @@
         <v>1</v>
       </c>
       <c r="J41" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K41" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L41">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M41">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N41">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O41" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="42">
@@ -2331,16 +2331,16 @@
         <v>847</v>
       </c>
       <c r="B42" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C42" t="str">
         <v>Blouse</v>
       </c>
       <c r="D42" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E42" t="str">
-        <v>Hang tag attach &amp; fold</v>
+        <v>Measurement checking</v>
       </c>
       <c r="F42" t="str">
         <v>HELP</v>
@@ -2355,22 +2355,22 @@
         <v>1</v>
       </c>
       <c r="J42" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K42" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L42">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M42">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N42">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="O42" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="43">
@@ -2378,16 +2378,16 @@
         <v>847</v>
       </c>
       <c r="B43" t="str">
-        <v>4461T::BL</v>
+        <v>9676T::BL</v>
       </c>
       <c r="C43" t="str">
         <v>Blouse</v>
       </c>
       <c r="D43" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E43" t="str">
-        <v>Poly bag &amp; pack into carton</v>
+        <v>Folding, hang tag &amp; polybag</v>
       </c>
       <c r="F43" t="str">
         <v>HELP</v>
@@ -2402,22 +2402,22 @@
         <v>1</v>
       </c>
       <c r="J43" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K43" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-22</v>
       </c>
       <c r="L43">
-        <v>646</v>
+        <v>694</v>
       </c>
       <c r="M43">
-        <v>16.15</v>
+        <v>18.7</v>
       </c>
       <c r="N43">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="O43" t="str">
-        <v>mudithaj</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="44">
@@ -2431,7 +2431,7 @@
         <v>Blouse</v>
       </c>
       <c r="D44" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E44" t="str">
         <v>Attach front yoke to body</v>
@@ -2449,10 +2449,10 @@
         <v>1</v>
       </c>
       <c r="J44" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K44" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L44">
         <v>694</v>
@@ -2478,7 +2478,7 @@
         <v>Blouse</v>
       </c>
       <c r="D45" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E45" t="str">
         <v>Attach collar band</v>
@@ -2496,10 +2496,10 @@
         <v>1</v>
       </c>
       <c r="J45" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K45" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L45">
         <v>694</v>
@@ -2525,7 +2525,7 @@
         <v>Blouse</v>
       </c>
       <c r="D46" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E46" t="str">
         <v>Set sleeve with easing</v>
@@ -2543,10 +2543,10 @@
         <v>1</v>
       </c>
       <c r="J46" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K46" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L46">
         <v>694</v>
@@ -2572,7 +2572,7 @@
         <v>Blouse</v>
       </c>
       <c r="D47" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E47" t="str">
         <v>Join underarm seam</v>
@@ -2590,10 +2590,10 @@
         <v>1</v>
       </c>
       <c r="J47" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K47" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L47">
         <v>694</v>
@@ -2619,7 +2619,7 @@
         <v>Blouse</v>
       </c>
       <c r="D48" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E48" t="str">
         <v>Overlock armhole edge</v>
@@ -2637,10 +2637,10 @@
         <v>1</v>
       </c>
       <c r="J48" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K48" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L48">
         <v>694</v>
@@ -2666,7 +2666,7 @@
         <v>Blouse</v>
       </c>
       <c r="D49" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E49" t="str">
         <v>Hem sleeve &amp; body</v>
@@ -2684,10 +2684,10 @@
         <v>1</v>
       </c>
       <c r="J49" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K49" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L49">
         <v>694</v>
@@ -2713,7 +2713,7 @@
         <v>Blouse</v>
       </c>
       <c r="D50" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E50" t="str">
         <v>Attach lining to facing</v>
@@ -2731,10 +2731,10 @@
         <v>1</v>
       </c>
       <c r="J50" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K50" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L50">
         <v>694</v>
@@ -2760,7 +2760,7 @@
         <v>Blouse</v>
       </c>
       <c r="D51" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E51" t="str">
         <v>Thread trimming &amp; spot cleaning</v>
@@ -2778,10 +2778,10 @@
         <v>1</v>
       </c>
       <c r="J51" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K51" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L51">
         <v>694</v>
@@ -2807,7 +2807,7 @@
         <v>Blouse</v>
       </c>
       <c r="D52" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E52" t="str">
         <v>Button hole marking &amp; sewing</v>
@@ -2825,10 +2825,10 @@
         <v>1</v>
       </c>
       <c r="J52" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K52" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L52">
         <v>694</v>
@@ -2854,7 +2854,7 @@
         <v>Blouse</v>
       </c>
       <c r="D53" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E53" t="str">
         <v>Top pressing full garment</v>
@@ -2872,10 +2872,10 @@
         <v>1</v>
       </c>
       <c r="J53" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K53" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L53">
         <v>694</v>
@@ -2901,7 +2901,7 @@
         <v>Blouse</v>
       </c>
       <c r="D54" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E54" t="str">
         <v>Press yoke &amp; collar area</v>
@@ -2919,10 +2919,10 @@
         <v>1</v>
       </c>
       <c r="J54" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K54" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L54">
         <v>694</v>
@@ -2948,7 +2948,7 @@
         <v>Blouse</v>
       </c>
       <c r="D55" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E55" t="str">
         <v>Label attach &amp; size sticker</v>
@@ -2966,10 +2966,10 @@
         <v>1</v>
       </c>
       <c r="J55" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K55" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L55">
         <v>694</v>
@@ -2995,7 +2995,7 @@
         <v>Blouse</v>
       </c>
       <c r="D56" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E56" t="str">
         <v>Measurement checking</v>
@@ -3013,10 +3013,10 @@
         <v>1</v>
       </c>
       <c r="J56" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K56" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L56">
         <v>694</v>
@@ -3042,7 +3042,7 @@
         <v>Blouse</v>
       </c>
       <c r="D57" t="str">
-        <v>BL::AU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E57" t="str">
         <v>Folding, hang tag &amp; polybag</v>
@@ -3060,10 +3060,10 @@
         <v>1</v>
       </c>
       <c r="J57" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-23</v>
       </c>
       <c r="K57" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-26</v>
       </c>
       <c r="L57">
         <v>694</v>
@@ -3089,7 +3089,7 @@
         <v>Blouse</v>
       </c>
       <c r="D58" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E58" t="str">
         <v>Attach front yoke to body</v>
@@ -3107,10 +3107,10 @@
         <v>1</v>
       </c>
       <c r="J58" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K58" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L58">
         <v>694</v>
@@ -3136,7 +3136,7 @@
         <v>Blouse</v>
       </c>
       <c r="D59" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E59" t="str">
         <v>Attach collar band</v>
@@ -3154,10 +3154,10 @@
         <v>1</v>
       </c>
       <c r="J59" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K59" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L59">
         <v>694</v>
@@ -3183,7 +3183,7 @@
         <v>Blouse</v>
       </c>
       <c r="D60" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E60" t="str">
         <v>Set sleeve with easing</v>
@@ -3201,10 +3201,10 @@
         <v>1</v>
       </c>
       <c r="J60" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K60" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L60">
         <v>694</v>
@@ -3230,7 +3230,7 @@
         <v>Blouse</v>
       </c>
       <c r="D61" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E61" t="str">
         <v>Join underarm seam</v>
@@ -3248,10 +3248,10 @@
         <v>1</v>
       </c>
       <c r="J61" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K61" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L61">
         <v>694</v>
@@ -3277,7 +3277,7 @@
         <v>Blouse</v>
       </c>
       <c r="D62" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E62" t="str">
         <v>Overlock armhole edge</v>
@@ -3295,10 +3295,10 @@
         <v>1</v>
       </c>
       <c r="J62" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K62" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L62">
         <v>694</v>
@@ -3324,7 +3324,7 @@
         <v>Blouse</v>
       </c>
       <c r="D63" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E63" t="str">
         <v>Hem sleeve &amp; body</v>
@@ -3342,10 +3342,10 @@
         <v>1</v>
       </c>
       <c r="J63" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K63" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L63">
         <v>694</v>
@@ -3371,7 +3371,7 @@
         <v>Blouse</v>
       </c>
       <c r="D64" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E64" t="str">
         <v>Attach lining to facing</v>
@@ -3389,10 +3389,10 @@
         <v>1</v>
       </c>
       <c r="J64" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K64" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L64">
         <v>694</v>
@@ -3418,7 +3418,7 @@
         <v>Blouse</v>
       </c>
       <c r="D65" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E65" t="str">
         <v>Thread trimming &amp; spot cleaning</v>
@@ -3436,10 +3436,10 @@
         <v>1</v>
       </c>
       <c r="J65" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K65" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L65">
         <v>694</v>
@@ -3465,7 +3465,7 @@
         <v>Blouse</v>
       </c>
       <c r="D66" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E66" t="str">
         <v>Button hole marking &amp; sewing</v>
@@ -3483,10 +3483,10 @@
         <v>1</v>
       </c>
       <c r="J66" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K66" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L66">
         <v>694</v>
@@ -3512,7 +3512,7 @@
         <v>Blouse</v>
       </c>
       <c r="D67" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E67" t="str">
         <v>Top pressing full garment</v>
@@ -3530,10 +3530,10 @@
         <v>1</v>
       </c>
       <c r="J67" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K67" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L67">
         <v>694</v>
@@ -3559,7 +3559,7 @@
         <v>Blouse</v>
       </c>
       <c r="D68" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E68" t="str">
         <v>Press yoke &amp; collar area</v>
@@ -3577,10 +3577,10 @@
         <v>1</v>
       </c>
       <c r="J68" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K68" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L68">
         <v>694</v>
@@ -3606,7 +3606,7 @@
         <v>Blouse</v>
       </c>
       <c r="D69" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E69" t="str">
         <v>Label attach &amp; size sticker</v>
@@ -3624,10 +3624,10 @@
         <v>1</v>
       </c>
       <c r="J69" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K69" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L69">
         <v>694</v>
@@ -3653,7 +3653,7 @@
         <v>Blouse</v>
       </c>
       <c r="D70" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E70" t="str">
         <v>Measurement checking</v>
@@ -3671,10 +3671,10 @@
         <v>1</v>
       </c>
       <c r="J70" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K70" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L70">
         <v>694</v>
@@ -3700,7 +3700,7 @@
         <v>Blouse</v>
       </c>
       <c r="D71" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E71" t="str">
         <v>Folding, hang tag &amp; polybag</v>
@@ -3718,10 +3718,10 @@
         <v>1</v>
       </c>
       <c r="J71" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-27</v>
       </c>
       <c r="K71" t="str">
-        <v>2026-05-26</v>
+        <v>2026-05-29</v>
       </c>
       <c r="L71">
         <v>694</v>
@@ -3738,19 +3738,19 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B72" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C72" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D72" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E72" t="str">
-        <v>Attach front yoke to body</v>
+        <v>Attach waistband to body</v>
       </c>
       <c r="F72" t="str">
         <v>SNL</v>
@@ -3765,39 +3765,39 @@
         <v>1</v>
       </c>
       <c r="J72" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K72" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L72">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M72">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N72">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="O72" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B73" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C73" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D73" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E73" t="str">
-        <v>Attach collar band</v>
+        <v>Join inseam stitch</v>
       </c>
       <c r="F73" t="str">
         <v>SNL</v>
@@ -3812,42 +3812,42 @@
         <v>1</v>
       </c>
       <c r="J73" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K73" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L73">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M73">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N73">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O73" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B74" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C74" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D74" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E74" t="str">
-        <v>Set sleeve with easing</v>
+        <v>Join outseam overlock</v>
       </c>
       <c r="F74" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G74" t="str">
         <v>Sewing</v>
@@ -3859,42 +3859,42 @@
         <v>1</v>
       </c>
       <c r="J74" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K74" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L74">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M74">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N74">
-        <v>1.8</v>
+        <v>0.75</v>
       </c>
       <c r="O74" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B75" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C75" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D75" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E75" t="str">
-        <v>Join underarm seam</v>
+        <v>Attach fly facing</v>
       </c>
       <c r="F75" t="str">
-        <v>SNL-SS</v>
+        <v>SNL</v>
       </c>
       <c r="G75" t="str">
         <v>Sewing</v>
@@ -3906,42 +3906,42 @@
         <v>1</v>
       </c>
       <c r="J75" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K75" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L75">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M75">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N75">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="O75" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B76" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C76" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D76" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E76" t="str">
-        <v>Overlock armhole edge</v>
+        <v>Hem bottom leg edge</v>
       </c>
       <c r="F76" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G76" t="str">
         <v>Sewing</v>
@@ -3953,42 +3953,42 @@
         <v>1</v>
       </c>
       <c r="J76" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K76" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L76">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M76">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N76">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="O76" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B77" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C77" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D77" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E77" t="str">
-        <v>Hem sleeve &amp; body</v>
+        <v>Bartack at stress points</v>
       </c>
       <c r="F77" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G77" t="str">
         <v>Sewing</v>
@@ -4000,42 +4000,42 @@
         <v>1</v>
       </c>
       <c r="J77" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K77" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L77">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M77">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N77">
-        <v>0.85</v>
+        <v>0.5</v>
       </c>
       <c r="O77" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B78" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C78" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D78" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E78" t="str">
-        <v>Attach lining to facing</v>
+        <v>Attach hook &amp; bar to w/b</v>
       </c>
       <c r="F78" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G78" t="str">
         <v>Sewing</v>
@@ -4047,39 +4047,39 @@
         <v>1</v>
       </c>
       <c r="J78" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K78" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L78">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M78">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N78">
-        <v>1.05</v>
+        <v>0.3</v>
       </c>
       <c r="O78" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B79" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C79" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D79" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E79" t="str">
-        <v>Thread trimming &amp; spot cleaning</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F79" t="str">
         <v>SNL</v>
@@ -4094,42 +4094,42 @@
         <v>1</v>
       </c>
       <c r="J79" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K79" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L79">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M79">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N79">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="O79" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B80" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C80" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D80" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E80" t="str">
-        <v>Button hole marking &amp; sewing</v>
+        <v>Press crease on legs</v>
       </c>
       <c r="F80" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G80" t="str">
         <v>Finishing</v>
@@ -4141,39 +4141,39 @@
         <v>1</v>
       </c>
       <c r="J80" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K80" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L80">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M80">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N80">
-        <v>1.6</v>
+        <v>2</v>
       </c>
       <c r="O80" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B81" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C81" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D81" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E81" t="str">
-        <v>Top pressing full garment</v>
+        <v>Final press waistband &amp; seams</v>
       </c>
       <c r="F81" t="str">
         <v>VIR</v>
@@ -4188,42 +4188,42 @@
         <v>1</v>
       </c>
       <c r="J81" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K81" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L81">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M81">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N81">
-        <v>3</v>
+        <v>1.8</v>
       </c>
       <c r="O81" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B82" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C82" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D82" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E82" t="str">
-        <v>Press yoke &amp; collar area</v>
+        <v>Attach main label manual</v>
       </c>
       <c r="F82" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G82" t="str">
         <v>Finishing</v>
@@ -4235,39 +4235,39 @@
         <v>1</v>
       </c>
       <c r="J82" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K82" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L82">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M82">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N82">
-        <v>1.4</v>
+        <v>0.7</v>
       </c>
       <c r="O82" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B83" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C83" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D83" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E83" t="str">
-        <v>Label attach &amp; size sticker</v>
+        <v>Hang tag attach &amp; fold</v>
       </c>
       <c r="F83" t="str">
         <v>HELP</v>
@@ -4282,39 +4282,39 @@
         <v>1</v>
       </c>
       <c r="J83" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K83" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L83">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M83">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N83">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O83" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B84" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C84" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D84" t="str">
-        <v>BL::US RT</v>
+        <v>PN::AU RT</v>
       </c>
       <c r="E84" t="str">
-        <v>Measurement checking</v>
+        <v>Poly bag &amp; pack carton</v>
       </c>
       <c r="F84" t="str">
         <v>HELP</v>
@@ -4329,45 +4329,45 @@
         <v>1</v>
       </c>
       <c r="J84" t="str">
-        <v>2026-05-27</v>
+        <v>2026-05-30</v>
       </c>
       <c r="K84" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L84">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M84">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N84">
         <v>1</v>
       </c>
       <c r="O84" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B85" t="str">
-        <v>9676T::BL</v>
+        <v>1111P/R1::PN</v>
       </c>
       <c r="C85" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D85" t="str">
-        <v>BL::US RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E85" t="str">
-        <v>Folding, hang tag &amp; polybag</v>
+        <v>Attach waistband to body</v>
       </c>
       <c r="F85" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G85" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H85" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -4376,22 +4376,22 @@
         <v>1</v>
       </c>
       <c r="J85" t="str">
-        <v>2026-05-27</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K85" t="str">
-        <v>2026-05-29</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L85">
-        <v>694</v>
+        <v>641</v>
       </c>
       <c r="M85">
-        <v>18.7</v>
+        <v>12.95</v>
       </c>
       <c r="N85">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O85" t="str">
-        <v>kamalag</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="86">
@@ -4405,10 +4405,10 @@
         <v>Pant</v>
       </c>
       <c r="D86" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E86" t="str">
-        <v>Attach waistband to body</v>
+        <v>Join inseam stitch</v>
       </c>
       <c r="F86" t="str">
         <v>SNL</v>
@@ -4423,10 +4423,10 @@
         <v>1</v>
       </c>
       <c r="J86" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K86" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L86">
         <v>641</v>
@@ -4435,7 +4435,7 @@
         <v>12.95</v>
       </c>
       <c r="N86">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O86" t="str">
         <v>sasanthar</v>
@@ -4452,13 +4452,13 @@
         <v>Pant</v>
       </c>
       <c r="D87" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E87" t="str">
-        <v>Join inseam stitch</v>
+        <v>Join outseam overlock</v>
       </c>
       <c r="F87" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G87" t="str">
         <v>Sewing</v>
@@ -4470,10 +4470,10 @@
         <v>1</v>
       </c>
       <c r="J87" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K87" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L87">
         <v>641</v>
@@ -4482,7 +4482,7 @@
         <v>12.95</v>
       </c>
       <c r="N87">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="O87" t="str">
         <v>sasanthar</v>
@@ -4499,13 +4499,13 @@
         <v>Pant</v>
       </c>
       <c r="D88" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E88" t="str">
-        <v>Join outseam overlock</v>
+        <v>Attach fly facing</v>
       </c>
       <c r="F88" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G88" t="str">
         <v>Sewing</v>
@@ -4517,10 +4517,10 @@
         <v>1</v>
       </c>
       <c r="J88" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K88" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L88">
         <v>641</v>
@@ -4529,7 +4529,7 @@
         <v>12.95</v>
       </c>
       <c r="N88">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O88" t="str">
         <v>sasanthar</v>
@@ -4546,10 +4546,10 @@
         <v>Pant</v>
       </c>
       <c r="D89" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E89" t="str">
-        <v>Attach fly facing</v>
+        <v>Hem bottom leg edge</v>
       </c>
       <c r="F89" t="str">
         <v>SNL</v>
@@ -4564,10 +4564,10 @@
         <v>1</v>
       </c>
       <c r="J89" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K89" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L89">
         <v>641</v>
@@ -4576,7 +4576,7 @@
         <v>12.95</v>
       </c>
       <c r="N89">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O89" t="str">
         <v>sasanthar</v>
@@ -4593,13 +4593,13 @@
         <v>Pant</v>
       </c>
       <c r="D90" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E90" t="str">
-        <v>Hem bottom leg edge</v>
+        <v>Bartack at stress points</v>
       </c>
       <c r="F90" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G90" t="str">
         <v>Sewing</v>
@@ -4611,10 +4611,10 @@
         <v>1</v>
       </c>
       <c r="J90" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K90" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L90">
         <v>641</v>
@@ -4623,7 +4623,7 @@
         <v>12.95</v>
       </c>
       <c r="N90">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="O90" t="str">
         <v>sasanthar</v>
@@ -4640,13 +4640,13 @@
         <v>Pant</v>
       </c>
       <c r="D91" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E91" t="str">
-        <v>Bartack at stress points</v>
+        <v>Attach hook &amp; bar to w/b</v>
       </c>
       <c r="F91" t="str">
-        <v>ASNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G91" t="str">
         <v>Sewing</v>
@@ -4658,10 +4658,10 @@
         <v>1</v>
       </c>
       <c r="J91" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K91" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L91">
         <v>641</v>
@@ -4670,7 +4670,7 @@
         <v>12.95</v>
       </c>
       <c r="N91">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O91" t="str">
         <v>sasanthar</v>
@@ -4687,16 +4687,16 @@
         <v>Pant</v>
       </c>
       <c r="D92" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E92" t="str">
-        <v>Attach hook &amp; bar to w/b</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F92" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G92" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H92" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -4705,10 +4705,10 @@
         <v>1</v>
       </c>
       <c r="J92" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K92" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L92">
         <v>641</v>
@@ -4717,7 +4717,7 @@
         <v>12.95</v>
       </c>
       <c r="N92">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="O92" t="str">
         <v>sasanthar</v>
@@ -4734,13 +4734,13 @@
         <v>Pant</v>
       </c>
       <c r="D93" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E93" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Press crease on legs</v>
       </c>
       <c r="F93" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G93" t="str">
         <v>Finishing</v>
@@ -4752,10 +4752,10 @@
         <v>1</v>
       </c>
       <c r="J93" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K93" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L93">
         <v>641</v>
@@ -4764,7 +4764,7 @@
         <v>12.95</v>
       </c>
       <c r="N93">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O93" t="str">
         <v>sasanthar</v>
@@ -4781,10 +4781,10 @@
         <v>Pant</v>
       </c>
       <c r="D94" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E94" t="str">
-        <v>Press crease on legs</v>
+        <v>Final press waistband &amp; seams</v>
       </c>
       <c r="F94" t="str">
         <v>VIR</v>
@@ -4799,10 +4799,10 @@
         <v>1</v>
       </c>
       <c r="J94" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K94" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L94">
         <v>641</v>
@@ -4811,7 +4811,7 @@
         <v>12.95</v>
       </c>
       <c r="N94">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O94" t="str">
         <v>sasanthar</v>
@@ -4828,13 +4828,13 @@
         <v>Pant</v>
       </c>
       <c r="D95" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E95" t="str">
-        <v>Final press waistband &amp; seams</v>
+        <v>Attach main label manual</v>
       </c>
       <c r="F95" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G95" t="str">
         <v>Finishing</v>
@@ -4846,10 +4846,10 @@
         <v>1</v>
       </c>
       <c r="J95" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K95" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L95">
         <v>641</v>
@@ -4858,7 +4858,7 @@
         <v>12.95</v>
       </c>
       <c r="N95">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="O95" t="str">
         <v>sasanthar</v>
@@ -4875,10 +4875,10 @@
         <v>Pant</v>
       </c>
       <c r="D96" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E96" t="str">
-        <v>Attach main label manual</v>
+        <v>Hang tag attach &amp; fold</v>
       </c>
       <c r="F96" t="str">
         <v>HELP</v>
@@ -4893,10 +4893,10 @@
         <v>1</v>
       </c>
       <c r="J96" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K96" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L96">
         <v>641</v>
@@ -4905,7 +4905,7 @@
         <v>12.95</v>
       </c>
       <c r="N96">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O96" t="str">
         <v>sasanthar</v>
@@ -4922,10 +4922,10 @@
         <v>Pant</v>
       </c>
       <c r="D97" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E97" t="str">
-        <v>Hang tag attach &amp; fold</v>
+        <v>Poly bag &amp; pack carton</v>
       </c>
       <c r="F97" t="str">
         <v>HELP</v>
@@ -4940,10 +4940,10 @@
         <v>1</v>
       </c>
       <c r="J97" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K97" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L97">
         <v>641</v>
@@ -4952,7 +4952,7 @@
         <v>12.95</v>
       </c>
       <c r="N97">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O97" t="str">
         <v>sasanthar</v>
@@ -4969,16 +4969,16 @@
         <v>Pant</v>
       </c>
       <c r="D98" t="str">
-        <v>PN::AU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E98" t="str">
-        <v>Poly bag &amp; pack carton</v>
+        <v>Attach waistband to body</v>
       </c>
       <c r="F98" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G98" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H98" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -4987,10 +4987,10 @@
         <v>1</v>
       </c>
       <c r="J98" t="str">
-        <v>2026-05-30</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K98" t="str">
-        <v>2026-06-02</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L98">
         <v>641</v>
@@ -4999,7 +4999,7 @@
         <v>12.95</v>
       </c>
       <c r="N98">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O98" t="str">
         <v>sasanthar</v>
@@ -5016,10 +5016,10 @@
         <v>Pant</v>
       </c>
       <c r="D99" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E99" t="str">
-        <v>Attach waistband to body</v>
+        <v>Join inseam stitch</v>
       </c>
       <c r="F99" t="str">
         <v>SNL</v>
@@ -5034,10 +5034,10 @@
         <v>1</v>
       </c>
       <c r="J99" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K99" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L99">
         <v>641</v>
@@ -5046,7 +5046,7 @@
         <v>12.95</v>
       </c>
       <c r="N99">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O99" t="str">
         <v>sasanthar</v>
@@ -5063,13 +5063,13 @@
         <v>Pant</v>
       </c>
       <c r="D100" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E100" t="str">
-        <v>Join inseam stitch</v>
+        <v>Join outseam overlock</v>
       </c>
       <c r="F100" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G100" t="str">
         <v>Sewing</v>
@@ -5081,10 +5081,10 @@
         <v>1</v>
       </c>
       <c r="J100" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K100" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L100">
         <v>641</v>
@@ -5093,7 +5093,7 @@
         <v>12.95</v>
       </c>
       <c r="N100">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="O100" t="str">
         <v>sasanthar</v>
@@ -5110,13 +5110,13 @@
         <v>Pant</v>
       </c>
       <c r="D101" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E101" t="str">
-        <v>Join outseam overlock</v>
+        <v>Attach fly facing</v>
       </c>
       <c r="F101" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G101" t="str">
         <v>Sewing</v>
@@ -5128,10 +5128,10 @@
         <v>1</v>
       </c>
       <c r="J101" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K101" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L101">
         <v>641</v>
@@ -5140,7 +5140,7 @@
         <v>12.95</v>
       </c>
       <c r="N101">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O101" t="str">
         <v>sasanthar</v>
@@ -5157,10 +5157,10 @@
         <v>Pant</v>
       </c>
       <c r="D102" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E102" t="str">
-        <v>Attach fly facing</v>
+        <v>Hem bottom leg edge</v>
       </c>
       <c r="F102" t="str">
         <v>SNL</v>
@@ -5175,10 +5175,10 @@
         <v>1</v>
       </c>
       <c r="J102" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K102" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L102">
         <v>641</v>
@@ -5187,7 +5187,7 @@
         <v>12.95</v>
       </c>
       <c r="N102">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O102" t="str">
         <v>sasanthar</v>
@@ -5204,13 +5204,13 @@
         <v>Pant</v>
       </c>
       <c r="D103" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E103" t="str">
-        <v>Hem bottom leg edge</v>
+        <v>Bartack at stress points</v>
       </c>
       <c r="F103" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G103" t="str">
         <v>Sewing</v>
@@ -5222,10 +5222,10 @@
         <v>1</v>
       </c>
       <c r="J103" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K103" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L103">
         <v>641</v>
@@ -5234,7 +5234,7 @@
         <v>12.95</v>
       </c>
       <c r="N103">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="O103" t="str">
         <v>sasanthar</v>
@@ -5251,13 +5251,13 @@
         <v>Pant</v>
       </c>
       <c r="D104" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E104" t="str">
-        <v>Bartack at stress points</v>
+        <v>Attach hook &amp; bar to w/b</v>
       </c>
       <c r="F104" t="str">
-        <v>ASNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G104" t="str">
         <v>Sewing</v>
@@ -5269,10 +5269,10 @@
         <v>1</v>
       </c>
       <c r="J104" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K104" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L104">
         <v>641</v>
@@ -5281,7 +5281,7 @@
         <v>12.95</v>
       </c>
       <c r="N104">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="O104" t="str">
         <v>sasanthar</v>
@@ -5298,16 +5298,16 @@
         <v>Pant</v>
       </c>
       <c r="D105" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E105" t="str">
-        <v>Attach hook &amp; bar to w/b</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F105" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G105" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H105" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -5316,10 +5316,10 @@
         <v>1</v>
       </c>
       <c r="J105" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K105" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L105">
         <v>641</v>
@@ -5328,7 +5328,7 @@
         <v>12.95</v>
       </c>
       <c r="N105">
-        <v>0.3</v>
+        <v>1.5</v>
       </c>
       <c r="O105" t="str">
         <v>sasanthar</v>
@@ -5345,13 +5345,13 @@
         <v>Pant</v>
       </c>
       <c r="D106" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E106" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Press crease on legs</v>
       </c>
       <c r="F106" t="str">
-        <v>SNL</v>
+        <v>VIR</v>
       </c>
       <c r="G106" t="str">
         <v>Finishing</v>
@@ -5363,10 +5363,10 @@
         <v>1</v>
       </c>
       <c r="J106" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K106" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L106">
         <v>641</v>
@@ -5375,7 +5375,7 @@
         <v>12.95</v>
       </c>
       <c r="N106">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O106" t="str">
         <v>sasanthar</v>
@@ -5392,10 +5392,10 @@
         <v>Pant</v>
       </c>
       <c r="D107" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E107" t="str">
-        <v>Press crease on legs</v>
+        <v>Final press waistband &amp; seams</v>
       </c>
       <c r="F107" t="str">
         <v>VIR</v>
@@ -5410,10 +5410,10 @@
         <v>1</v>
       </c>
       <c r="J107" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K107" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L107">
         <v>641</v>
@@ -5422,7 +5422,7 @@
         <v>12.95</v>
       </c>
       <c r="N107">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O107" t="str">
         <v>sasanthar</v>
@@ -5439,13 +5439,13 @@
         <v>Pant</v>
       </c>
       <c r="D108" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E108" t="str">
-        <v>Final press waistband &amp; seams</v>
+        <v>Attach main label manual</v>
       </c>
       <c r="F108" t="str">
-        <v>VIR</v>
+        <v>HELP</v>
       </c>
       <c r="G108" t="str">
         <v>Finishing</v>
@@ -5457,10 +5457,10 @@
         <v>1</v>
       </c>
       <c r="J108" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K108" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L108">
         <v>641</v>
@@ -5469,7 +5469,7 @@
         <v>12.95</v>
       </c>
       <c r="N108">
-        <v>1.8</v>
+        <v>0.7</v>
       </c>
       <c r="O108" t="str">
         <v>sasanthar</v>
@@ -5486,10 +5486,10 @@
         <v>Pant</v>
       </c>
       <c r="D109" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E109" t="str">
-        <v>Attach main label manual</v>
+        <v>Hang tag attach &amp; fold</v>
       </c>
       <c r="F109" t="str">
         <v>HELP</v>
@@ -5504,10 +5504,10 @@
         <v>1</v>
       </c>
       <c r="J109" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K109" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L109">
         <v>641</v>
@@ -5516,7 +5516,7 @@
         <v>12.95</v>
       </c>
       <c r="N109">
-        <v>0.7</v>
+        <v>0.85</v>
       </c>
       <c r="O109" t="str">
         <v>sasanthar</v>
@@ -5533,10 +5533,10 @@
         <v>Pant</v>
       </c>
       <c r="D110" t="str">
-        <v>PN::EU RT</v>
+        <v>PN::US RT</v>
       </c>
       <c r="E110" t="str">
-        <v>Hang tag attach &amp; fold</v>
+        <v>Poly bag &amp; pack carton</v>
       </c>
       <c r="F110" t="str">
         <v>HELP</v>
@@ -5551,10 +5551,10 @@
         <v>1</v>
       </c>
       <c r="J110" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K110" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L110">
         <v>641</v>
@@ -5563,7 +5563,7 @@
         <v>12.95</v>
       </c>
       <c r="N110">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O110" t="str">
         <v>sasanthar</v>
@@ -5571,66 +5571,66 @@
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B111" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C111" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D111" t="str">
-        <v>PN::EU RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E111" t="str">
-        <v>Poly bag &amp; pack carton</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F111" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G111" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H111" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J111" t="str">
-        <v>2026-06-03</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K111" t="str">
-        <v>2026-06-05</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L111">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M111">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N111">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="O111" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B112" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C112" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D112" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E112" t="str">
-        <v>Attach waistband to body</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F112" t="str">
         <v>SNL</v>
@@ -5642,42 +5642,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I112">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J112" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K112" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L112">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M112">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N112">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O112" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B113" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C113" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D113" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E113" t="str">
-        <v>Join inseam stitch</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F113" t="str">
         <v>SNL</v>
@@ -5689,45 +5689,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I113">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J113" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K113" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L113">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M113">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N113">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="O113" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B114" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C114" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D114" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E114" t="str">
-        <v>Join outseam overlock</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F114" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G114" t="str">
         <v>Sewing</v>
@@ -5736,42 +5736,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I114">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J114" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K114" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L114">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M114">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N114">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="O114" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B115" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C115" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D115" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E115" t="str">
-        <v>Attach fly facing</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F115" t="str">
         <v>SNL</v>
@@ -5783,42 +5783,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K115" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L115">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M115">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N115">
-        <v>0.85</v>
+        <v>0.45</v>
       </c>
       <c r="O115" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B116" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C116" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D116" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E116" t="str">
-        <v>Hem bottom leg edge</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F116" t="str">
         <v>SNL</v>
@@ -5830,45 +5830,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I116">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J116" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K116" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L116">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M116">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N116">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="O116" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B117" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C117" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D117" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E117" t="str">
-        <v>Bartack at stress points</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F117" t="str">
-        <v>ASNL</v>
+        <v>SNL</v>
       </c>
       <c r="G117" t="str">
         <v>Sewing</v>
@@ -5877,42 +5877,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J117" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K117" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L117">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M117">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N117">
-        <v>0.5</v>
+        <v>0.61</v>
       </c>
       <c r="O117" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B118" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C118" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D118" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E118" t="str">
-        <v>Attach hook &amp; bar to w/b</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F118" t="str">
         <v>RM/L</v>
@@ -5924,39 +5924,39 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J118" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K118" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L118">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M118">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N118">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="O118" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B119" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C119" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D119" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E119" t="str">
         <v>Thread trimming full garment</v>
@@ -5971,45 +5971,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J119" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K119" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L119">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M119">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N119">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="O119" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B120" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C120" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D120" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E120" t="str">
-        <v>Press crease on legs</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F120" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G120" t="str">
         <v>Finishing</v>
@@ -6018,42 +6018,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120" t="str">
+        <v>2026-05-12</v>
+      </c>
+      <c r="K120" t="str">
+        <v>2026-05-14</v>
+      </c>
+      <c r="L120">
+        <v>646</v>
+      </c>
+      <c r="M120">
+        <v>15.28</v>
+      </c>
+      <c r="N120">
         <v>1</v>
       </c>
-      <c r="J120" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="K120" t="str">
-        <v>2026-06-09</v>
-      </c>
-      <c r="L120">
-        <v>641</v>
-      </c>
-      <c r="M120">
-        <v>12.95</v>
-      </c>
-      <c r="N120">
-        <v>2</v>
-      </c>
       <c r="O120" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B121" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C121" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D121" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E121" t="str">
-        <v>Final press waistband &amp; seams</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F121" t="str">
         <v>VIR</v>
@@ -6065,45 +6065,45 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J121" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K121" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L121">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M121">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N121">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="O121" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B122" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C122" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D122" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E122" t="str">
-        <v>Attach main label manual</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F122" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G122" t="str">
         <v>Finishing</v>
@@ -6112,42 +6112,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I122">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J122" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K122" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L122">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M122">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N122">
-        <v>0.7</v>
+        <v>2.5</v>
       </c>
       <c r="O122" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B123" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C123" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D123" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E123" t="str">
-        <v>Hang tag attach &amp; fold</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F123" t="str">
         <v>HELP</v>
@@ -6159,42 +6159,42 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J123" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K123" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L123">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M123">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N123">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="O123" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="B124" t="str">
-        <v>1111P/R1::PN</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C124" t="str">
-        <v>Pant</v>
+        <v>Shirt</v>
       </c>
       <c r="D124" t="str">
-        <v>PN::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E124" t="str">
-        <v>Poly bag &amp; pack carton</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F124" t="str">
         <v>HELP</v>
@@ -6206,25 +6206,25 @@
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I124">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J124" t="str">
-        <v>2026-06-06</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K124" t="str">
-        <v>2026-06-09</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L124">
-        <v>641</v>
+        <v>646</v>
       </c>
       <c r="M124">
-        <v>12.95</v>
+        <v>15.28</v>
       </c>
       <c r="N124">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O124" t="str">
-        <v>sasanthar</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="125">
@@ -6238,16 +6238,16 @@
         <v>Shirt</v>
       </c>
       <c r="D125" t="str">
-        <v>SH::US RT</v>
+        <v>SH::EU RT</v>
       </c>
       <c r="E125" t="str">
-        <v>Attach label 2 sides</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F125" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G125" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H125" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -6256,10 +6256,10 @@
         <v>2</v>
       </c>
       <c r="J125" t="str">
-        <v>2026-05-15</v>
+        <v>2026-05-12</v>
       </c>
       <c r="K125" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L125">
         <v>646</v>
@@ -6268,7 +6268,7 @@
         <v>15.28</v>
       </c>
       <c r="N125">
-        <v>0.25</v>
+        <v>1.1</v>
       </c>
       <c r="O125" t="str">
         <v>priyanthi</v>
@@ -6288,7 +6288,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E126" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Attach label 2 sides</v>
       </c>
       <c r="F126" t="str">
         <v>SNL</v>
@@ -6315,7 +6315,7 @@
         <v>15.28</v>
       </c>
       <c r="N126">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="O126" t="str">
         <v>priyanthi</v>
@@ -6335,7 +6335,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E127" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Attach binding @ in seam 2x2</v>
       </c>
       <c r="F127" t="str">
         <v>SNL</v>
@@ -6362,7 +6362,7 @@
         <v>15.28</v>
       </c>
       <c r="N127">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="O127" t="str">
         <v>priyanthi</v>
@@ -6382,7 +6382,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E128" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach bottom triangle</v>
       </c>
       <c r="F128" t="str">
         <v>SNL</v>
@@ -6409,7 +6409,7 @@
         <v>15.28</v>
       </c>
       <c r="N128">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="O128" t="str">
         <v>priyanthi</v>
@@ -6429,7 +6429,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E129" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach curve contour w/b</v>
       </c>
       <c r="F129" t="str">
         <v>SNL</v>
@@ -6456,7 +6456,7 @@
         <v>15.28</v>
       </c>
       <c r="N129">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="O129" t="str">
         <v>priyanthi</v>
@@ -6476,7 +6476,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E130" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach FLAP pocket</v>
       </c>
       <c r="F130" t="str">
         <v>SNL</v>
@@ -6503,7 +6503,7 @@
         <v>15.28</v>
       </c>
       <c r="N130">
-        <v>1.6</v>
+        <v>0.45</v>
       </c>
       <c r="O130" t="str">
         <v>priyanthi</v>
@@ -6523,7 +6523,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E131" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Attach hem facing to btm leg</v>
       </c>
       <c r="F131" t="str">
         <v>SNL</v>
@@ -6550,7 +6550,7 @@
         <v>15.28</v>
       </c>
       <c r="N131">
-        <v>0.61</v>
+        <v>1.6</v>
       </c>
       <c r="O131" t="str">
         <v>priyanthi</v>
@@ -6570,10 +6570,10 @@
         <v>SH::US RT</v>
       </c>
       <c r="E132" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Join zip nip + fly attach</v>
       </c>
       <c r="F132" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G132" t="str">
         <v>Sewing</v>
@@ -6597,7 +6597,7 @@
         <v>15.28</v>
       </c>
       <c r="N132">
-        <v>0.42</v>
+        <v>0.61</v>
       </c>
       <c r="O132" t="str">
         <v>priyanthi</v>
@@ -6617,13 +6617,13 @@
         <v>SH::US RT</v>
       </c>
       <c r="E133" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Mark &amp; attach bar to w/b</v>
       </c>
       <c r="F133" t="str">
-        <v>SNL</v>
+        <v>RM/L</v>
       </c>
       <c r="G133" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H133" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -6644,7 +6644,7 @@
         <v>15.28</v>
       </c>
       <c r="N133">
-        <v>1.6</v>
+        <v>0.42</v>
       </c>
       <c r="O133" t="str">
         <v>priyanthi</v>
@@ -6664,7 +6664,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E134" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F134" t="str">
         <v>SNL</v>
@@ -6691,7 +6691,7 @@
         <v>15.28</v>
       </c>
       <c r="N134">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O134" t="str">
         <v>priyanthi</v>
@@ -6711,10 +6711,10 @@
         <v>SH::US RT</v>
       </c>
       <c r="E135" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F135" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G135" t="str">
         <v>Finishing</v>
@@ -6738,7 +6738,7 @@
         <v>15.28</v>
       </c>
       <c r="N135">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O135" t="str">
         <v>priyanthi</v>
@@ -6758,7 +6758,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E136" t="str">
-        <v>Final press full shirt</v>
+        <v>Press waistband &amp; seam</v>
       </c>
       <c r="F136" t="str">
         <v>VIR</v>
@@ -6785,7 +6785,7 @@
         <v>15.28</v>
       </c>
       <c r="N136">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="O136" t="str">
         <v>priyanthi</v>
@@ -6805,10 +6805,10 @@
         <v>SH::US RT</v>
       </c>
       <c r="E137" t="str">
-        <v>Label attach manual</v>
+        <v>Final press full shirt</v>
       </c>
       <c r="F137" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G137" t="str">
         <v>Finishing</v>
@@ -6832,7 +6832,7 @@
         <v>15.28</v>
       </c>
       <c r="N137">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="O137" t="str">
         <v>priyanthi</v>
@@ -6852,7 +6852,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E138" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Label attach manual</v>
       </c>
       <c r="F138" t="str">
         <v>HELP</v>
@@ -6879,7 +6879,7 @@
         <v>15.28</v>
       </c>
       <c r="N138">
-        <v>0.9</v>
+        <v>0.75</v>
       </c>
       <c r="O138" t="str">
         <v>priyanthi</v>
@@ -6899,7 +6899,7 @@
         <v>SH::US RT</v>
       </c>
       <c r="E139" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F139" t="str">
         <v>HELP</v>
@@ -6926,7 +6926,7 @@
         <v>15.28</v>
       </c>
       <c r="N139">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O139" t="str">
         <v>priyanthi</v>
@@ -6934,25 +6934,25 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>847</v>
+        <v>935</v>
       </c>
       <c r="B140" t="str">
-        <v>6882T::BL</v>
+        <v>4462A::SH</v>
       </c>
       <c r="C140" t="str">
-        <v>Blouse</v>
+        <v>Shirt</v>
       </c>
       <c r="D140" t="str">
-        <v>BL::AU RT</v>
+        <v>SH::US RT</v>
       </c>
       <c r="E140" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Fold, bag &amp; carton pack</v>
       </c>
       <c r="F140" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G140" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H140" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -6961,22 +6961,22 @@
         <v>2</v>
       </c>
       <c r="J140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K140" t="str">
-        <v>2026-05-18</v>
+        <v>2026-05-16</v>
       </c>
       <c r="L140">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M140">
-        <v>17.96</v>
+        <v>15.28</v>
       </c>
       <c r="N140">
-        <v>0.43</v>
+        <v>1.1</v>
       </c>
       <c r="O140" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="141">
@@ -6993,7 +6993,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E141" t="str">
-        <v>Attach cuff</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F141" t="str">
         <v>SNL</v>
@@ -7020,7 +7020,7 @@
         <v>17.96</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O141" t="str">
         <v>mudithaj</v>
@@ -7040,7 +7040,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E142" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F142" t="str">
         <v>SNL</v>
@@ -7067,7 +7067,7 @@
         <v>17.96</v>
       </c>
       <c r="N142">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O142" t="str">
         <v>mudithaj</v>
@@ -7087,7 +7087,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E143" t="str">
-        <v>Attach sleeve</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F143" t="str">
         <v>SNL</v>
@@ -7114,7 +7114,7 @@
         <v>17.96</v>
       </c>
       <c r="N143">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O143" t="str">
         <v>mudithaj</v>
@@ -7134,7 +7134,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E144" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F144" t="str">
         <v>SNL</v>
@@ -7161,7 +7161,7 @@
         <v>17.96</v>
       </c>
       <c r="N144">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O144" t="str">
         <v>mudithaj</v>
@@ -7181,7 +7181,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E145" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F145" t="str">
         <v>SNL</v>
@@ -7208,7 +7208,7 @@
         <v>17.96</v>
       </c>
       <c r="N145">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O145" t="str">
         <v>mudithaj</v>
@@ -7228,10 +7228,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E146" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F146" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G146" t="str">
         <v>Sewing</v>
@@ -7255,7 +7255,7 @@
         <v>17.96</v>
       </c>
       <c r="N146">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O146" t="str">
         <v>mudithaj</v>
@@ -7275,13 +7275,13 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E147" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F147" t="str">
-        <v>SNL</v>
+        <v>SNLU</v>
       </c>
       <c r="G147" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H147" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7302,7 +7302,7 @@
         <v>17.96</v>
       </c>
       <c r="N147">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O147" t="str">
         <v>mudithaj</v>
@@ -7322,7 +7322,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E148" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F148" t="str">
         <v>SNL</v>
@@ -7349,7 +7349,7 @@
         <v>17.96</v>
       </c>
       <c r="N148">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O148" t="str">
         <v>mudithaj</v>
@@ -7369,10 +7369,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E149" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F149" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G149" t="str">
         <v>Finishing</v>
@@ -7416,7 +7416,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E150" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F150" t="str">
         <v>VIR</v>
@@ -7443,7 +7443,7 @@
         <v>17.96</v>
       </c>
       <c r="N150">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="O150" t="str">
         <v>mudithaj</v>
@@ -7463,10 +7463,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E151" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F151" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G151" t="str">
         <v>Finishing</v>
@@ -7490,7 +7490,7 @@
         <v>17.96</v>
       </c>
       <c r="N151">
-        <v>0.7</v>
+        <v>2.2</v>
       </c>
       <c r="O151" t="str">
         <v>mudithaj</v>
@@ -7510,7 +7510,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E152" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F152" t="str">
         <v>HELP</v>
@@ -7537,7 +7537,7 @@
         <v>17.96</v>
       </c>
       <c r="N152">
-        <v>0.85</v>
+        <v>0.7</v>
       </c>
       <c r="O152" t="str">
         <v>mudithaj</v>
@@ -7557,7 +7557,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E153" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F153" t="str">
         <v>HELP</v>
@@ -7584,7 +7584,7 @@
         <v>17.96</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O153" t="str">
         <v>mudithaj</v>
@@ -7592,25 +7592,25 @@
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B154" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C154" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D154" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E154" t="str">
-        <v>Attach waistband - curved</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F154" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G154" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H154" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7619,39 +7619,39 @@
         <v>2</v>
       </c>
       <c r="J154" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-18</v>
       </c>
       <c r="K154" t="str">
-        <v>2026-05-21</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L154">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M154">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N154">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O154" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B155" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C155" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D155" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E155" t="str">
-        <v>Join inseam double stitch</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F155" t="str">
         <v>SNL</v>
@@ -7672,36 +7672,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L155">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M155">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.43</v>
       </c>
       <c r="O155" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B156" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C156" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D156" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E156" t="str">
-        <v>Outseam overlock &amp; topstitch</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F156" t="str">
-        <v>3O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G156" t="str">
         <v>Sewing</v>
@@ -7719,36 +7719,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L156">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M156">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N156">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="O156" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B157" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C157" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D157" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E157" t="str">
-        <v>Attach zipper to fly</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F157" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G157" t="str">
         <v>Sewing</v>
@@ -7766,33 +7766,33 @@
         <v>2026-05-21</v>
       </c>
       <c r="L157">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M157">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N157">
-        <v>1.1</v>
+        <v>0.68</v>
       </c>
       <c r="O157" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B158" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C158" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D158" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E158" t="str">
-        <v>Hem bottom with blind stitch</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F158" t="str">
         <v>SNL</v>
@@ -7813,36 +7813,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L158">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M158">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N158">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="O158" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B159" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C159" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D159" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E159" t="str">
-        <v>Bartack pocket corners</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F159" t="str">
-        <v>ASNL</v>
+        <v>SNL</v>
       </c>
       <c r="G159" t="str">
         <v>Sewing</v>
@@ -7860,39 +7860,39 @@
         <v>2026-05-21</v>
       </c>
       <c r="L159">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M159">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N159">
-        <v>0.45</v>
+        <v>2</v>
       </c>
       <c r="O159" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B160" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C160" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D160" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E160" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F160" t="str">
         <v>SNL</v>
       </c>
       <c r="G160" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H160" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7907,39 +7907,39 @@
         <v>2026-05-21</v>
       </c>
       <c r="L160">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M160">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N160">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="O160" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B161" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C161" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D161" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E161" t="str">
-        <v>Press leg crease both sides</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F161" t="str">
-        <v>VIR</v>
+        <v>SNLU</v>
       </c>
       <c r="G161" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H161" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -7954,36 +7954,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L161">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M161">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N161">
-        <v>2.2</v>
+        <v>1</v>
       </c>
       <c r="O161" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B162" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C162" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D162" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E162" t="str">
-        <v>Final press &amp; steam waistband</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F162" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G162" t="str">
         <v>Finishing</v>
@@ -8001,36 +8001,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L162">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M162">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N162">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="O162" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B163" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C163" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D163" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E163" t="str">
-        <v>Attach main &amp; care label</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F163" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G163" t="str">
         <v>Finishing</v>
@@ -8048,36 +8048,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L163">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M163">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N163">
-        <v>0.75</v>
+        <v>1.8</v>
       </c>
       <c r="O163" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B164" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C164" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D164" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E164" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F164" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G164" t="str">
         <v>Finishing</v>
@@ -8095,36 +8095,36 @@
         <v>2026-05-21</v>
       </c>
       <c r="L164">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M164">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N164">
-        <v>0.9</v>
+        <v>1.8</v>
       </c>
       <c r="O164" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>910</v>
+        <v>847</v>
       </c>
       <c r="B165" t="str">
-        <v>3524P::PN</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C165" t="str">
-        <v>Pant</v>
+        <v>Blouse</v>
       </c>
       <c r="D165" t="str">
-        <v>PN::EU RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E165" t="str">
-        <v>Fold, board insert &amp; poly bag</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F165" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G165" t="str">
         <v>Finishing</v>
@@ -8142,16 +8142,16 @@
         <v>2026-05-21</v>
       </c>
       <c r="L165">
-        <v>1890</v>
+        <v>2190</v>
       </c>
       <c r="M165">
-        <v>14</v>
+        <v>17.96</v>
       </c>
       <c r="N165">
-        <v>1.05</v>
+        <v>2.2</v>
       </c>
       <c r="O165" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="166">
@@ -8165,16 +8165,16 @@
         <v>Blouse</v>
       </c>
       <c r="D166" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E166" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F166" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G166" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H166" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8183,10 +8183,10 @@
         <v>2</v>
       </c>
       <c r="J166" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K166" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L166">
         <v>2190</v>
@@ -8195,7 +8195,7 @@
         <v>17.96</v>
       </c>
       <c r="N166">
-        <v>0.43</v>
+        <v>0.7</v>
       </c>
       <c r="O166" t="str">
         <v>mudithaj</v>
@@ -8212,16 +8212,16 @@
         <v>Blouse</v>
       </c>
       <c r="D167" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E167" t="str">
-        <v>Attach cuff</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F167" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G167" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H167" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8230,10 +8230,10 @@
         <v>2</v>
       </c>
       <c r="J167" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K167" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L167">
         <v>2190</v>
@@ -8242,7 +8242,7 @@
         <v>17.96</v>
       </c>
       <c r="N167">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="O167" t="str">
         <v>mudithaj</v>
@@ -8259,16 +8259,16 @@
         <v>Blouse</v>
       </c>
       <c r="D168" t="str">
-        <v>BL::UK RT</v>
+        <v>BL::MX RT</v>
       </c>
       <c r="E168" t="str">
-        <v>Attach set band collar</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F168" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G168" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H168" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8277,10 +8277,10 @@
         <v>2</v>
       </c>
       <c r="J168" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-19</v>
       </c>
       <c r="K168" t="str">
-        <v>2026-05-23</v>
+        <v>2026-05-21</v>
       </c>
       <c r="L168">
         <v>2190</v>
@@ -8289,7 +8289,7 @@
         <v>17.96</v>
       </c>
       <c r="N168">
-        <v>0.68</v>
+        <v>1</v>
       </c>
       <c r="O168" t="str">
         <v>mudithaj</v>
@@ -8309,7 +8309,7 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E169" t="str">
-        <v>Attach sleeve</v>
+        <v>02 pc back yoke attach to back</v>
       </c>
       <c r="F169" t="str">
         <v>SNL</v>
@@ -8336,7 +8336,7 @@
         <v>17.96</v>
       </c>
       <c r="N169">
-        <v>1.5</v>
+        <v>0.43</v>
       </c>
       <c r="O169" t="str">
         <v>mudithaj</v>
@@ -8356,7 +8356,7 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E170" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Attach cuff</v>
       </c>
       <c r="F170" t="str">
         <v>SNL</v>
@@ -8383,7 +8383,7 @@
         <v>17.96</v>
       </c>
       <c r="N170">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O170" t="str">
         <v>mudithaj</v>
@@ -8403,7 +8403,7 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E171" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach set band collar</v>
       </c>
       <c r="F171" t="str">
         <v>SNL</v>
@@ -8430,7 +8430,7 @@
         <v>17.96</v>
       </c>
       <c r="N171">
-        <v>1.5</v>
+        <v>0.68</v>
       </c>
       <c r="O171" t="str">
         <v>mudithaj</v>
@@ -8450,10 +8450,10 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E172" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Attach sleeve</v>
       </c>
       <c r="F172" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G172" t="str">
         <v>Sewing</v>
@@ -8477,7 +8477,7 @@
         <v>17.96</v>
       </c>
       <c r="N172">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="O172" t="str">
         <v>mudithaj</v>
@@ -8497,13 +8497,13 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E173" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Attach thearraway to arm hole</v>
       </c>
       <c r="F173" t="str">
         <v>SNL</v>
       </c>
       <c r="G173" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H173" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8524,7 +8524,7 @@
         <v>17.96</v>
       </c>
       <c r="N173">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O173" t="str">
         <v>mudithaj</v>
@@ -8544,13 +8544,13 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E174" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Attach thearraway to hem</v>
       </c>
       <c r="F174" t="str">
         <v>SNL</v>
       </c>
       <c r="G174" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H174" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8571,7 +8571,7 @@
         <v>17.96</v>
       </c>
       <c r="N174">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="O174" t="str">
         <v>mudithaj</v>
@@ -8591,13 +8591,13 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E175" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Tag sleeve before attach</v>
       </c>
       <c r="F175" t="str">
-        <v>VIR</v>
+        <v>SNLU</v>
       </c>
       <c r="G175" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H175" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8618,7 +8618,7 @@
         <v>17.96</v>
       </c>
       <c r="N175">
-        <v>1.8</v>
+        <v>1</v>
       </c>
       <c r="O175" t="str">
         <v>mudithaj</v>
@@ -8638,10 +8638,10 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E176" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Thread trim &amp; broken stitch check</v>
       </c>
       <c r="F176" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G176" t="str">
         <v>Finishing</v>
@@ -8665,7 +8665,7 @@
         <v>17.96</v>
       </c>
       <c r="N176">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="O176" t="str">
         <v>mudithaj</v>
@@ -8685,10 +8685,10 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E177" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Button attach (5 buttons)</v>
       </c>
       <c r="F177" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G177" t="str">
         <v>Finishing</v>
@@ -8712,7 +8712,7 @@
         <v>17.96</v>
       </c>
       <c r="N177">
-        <v>0.7</v>
+        <v>1.8</v>
       </c>
       <c r="O177" t="str">
         <v>mudithaj</v>
@@ -8732,10 +8732,10 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E178" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Steam press collar &amp; cuff</v>
       </c>
       <c r="F178" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G178" t="str">
         <v>Finishing</v>
@@ -8759,7 +8759,7 @@
         <v>17.96</v>
       </c>
       <c r="N178">
-        <v>0.85</v>
+        <v>1.8</v>
       </c>
       <c r="O178" t="str">
         <v>mudithaj</v>
@@ -8779,10 +8779,10 @@
         <v>BL::UK RT</v>
       </c>
       <c r="E179" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Final press body &amp; sleeves</v>
       </c>
       <c r="F179" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G179" t="str">
         <v>Finishing</v>
@@ -8806,7 +8806,7 @@
         <v>17.96</v>
       </c>
       <c r="N179">
-        <v>1</v>
+        <v>2.2</v>
       </c>
       <c r="O179" t="str">
         <v>mudithaj</v>
@@ -8814,25 +8814,25 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B180" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C180" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D180" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E180" t="str">
-        <v>Attach back stitch</v>
+        <v>Attach woven label &amp; care label</v>
       </c>
       <c r="F180" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G180" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H180" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8841,45 +8841,45 @@
         <v>2</v>
       </c>
       <c r="J180" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K180" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L180">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M180">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N180">
-        <v>1.26</v>
+        <v>0.7</v>
       </c>
       <c r="O180" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B181" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C181" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D181" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E181" t="str">
-        <v>Attach pocket bag</v>
+        <v>Hang tag attach both sides</v>
       </c>
       <c r="F181" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G181" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H181" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8888,45 +8888,45 @@
         <v>2</v>
       </c>
       <c r="J181" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K181" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L181">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M181">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N181">
-        <v>0.56</v>
+        <v>0.85</v>
       </c>
       <c r="O181" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>920</v>
+        <v>847</v>
       </c>
       <c r="B182" t="str">
-        <v>GOT12524N::JK</v>
+        <v>6882T::BL</v>
       </c>
       <c r="C182" t="str">
-        <v>Jacket</v>
+        <v>Blouse</v>
       </c>
       <c r="D182" t="str">
-        <v>JK::B</v>
+        <v>BL::UK RT</v>
       </c>
       <c r="E182" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Fold, insert board &amp; poly bag</v>
       </c>
       <c r="F182" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G182" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H182" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -8935,22 +8935,22 @@
         <v>2</v>
       </c>
       <c r="J182" t="str">
-        <v>2026-05-25</v>
+        <v>2026-05-22</v>
       </c>
       <c r="K182" t="str">
-        <v>2026-05-28</v>
+        <v>2026-05-23</v>
       </c>
       <c r="L182">
-        <v>500</v>
+        <v>2190</v>
       </c>
       <c r="M182">
-        <v>22.22</v>
+        <v>17.96</v>
       </c>
       <c r="N182">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="O182" t="str">
-        <v>kamalag</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="183">
@@ -8967,7 +8967,7 @@
         <v>JK::B</v>
       </c>
       <c r="E183" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F183" t="str">
         <v>SNL</v>
@@ -8994,7 +8994,7 @@
         <v>22.22</v>
       </c>
       <c r="N183">
-        <v>0.77</v>
+        <v>1.26</v>
       </c>
       <c r="O183" t="str">
         <v>kamalag</v>
@@ -9014,10 +9014,10 @@
         <v>JK::B</v>
       </c>
       <c r="E184" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F184" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G184" t="str">
         <v>Sewing</v>
@@ -9041,7 +9041,7 @@
         <v>22.22</v>
       </c>
       <c r="N184">
-        <v>0.84</v>
+        <v>0.56</v>
       </c>
       <c r="O184" t="str">
         <v>kamalag</v>
@@ -9061,10 +9061,10 @@
         <v>JK::B</v>
       </c>
       <c r="E185" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F185" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G185" t="str">
         <v>Sewing</v>
@@ -9088,7 +9088,7 @@
         <v>22.22</v>
       </c>
       <c r="N185">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="O185" t="str">
         <v>kamalag</v>
@@ -9108,10 +9108,10 @@
         <v>JK::B</v>
       </c>
       <c r="E186" t="str">
-        <v>Attach zipper front</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F186" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G186" t="str">
         <v>Sewing</v>
@@ -9135,7 +9135,7 @@
         <v>22.22</v>
       </c>
       <c r="N186">
-        <v>2.48</v>
+        <v>0.77</v>
       </c>
       <c r="O186" t="str">
         <v>kamalag</v>
@@ -9155,10 +9155,10 @@
         <v>JK::B</v>
       </c>
       <c r="E187" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F187" t="str">
-        <v>LDN</v>
+        <v>4O/L</v>
       </c>
       <c r="G187" t="str">
         <v>Sewing</v>
@@ -9182,7 +9182,7 @@
         <v>22.22</v>
       </c>
       <c r="N187">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="O187" t="str">
         <v>kamalag</v>
@@ -9202,13 +9202,13 @@
         <v>JK::B</v>
       </c>
       <c r="E188" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F188" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G188" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H188" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9229,7 +9229,7 @@
         <v>22.22</v>
       </c>
       <c r="N188">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="O188" t="str">
         <v>kamalag</v>
@@ -9249,13 +9249,13 @@
         <v>JK::B</v>
       </c>
       <c r="E189" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F189" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G189" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H189" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9276,7 +9276,7 @@
         <v>22.22</v>
       </c>
       <c r="N189">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="O189" t="str">
         <v>kamalag</v>
@@ -9296,13 +9296,13 @@
         <v>JK::B</v>
       </c>
       <c r="E190" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F190" t="str">
-        <v>VIR</v>
+        <v>LDN</v>
       </c>
       <c r="G190" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H190" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9323,7 +9323,7 @@
         <v>22.22</v>
       </c>
       <c r="N190">
-        <v>2.8</v>
+        <v>0.63</v>
       </c>
       <c r="O190" t="str">
         <v>kamalag</v>
@@ -9343,10 +9343,10 @@
         <v>JK::B</v>
       </c>
       <c r="E191" t="str">
-        <v>Final press full jacket</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F191" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G191" t="str">
         <v>Finishing</v>
@@ -9370,7 +9370,7 @@
         <v>22.22</v>
       </c>
       <c r="N191">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O191" t="str">
         <v>kamalag</v>
@@ -9390,10 +9390,10 @@
         <v>JK::B</v>
       </c>
       <c r="E192" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F192" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G192" t="str">
         <v>Finishing</v>
@@ -9417,7 +9417,7 @@
         <v>22.22</v>
       </c>
       <c r="N192">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="O192" t="str">
         <v>kamalag</v>
@@ -9437,10 +9437,10 @@
         <v>JK::B</v>
       </c>
       <c r="E193" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F193" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G193" t="str">
         <v>Finishing</v>
@@ -9464,7 +9464,7 @@
         <v>22.22</v>
       </c>
       <c r="N193">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O193" t="str">
         <v>kamalag</v>
@@ -9484,10 +9484,10 @@
         <v>JK::B</v>
       </c>
       <c r="E194" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F194" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G194" t="str">
         <v>Finishing</v>
@@ -9511,7 +9511,7 @@
         <v>22.22</v>
       </c>
       <c r="N194">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="O194" t="str">
         <v>kamalag</v>
@@ -9528,16 +9528,16 @@
         <v>Jacket</v>
       </c>
       <c r="D195" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E195" t="str">
-        <v>Attach back stitch</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F195" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G195" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H195" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9546,10 +9546,10 @@
         <v>2</v>
       </c>
       <c r="J195" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K195" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L195">
         <v>500</v>
@@ -9558,7 +9558,7 @@
         <v>22.22</v>
       </c>
       <c r="N195">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
       <c r="O195" t="str">
         <v>kamalag</v>
@@ -9575,16 +9575,16 @@
         <v>Jacket</v>
       </c>
       <c r="D196" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E196" t="str">
-        <v>Attach pocket bag</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F196" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G196" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H196" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9593,10 +9593,10 @@
         <v>2</v>
       </c>
       <c r="J196" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K196" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L196">
         <v>500</v>
@@ -9605,7 +9605,7 @@
         <v>22.22</v>
       </c>
       <c r="N196">
-        <v>0.56</v>
+        <v>1.1</v>
       </c>
       <c r="O196" t="str">
         <v>kamalag</v>
@@ -9622,16 +9622,16 @@
         <v>Jacket</v>
       </c>
       <c r="D197" t="str">
-        <v>JK::G</v>
+        <v>JK::B</v>
       </c>
       <c r="E197" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F197" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G197" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H197" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9640,10 +9640,10 @@
         <v>2</v>
       </c>
       <c r="J197" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-25</v>
       </c>
       <c r="K197" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-28</v>
       </c>
       <c r="L197">
         <v>500</v>
@@ -9652,7 +9652,7 @@
         <v>22.22</v>
       </c>
       <c r="N197">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="O197" t="str">
         <v>kamalag</v>
@@ -9672,7 +9672,7 @@
         <v>JK::G</v>
       </c>
       <c r="E198" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F198" t="str">
         <v>SNL</v>
@@ -9699,7 +9699,7 @@
         <v>22.22</v>
       </c>
       <c r="N198">
-        <v>0.77</v>
+        <v>1.26</v>
       </c>
       <c r="O198" t="str">
         <v>kamalag</v>
@@ -9719,10 +9719,10 @@
         <v>JK::G</v>
       </c>
       <c r="E199" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F199" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G199" t="str">
         <v>Sewing</v>
@@ -9746,7 +9746,7 @@
         <v>22.22</v>
       </c>
       <c r="N199">
-        <v>0.84</v>
+        <v>0.56</v>
       </c>
       <c r="O199" t="str">
         <v>kamalag</v>
@@ -9766,10 +9766,10 @@
         <v>JK::G</v>
       </c>
       <c r="E200" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F200" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G200" t="str">
         <v>Sewing</v>
@@ -9793,7 +9793,7 @@
         <v>22.22</v>
       </c>
       <c r="N200">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="O200" t="str">
         <v>kamalag</v>
@@ -9813,10 +9813,10 @@
         <v>JK::G</v>
       </c>
       <c r="E201" t="str">
-        <v>Attach zipper front</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F201" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G201" t="str">
         <v>Sewing</v>
@@ -9840,7 +9840,7 @@
         <v>22.22</v>
       </c>
       <c r="N201">
-        <v>2.48</v>
+        <v>0.77</v>
       </c>
       <c r="O201" t="str">
         <v>kamalag</v>
@@ -9860,10 +9860,10 @@
         <v>JK::G</v>
       </c>
       <c r="E202" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F202" t="str">
-        <v>LDN</v>
+        <v>4O/L</v>
       </c>
       <c r="G202" t="str">
         <v>Sewing</v>
@@ -9887,7 +9887,7 @@
         <v>22.22</v>
       </c>
       <c r="N202">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="O202" t="str">
         <v>kamalag</v>
@@ -9907,13 +9907,13 @@
         <v>JK::G</v>
       </c>
       <c r="E203" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F203" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G203" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H203" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9934,7 +9934,7 @@
         <v>22.22</v>
       </c>
       <c r="N203">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="O203" t="str">
         <v>kamalag</v>
@@ -9954,13 +9954,13 @@
         <v>JK::G</v>
       </c>
       <c r="E204" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F204" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G204" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H204" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -9981,7 +9981,7 @@
         <v>22.22</v>
       </c>
       <c r="N204">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="O204" t="str">
         <v>kamalag</v>
@@ -10001,13 +10001,13 @@
         <v>JK::G</v>
       </c>
       <c r="E205" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F205" t="str">
-        <v>VIR</v>
+        <v>LDN</v>
       </c>
       <c r="G205" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H205" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10028,7 +10028,7 @@
         <v>22.22</v>
       </c>
       <c r="N205">
-        <v>2.8</v>
+        <v>0.63</v>
       </c>
       <c r="O205" t="str">
         <v>kamalag</v>
@@ -10048,10 +10048,10 @@
         <v>JK::G</v>
       </c>
       <c r="E206" t="str">
-        <v>Final press full jacket</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F206" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G206" t="str">
         <v>Finishing</v>
@@ -10075,7 +10075,7 @@
         <v>22.22</v>
       </c>
       <c r="N206">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O206" t="str">
         <v>kamalag</v>
@@ -10095,10 +10095,10 @@
         <v>JK::G</v>
       </c>
       <c r="E207" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F207" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G207" t="str">
         <v>Finishing</v>
@@ -10122,7 +10122,7 @@
         <v>22.22</v>
       </c>
       <c r="N207">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="O207" t="str">
         <v>kamalag</v>
@@ -10142,10 +10142,10 @@
         <v>JK::G</v>
       </c>
       <c r="E208" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F208" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G208" t="str">
         <v>Finishing</v>
@@ -10169,7 +10169,7 @@
         <v>22.22</v>
       </c>
       <c r="N208">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O208" t="str">
         <v>kamalag</v>
@@ -10189,10 +10189,10 @@
         <v>JK::G</v>
       </c>
       <c r="E209" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F209" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G209" t="str">
         <v>Finishing</v>
@@ -10216,7 +10216,7 @@
         <v>22.22</v>
       </c>
       <c r="N209">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="O209" t="str">
         <v>kamalag</v>
@@ -10233,16 +10233,16 @@
         <v>Jacket</v>
       </c>
       <c r="D210" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E210" t="str">
-        <v>Attach back stitch</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F210" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G210" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H210" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10251,10 +10251,10 @@
         <v>2</v>
       </c>
       <c r="J210" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K210" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L210">
         <v>500</v>
@@ -10263,7 +10263,7 @@
         <v>22.22</v>
       </c>
       <c r="N210">
-        <v>1.26</v>
+        <v>0.9</v>
       </c>
       <c r="O210" t="str">
         <v>kamalag</v>
@@ -10280,16 +10280,16 @@
         <v>Jacket</v>
       </c>
       <c r="D211" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E211" t="str">
-        <v>Attach pocket bag</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F211" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G211" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H211" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10298,10 +10298,10 @@
         <v>2</v>
       </c>
       <c r="J211" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K211" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L211">
         <v>500</v>
@@ -10310,7 +10310,7 @@
         <v>22.22</v>
       </c>
       <c r="N211">
-        <v>0.56</v>
+        <v>1.1</v>
       </c>
       <c r="O211" t="str">
         <v>kamalag</v>
@@ -10327,16 +10327,16 @@
         <v>Jacket</v>
       </c>
       <c r="D212" t="str">
-        <v>JK::W</v>
+        <v>JK::G</v>
       </c>
       <c r="E212" t="str">
-        <v>Attach self &amp; lining sleeve</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F212" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G212" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H212" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10345,10 +10345,10 @@
         <v>2</v>
       </c>
       <c r="J212" t="str">
-        <v>2026-06-01</v>
+        <v>2026-05-29</v>
       </c>
       <c r="K212" t="str">
-        <v>2026-06-02</v>
+        <v>2026-05-30</v>
       </c>
       <c r="L212">
         <v>500</v>
@@ -10357,7 +10357,7 @@
         <v>22.22</v>
       </c>
       <c r="N212">
-        <v>1.04</v>
+        <v>1.3</v>
       </c>
       <c r="O212" t="str">
         <v>kamalag</v>
@@ -10377,7 +10377,7 @@
         <v>JK::W</v>
       </c>
       <c r="E213" t="str">
-        <v>Collar attach to body</v>
+        <v>Attach back stitch</v>
       </c>
       <c r="F213" t="str">
         <v>SNL</v>
@@ -10404,7 +10404,7 @@
         <v>22.22</v>
       </c>
       <c r="N213">
-        <v>0.77</v>
+        <v>1.26</v>
       </c>
       <c r="O213" t="str">
         <v>kamalag</v>
@@ -10424,10 +10424,10 @@
         <v>JK::W</v>
       </c>
       <c r="E214" t="str">
-        <v>Collar attach lining</v>
+        <v>Attach pocket bag</v>
       </c>
       <c r="F214" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G214" t="str">
         <v>Sewing</v>
@@ -10451,7 +10451,7 @@
         <v>22.22</v>
       </c>
       <c r="N214">
-        <v>0.84</v>
+        <v>0.56</v>
       </c>
       <c r="O214" t="str">
         <v>kamalag</v>
@@ -10471,10 +10471,10 @@
         <v>JK::W</v>
       </c>
       <c r="E215" t="str">
-        <v>Sleeve attach overlock</v>
+        <v>Attach self &amp; lining sleeve</v>
       </c>
       <c r="F215" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G215" t="str">
         <v>Sewing</v>
@@ -10498,7 +10498,7 @@
         <v>22.22</v>
       </c>
       <c r="N215">
-        <v>1.34</v>
+        <v>1.04</v>
       </c>
       <c r="O215" t="str">
         <v>kamalag</v>
@@ -10518,10 +10518,10 @@
         <v>JK::W</v>
       </c>
       <c r="E216" t="str">
-        <v>Attach zipper front</v>
+        <v>Collar attach to body</v>
       </c>
       <c r="F216" t="str">
-        <v>SNNF</v>
+        <v>SNL</v>
       </c>
       <c r="G216" t="str">
         <v>Sewing</v>
@@ -10545,7 +10545,7 @@
         <v>22.22</v>
       </c>
       <c r="N216">
-        <v>2.48</v>
+        <v>0.77</v>
       </c>
       <c r="O216" t="str">
         <v>kamalag</v>
@@ -10565,10 +10565,10 @@
         <v>JK::W</v>
       </c>
       <c r="E217" t="str">
-        <v>Attach welt pocket by D/N</v>
+        <v>Collar attach lining</v>
       </c>
       <c r="F217" t="str">
-        <v>LDN</v>
+        <v>4O/L</v>
       </c>
       <c r="G217" t="str">
         <v>Sewing</v>
@@ -10592,7 +10592,7 @@
         <v>22.22</v>
       </c>
       <c r="N217">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="O217" t="str">
         <v>kamalag</v>
@@ -10612,13 +10612,13 @@
         <v>JK::W</v>
       </c>
       <c r="E218" t="str">
-        <v>Thread trim &amp; broken check</v>
+        <v>Sleeve attach overlock</v>
       </c>
       <c r="F218" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G218" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H218" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10639,7 +10639,7 @@
         <v>22.22</v>
       </c>
       <c r="N218">
-        <v>2.5</v>
+        <v>1.34</v>
       </c>
       <c r="O218" t="str">
         <v>kamalag</v>
@@ -10659,13 +10659,13 @@
         <v>JK::W</v>
       </c>
       <c r="E219" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Attach zipper front</v>
       </c>
       <c r="F219" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G219" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H219" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10686,7 +10686,7 @@
         <v>22.22</v>
       </c>
       <c r="N219">
-        <v>1.2</v>
+        <v>2.48</v>
       </c>
       <c r="O219" t="str">
         <v>kamalag</v>
@@ -10706,13 +10706,13 @@
         <v>JK::W</v>
       </c>
       <c r="E220" t="str">
-        <v>Press collar &amp; lapel area</v>
+        <v>Attach welt pocket by D/N</v>
       </c>
       <c r="F220" t="str">
-        <v>VIR</v>
+        <v>LDN</v>
       </c>
       <c r="G220" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H220" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10733,7 +10733,7 @@
         <v>22.22</v>
       </c>
       <c r="N220">
-        <v>2.8</v>
+        <v>0.63</v>
       </c>
       <c r="O220" t="str">
         <v>kamalag</v>
@@ -10753,10 +10753,10 @@
         <v>JK::W</v>
       </c>
       <c r="E221" t="str">
-        <v>Final press full jacket</v>
+        <v>Thread trim &amp; broken check</v>
       </c>
       <c r="F221" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G221" t="str">
         <v>Finishing</v>
@@ -10780,7 +10780,7 @@
         <v>22.22</v>
       </c>
       <c r="N221">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="O221" t="str">
         <v>kamalag</v>
@@ -10800,10 +10800,10 @@
         <v>JK::W</v>
       </c>
       <c r="E222" t="str">
-        <v>Label attach - main &amp; care</v>
+        <v>Button attach (2 buttons)</v>
       </c>
       <c r="F222" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G222" t="str">
         <v>Finishing</v>
@@ -10827,7 +10827,7 @@
         <v>22.22</v>
       </c>
       <c r="N222">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="O222" t="str">
         <v>kamalag</v>
@@ -10847,10 +10847,10 @@
         <v>JK::W</v>
       </c>
       <c r="E223" t="str">
-        <v>Hang tag attach &amp; measurement check</v>
+        <v>Press collar &amp; lapel area</v>
       </c>
       <c r="F223" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G223" t="str">
         <v>Finishing</v>
@@ -10874,7 +10874,7 @@
         <v>22.22</v>
       </c>
       <c r="N223">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="O223" t="str">
         <v>kamalag</v>
@@ -10894,10 +10894,10 @@
         <v>JK::W</v>
       </c>
       <c r="E224" t="str">
-        <v>Fold on hanger &amp; poly bag</v>
+        <v>Final press full jacket</v>
       </c>
       <c r="F224" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G224" t="str">
         <v>Finishing</v>
@@ -10921,7 +10921,7 @@
         <v>22.22</v>
       </c>
       <c r="N224">
-        <v>1.3</v>
+        <v>3.5</v>
       </c>
       <c r="O224" t="str">
         <v>kamalag</v>
@@ -10929,25 +10929,25 @@
     </row>
     <row r="225">
       <c r="A225" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B225" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C225" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D225" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E225" t="str">
-        <v>Attach back panel to front</v>
+        <v>Label attach - main &amp; care</v>
       </c>
       <c r="F225" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G225" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H225" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -10956,45 +10956,45 @@
         <v>2</v>
       </c>
       <c r="J225" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K225" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L225">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M225">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N225">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="O225" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B226" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C226" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D226" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E226" t="str">
-        <v>Attach collar to body</v>
+        <v>Hang tag attach &amp; measurement check</v>
       </c>
       <c r="F226" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G226" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H226" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11003,45 +11003,45 @@
         <v>2</v>
       </c>
       <c r="J226" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K226" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L226">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M226">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N226">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="O226" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
-        <v>847</v>
+        <v>920</v>
       </c>
       <c r="B227" t="str">
-        <v>8774T::BL</v>
+        <v>GOT12524N::JK</v>
       </c>
       <c r="C227" t="str">
-        <v>Blouse</v>
+        <v>Jacket</v>
       </c>
       <c r="D227" t="str">
-        <v>BL::AU RT</v>
+        <v>JK::W</v>
       </c>
       <c r="E227" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Fold on hanger &amp; poly bag</v>
       </c>
       <c r="F227" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G227" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H227" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11050,22 +11050,22 @@
         <v>2</v>
       </c>
       <c r="J227" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-01</v>
       </c>
       <c r="K227" t="str">
-        <v>2026-06-05</v>
+        <v>2026-06-02</v>
       </c>
       <c r="L227">
-        <v>607</v>
+        <v>500</v>
       </c>
       <c r="M227">
-        <v>19</v>
+        <v>22.22</v>
       </c>
       <c r="N227">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="O227" t="str">
-        <v>sasanthar</v>
+        <v>kamalag</v>
       </c>
     </row>
     <row r="228">
@@ -11082,10 +11082,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E228" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F228" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G228" t="str">
         <v>Sewing</v>
@@ -11109,7 +11109,7 @@
         <v>19</v>
       </c>
       <c r="N228">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="O228" t="str">
         <v>sasanthar</v>
@@ -11129,7 +11129,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E229" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F229" t="str">
         <v>SNL</v>
@@ -11156,7 +11156,7 @@
         <v>19</v>
       </c>
       <c r="N229">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="O229" t="str">
         <v>sasanthar</v>
@@ -11176,7 +11176,7 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E230" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F230" t="str">
         <v>SNL</v>
@@ -11203,7 +11203,7 @@
         <v>19</v>
       </c>
       <c r="N230">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O230" t="str">
         <v>sasanthar</v>
@@ -11223,10 +11223,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E231" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F231" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G231" t="str">
         <v>Sewing</v>
@@ -11250,7 +11250,7 @@
         <v>19</v>
       </c>
       <c r="N231">
-        <v>1.3</v>
+        <v>0.75</v>
       </c>
       <c r="O231" t="str">
         <v>sasanthar</v>
@@ -11270,13 +11270,13 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E232" t="str">
-        <v>Thread trim full garment</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F232" t="str">
         <v>SNL</v>
       </c>
       <c r="G232" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H232" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11297,7 +11297,7 @@
         <v>19</v>
       </c>
       <c r="N232">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="O232" t="str">
         <v>sasanthar</v>
@@ -11317,13 +11317,13 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E233" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F233" t="str">
         <v>SNL</v>
       </c>
       <c r="G233" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H233" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11344,7 +11344,7 @@
         <v>19</v>
       </c>
       <c r="N233">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O233" t="str">
         <v>sasanthar</v>
@@ -11364,13 +11364,13 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E234" t="str">
-        <v>Full body pressing</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F234" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G234" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H234" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11391,7 +11391,7 @@
         <v>19</v>
       </c>
       <c r="N234">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="O234" t="str">
         <v>sasanthar</v>
@@ -11411,10 +11411,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E235" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F235" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G235" t="str">
         <v>Finishing</v>
@@ -11438,7 +11438,7 @@
         <v>19</v>
       </c>
       <c r="N235">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O235" t="str">
         <v>sasanthar</v>
@@ -11458,10 +11458,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E236" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F236" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G236" t="str">
         <v>Finishing</v>
@@ -11485,7 +11485,7 @@
         <v>19</v>
       </c>
       <c r="N236">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="O236" t="str">
         <v>sasanthar</v>
@@ -11505,10 +11505,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E237" t="str">
-        <v>Hang tag attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F237" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G237" t="str">
         <v>Finishing</v>
@@ -11532,7 +11532,7 @@
         <v>19</v>
       </c>
       <c r="N237">
-        <v>0.85</v>
+        <v>3.2</v>
       </c>
       <c r="O237" t="str">
         <v>sasanthar</v>
@@ -11552,10 +11552,10 @@
         <v>BL::AU RT</v>
       </c>
       <c r="E238" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F238" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G238" t="str">
         <v>Finishing</v>
@@ -11579,7 +11579,7 @@
         <v>19</v>
       </c>
       <c r="N238">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O238" t="str">
         <v>sasanthar</v>
@@ -11596,16 +11596,16 @@
         <v>Blouse</v>
       </c>
       <c r="D239" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E239" t="str">
-        <v>Attach back panel to front</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F239" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G239" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H239" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11614,10 +11614,10 @@
         <v>2</v>
       </c>
       <c r="J239" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K239" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L239">
         <v>607</v>
@@ -11626,7 +11626,7 @@
         <v>19</v>
       </c>
       <c r="N239">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O239" t="str">
         <v>sasanthar</v>
@@ -11643,16 +11643,16 @@
         <v>Blouse</v>
       </c>
       <c r="D240" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E240" t="str">
-        <v>Attach collar to body</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F240" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G240" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H240" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11661,10 +11661,10 @@
         <v>2</v>
       </c>
       <c r="J240" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K240" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L240">
         <v>607</v>
@@ -11673,7 +11673,7 @@
         <v>19</v>
       </c>
       <c r="N240">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="O240" t="str">
         <v>sasanthar</v>
@@ -11690,16 +11690,16 @@
         <v>Blouse</v>
       </c>
       <c r="D241" t="str">
-        <v>BL::US RT</v>
+        <v>BL::AU RT</v>
       </c>
       <c r="E241" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F241" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G241" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H241" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11708,10 +11708,10 @@
         <v>2</v>
       </c>
       <c r="J241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-03</v>
       </c>
       <c r="K241" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-05</v>
       </c>
       <c r="L241">
         <v>607</v>
@@ -11720,7 +11720,7 @@
         <v>19</v>
       </c>
       <c r="N241">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O241" t="str">
         <v>sasanthar</v>
@@ -11740,10 +11740,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E242" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F242" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G242" t="str">
         <v>Sewing</v>
@@ -11767,7 +11767,7 @@
         <v>19</v>
       </c>
       <c r="N242">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="O242" t="str">
         <v>sasanthar</v>
@@ -11787,7 +11787,7 @@
         <v>BL::US RT</v>
       </c>
       <c r="E243" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F243" t="str">
         <v>SNL</v>
@@ -11814,7 +11814,7 @@
         <v>19</v>
       </c>
       <c r="N243">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="O243" t="str">
         <v>sasanthar</v>
@@ -11834,7 +11834,7 @@
         <v>BL::US RT</v>
       </c>
       <c r="E244" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F244" t="str">
         <v>SNL</v>
@@ -11861,7 +11861,7 @@
         <v>19</v>
       </c>
       <c r="N244">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O244" t="str">
         <v>sasanthar</v>
@@ -11881,10 +11881,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E245" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F245" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G245" t="str">
         <v>Sewing</v>
@@ -11908,7 +11908,7 @@
         <v>19</v>
       </c>
       <c r="N245">
-        <v>1.3</v>
+        <v>0.75</v>
       </c>
       <c r="O245" t="str">
         <v>sasanthar</v>
@@ -11928,13 +11928,13 @@
         <v>BL::US RT</v>
       </c>
       <c r="E246" t="str">
-        <v>Thread trim full garment</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F246" t="str">
         <v>SNL</v>
       </c>
       <c r="G246" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H246" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -11955,7 +11955,7 @@
         <v>19</v>
       </c>
       <c r="N246">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="O246" t="str">
         <v>sasanthar</v>
@@ -11975,13 +11975,13 @@
         <v>BL::US RT</v>
       </c>
       <c r="E247" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F247" t="str">
         <v>SNL</v>
       </c>
       <c r="G247" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H247" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12002,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="N247">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O247" t="str">
         <v>sasanthar</v>
@@ -12022,13 +12022,13 @@
         <v>BL::US RT</v>
       </c>
       <c r="E248" t="str">
-        <v>Full body pressing</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F248" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G248" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H248" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12049,7 +12049,7 @@
         <v>19</v>
       </c>
       <c r="N248">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="O248" t="str">
         <v>sasanthar</v>
@@ -12069,10 +12069,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E249" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F249" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G249" t="str">
         <v>Finishing</v>
@@ -12096,7 +12096,7 @@
         <v>19</v>
       </c>
       <c r="N249">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O249" t="str">
         <v>sasanthar</v>
@@ -12116,10 +12116,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E250" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F250" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G250" t="str">
         <v>Finishing</v>
@@ -12143,7 +12143,7 @@
         <v>19</v>
       </c>
       <c r="N250">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="O250" t="str">
         <v>sasanthar</v>
@@ -12163,10 +12163,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E251" t="str">
-        <v>Hang tag attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F251" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G251" t="str">
         <v>Finishing</v>
@@ -12190,7 +12190,7 @@
         <v>19</v>
       </c>
       <c r="N251">
-        <v>0.85</v>
+        <v>3.2</v>
       </c>
       <c r="O251" t="str">
         <v>sasanthar</v>
@@ -12210,10 +12210,10 @@
         <v>BL::US RT</v>
       </c>
       <c r="E252" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F252" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G252" t="str">
         <v>Finishing</v>
@@ -12237,7 +12237,7 @@
         <v>19</v>
       </c>
       <c r="N252">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O252" t="str">
         <v>sasanthar</v>
@@ -12254,16 +12254,16 @@
         <v>Blouse</v>
       </c>
       <c r="D253" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E253" t="str">
-        <v>Attach back panel to front</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F253" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G253" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H253" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12272,10 +12272,10 @@
         <v>2</v>
       </c>
       <c r="J253" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K253" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L253">
         <v>607</v>
@@ -12284,7 +12284,7 @@
         <v>19</v>
       </c>
       <c r="N253">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="O253" t="str">
         <v>sasanthar</v>
@@ -12301,16 +12301,16 @@
         <v>Blouse</v>
       </c>
       <c r="D254" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E254" t="str">
-        <v>Attach collar to body</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F254" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G254" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H254" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12319,10 +12319,10 @@
         <v>2</v>
       </c>
       <c r="J254" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K254" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L254">
         <v>607</v>
@@ -12331,7 +12331,7 @@
         <v>19</v>
       </c>
       <c r="N254">
-        <v>1.2</v>
+        <v>0.85</v>
       </c>
       <c r="O254" t="str">
         <v>sasanthar</v>
@@ -12348,16 +12348,16 @@
         <v>Blouse</v>
       </c>
       <c r="D255" t="str">
-        <v>BL::EU RT</v>
+        <v>BL::US RT</v>
       </c>
       <c r="E255" t="str">
-        <v>Attach sleeve to armhole</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F255" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G255" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H255" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12366,10 +12366,10 @@
         <v>2</v>
       </c>
       <c r="J255" t="str">
-        <v>2026-06-08</v>
+        <v>2026-06-06</v>
       </c>
       <c r="K255" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-06</v>
       </c>
       <c r="L255">
         <v>607</v>
@@ -12378,7 +12378,7 @@
         <v>19</v>
       </c>
       <c r="N255">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="O255" t="str">
         <v>sasanthar</v>
@@ -12398,10 +12398,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E256" t="str">
-        <v>Side seam overlock stitch</v>
+        <v>Attach back panel to front</v>
       </c>
       <c r="F256" t="str">
-        <v>4O/L</v>
+        <v>SNL</v>
       </c>
       <c r="G256" t="str">
         <v>Sewing</v>
@@ -12425,7 +12425,7 @@
         <v>19</v>
       </c>
       <c r="N256">
-        <v>0.75</v>
+        <v>1.1</v>
       </c>
       <c r="O256" t="str">
         <v>sasanthar</v>
@@ -12445,7 +12445,7 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E257" t="str">
-        <v>Hem sleeve bottom</v>
+        <v>Attach collar to body</v>
       </c>
       <c r="F257" t="str">
         <v>SNL</v>
@@ -12472,7 +12472,7 @@
         <v>19</v>
       </c>
       <c r="N257">
-        <v>0.7</v>
+        <v>1.2</v>
       </c>
       <c r="O257" t="str">
         <v>sasanthar</v>
@@ -12492,7 +12492,7 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E258" t="str">
-        <v>Cuff attach &amp; topstitch</v>
+        <v>Attach sleeve to armhole</v>
       </c>
       <c r="F258" t="str">
         <v>SNL</v>
@@ -12519,7 +12519,7 @@
         <v>19</v>
       </c>
       <c r="N258">
-        <v>1</v>
+        <v>1.6</v>
       </c>
       <c r="O258" t="str">
         <v>sasanthar</v>
@@ -12539,10 +12539,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E259" t="str">
-        <v>Placket attach &amp; close</v>
+        <v>Side seam overlock stitch</v>
       </c>
       <c r="F259" t="str">
-        <v>SNL</v>
+        <v>4O/L</v>
       </c>
       <c r="G259" t="str">
         <v>Sewing</v>
@@ -12566,7 +12566,7 @@
         <v>19</v>
       </c>
       <c r="N259">
-        <v>1.3</v>
+        <v>0.75</v>
       </c>
       <c r="O259" t="str">
         <v>sasanthar</v>
@@ -12586,13 +12586,13 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E260" t="str">
-        <v>Thread trim full garment</v>
+        <v>Hem sleeve bottom</v>
       </c>
       <c r="F260" t="str">
         <v>SNL</v>
       </c>
       <c r="G260" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H260" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12613,7 +12613,7 @@
         <v>19</v>
       </c>
       <c r="N260">
-        <v>2</v>
+        <v>0.7</v>
       </c>
       <c r="O260" t="str">
         <v>sasanthar</v>
@@ -12633,13 +12633,13 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E261" t="str">
-        <v>Button hole make &amp; button attach</v>
+        <v>Cuff attach &amp; topstitch</v>
       </c>
       <c r="F261" t="str">
         <v>SNL</v>
       </c>
       <c r="G261" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H261" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12660,7 +12660,7 @@
         <v>19</v>
       </c>
       <c r="N261">
-        <v>1.9</v>
+        <v>1</v>
       </c>
       <c r="O261" t="str">
         <v>sasanthar</v>
@@ -12680,13 +12680,13 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E262" t="str">
-        <v>Full body pressing</v>
+        <v>Placket attach &amp; close</v>
       </c>
       <c r="F262" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G262" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H262" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -12707,7 +12707,7 @@
         <v>19</v>
       </c>
       <c r="N262">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="O262" t="str">
         <v>sasanthar</v>
@@ -12727,10 +12727,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E263" t="str">
-        <v>Collar &amp; cuff press</v>
+        <v>Thread trim full garment</v>
       </c>
       <c r="F263" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G263" t="str">
         <v>Finishing</v>
@@ -12754,7 +12754,7 @@
         <v>19</v>
       </c>
       <c r="N263">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="O263" t="str">
         <v>sasanthar</v>
@@ -12774,10 +12774,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E264" t="str">
-        <v>Main &amp; care label attach</v>
+        <v>Button hole make &amp; button attach</v>
       </c>
       <c r="F264" t="str">
-        <v>HELP</v>
+        <v>SNL</v>
       </c>
       <c r="G264" t="str">
         <v>Finishing</v>
@@ -12801,7 +12801,7 @@
         <v>19</v>
       </c>
       <c r="N264">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="O264" t="str">
         <v>sasanthar</v>
@@ -12821,10 +12821,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E265" t="str">
-        <v>Hang tag attach</v>
+        <v>Full body pressing</v>
       </c>
       <c r="F265" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G265" t="str">
         <v>Finishing</v>
@@ -12848,7 +12848,7 @@
         <v>19</v>
       </c>
       <c r="N265">
-        <v>0.85</v>
+        <v>3.2</v>
       </c>
       <c r="O265" t="str">
         <v>sasanthar</v>
@@ -12868,10 +12868,10 @@
         <v>BL::EU RT</v>
       </c>
       <c r="E266" t="str">
-        <v>Fold, board &amp; polybag pack</v>
+        <v>Collar &amp; cuff press</v>
       </c>
       <c r="F266" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G266" t="str">
         <v>Finishing</v>
@@ -12895,7 +12895,7 @@
         <v>19</v>
       </c>
       <c r="N266">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="O266" t="str">
         <v>sasanthar</v>
@@ -12903,160 +12903,160 @@
     </row>
     <row r="267">
       <c r="A267" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B267" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C267" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D267" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E267" t="str">
-        <v>Attach label 2 sides</v>
+        <v>Main &amp; care label attach</v>
       </c>
       <c r="F267" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G267" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H267" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I267">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J267" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K267" t="str">
-        <v>2026-05-19</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L267">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M267">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N267">
-        <v>0.25</v>
+        <v>0.8</v>
       </c>
       <c r="O267" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B268" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C268" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D268" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E268" t="str">
-        <v>Attach binding @ in seam 2x2</v>
+        <v>Hang tag attach</v>
       </c>
       <c r="F268" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G268" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H268" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I268">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J268" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K268" t="str">
-        <v>2026-05-19</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L268">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M268">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N268">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="O268" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B269" t="str">
-        <v>4462A::SH</v>
+        <v>8774T::BL</v>
       </c>
       <c r="C269" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D269" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E269" t="str">
-        <v>Attach bottom triangle</v>
+        <v>Fold, board &amp; polybag pack</v>
       </c>
       <c r="F269" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G269" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H269" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
       </c>
       <c r="I269">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J269" t="str">
-        <v>2026-05-16</v>
+        <v>2026-06-08</v>
       </c>
       <c r="K269" t="str">
-        <v>2026-05-19</v>
+        <v>2026-06-09</v>
       </c>
       <c r="L269">
-        <v>646</v>
+        <v>607</v>
       </c>
       <c r="M269">
-        <v>15.28</v>
+        <v>19</v>
       </c>
       <c r="N269">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="O269" t="str">
-        <v>priyanthi</v>
+        <v>sasanthar</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B270" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C270" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D270" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E270" t="str">
-        <v>Attach curve contour w/b</v>
+        <v>Attach front placket</v>
       </c>
       <c r="F270" t="str">
         <v>SNL</v>
@@ -13071,39 +13071,39 @@
         <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L270">
         <v>646</v>
       </c>
       <c r="M270">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N270">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="O270" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B271" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C271" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D271" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E271" t="str">
-        <v>Attach FLAP pocket</v>
+        <v>Attach collar to neckline</v>
       </c>
       <c r="F271" t="str">
         <v>SNL</v>
@@ -13118,39 +13118,39 @@
         <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L271">
         <v>646</v>
       </c>
       <c r="M271">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N271">
-        <v>0.45</v>
+        <v>0.95</v>
       </c>
       <c r="O271" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B272" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C272" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D272" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E272" t="str">
-        <v>Attach hem facing to btm leg</v>
+        <v>Attach sleeve to body</v>
       </c>
       <c r="F272" t="str">
         <v>SNL</v>
@@ -13165,42 +13165,42 @@
         <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L272">
         <v>646</v>
       </c>
       <c r="M272">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N272">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="O272" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B273" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C273" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D273" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E273" t="str">
-        <v>Join zip nip + fly attach</v>
+        <v>Join side seams</v>
       </c>
       <c r="F273" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G273" t="str">
         <v>Sewing</v>
@@ -13212,42 +13212,42 @@
         <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L273">
         <v>646</v>
       </c>
       <c r="M273">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N273">
-        <v>0.61</v>
+        <v>0.8</v>
       </c>
       <c r="O273" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B274" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C274" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D274" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E274" t="str">
-        <v>Mark &amp; attach bar to w/b</v>
+        <v>Hem bottom edge</v>
       </c>
       <c r="F274" t="str">
-        <v>RM/L</v>
+        <v>SNL</v>
       </c>
       <c r="G274" t="str">
         <v>Sewing</v>
@@ -13259,45 +13259,45 @@
         <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L274">
         <v>646</v>
       </c>
       <c r="M274">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N274">
-        <v>0.42</v>
+        <v>0.7</v>
       </c>
       <c r="O274" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B275" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C275" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D275" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E275" t="str">
-        <v>Thread trimming full garment</v>
+        <v>Attach cuff to sleeve</v>
       </c>
       <c r="F275" t="str">
         <v>SNL</v>
       </c>
       <c r="G275" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H275" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13306,45 +13306,45 @@
         <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L275">
         <v>646</v>
       </c>
       <c r="M275">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N275">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="O275" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B276" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C276" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D276" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E276" t="str">
-        <v>Button attach (2 buttons)</v>
+        <v>Overlock neckline edge</v>
       </c>
       <c r="F276" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G276" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H276" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13353,42 +13353,42 @@
         <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L276">
         <v>646</v>
       </c>
       <c r="M276">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N276">
-        <v>1</v>
+        <v>0.55</v>
       </c>
       <c r="O276" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B277" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C277" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D277" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E277" t="str">
-        <v>Press waistband &amp; seam</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F277" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G277" t="str">
         <v>Finishing</v>
@@ -13400,42 +13400,42 @@
         <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L277">
         <v>646</v>
       </c>
       <c r="M277">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N277">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="O277" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B278" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C278" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D278" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E278" t="str">
-        <v>Final press full shirt</v>
+        <v>Button attach (3 buttons)</v>
       </c>
       <c r="F278" t="str">
-        <v>VIR</v>
+        <v>SNL</v>
       </c>
       <c r="G278" t="str">
         <v>Finishing</v>
@@ -13447,42 +13447,42 @@
         <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L278">
         <v>646</v>
       </c>
       <c r="M278">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N278">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="O278" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B279" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C279" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D279" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E279" t="str">
-        <v>Label attach manual</v>
+        <v>Final pressing body</v>
       </c>
       <c r="F279" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G279" t="str">
         <v>Finishing</v>
@@ -13494,42 +13494,42 @@
         <v>3</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L279">
         <v>646</v>
       </c>
       <c r="M279">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N279">
-        <v>0.75</v>
+        <v>2.5</v>
       </c>
       <c r="O279" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B280" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C280" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D280" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E280" t="str">
-        <v>Measurement check &amp; hang tag</v>
+        <v>Press collar &amp; cuff</v>
       </c>
       <c r="F280" t="str">
-        <v>HELP</v>
+        <v>VIR</v>
       </c>
       <c r="G280" t="str">
         <v>Finishing</v>
@@ -13541,39 +13541,39 @@
         <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L280">
         <v>646</v>
       </c>
       <c r="M280">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N280">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
       <c r="O280" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="str">
-        <v>935</v>
+        <v>847</v>
       </c>
       <c r="B281" t="str">
-        <v>4462A::SH</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C281" t="str">
-        <v>Shirt</v>
+        <v>Blouse</v>
       </c>
       <c r="D281" t="str">
-        <v>SH::EU RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E281" t="str">
-        <v>Fold, bag &amp; carton pack</v>
+        <v>Attach main label manual</v>
       </c>
       <c r="F281" t="str">
         <v>HELP</v>
@@ -13588,22 +13588,22 @@
         <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-16</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-19</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L281">
         <v>646</v>
       </c>
       <c r="M281">
-        <v>15.28</v>
+        <v>16.15</v>
       </c>
       <c r="N281">
-        <v>1.1</v>
+        <v>0.75</v>
       </c>
       <c r="O281" t="str">
-        <v>priyanthi</v>
+        <v>mudithaj</v>
       </c>
     </row>
     <row r="282">
@@ -13611,22 +13611,22 @@
         <v>847</v>
       </c>
       <c r="B282" t="str">
-        <v>6882T::BL</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C282" t="str">
         <v>Blouse</v>
       </c>
       <c r="D282" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E282" t="str">
-        <v>02 pc back yoke attach to back</v>
+        <v>Hang tag attach &amp; fold</v>
       </c>
       <c r="F282" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G282" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H282" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13635,19 +13635,19 @@
         <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L282">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M282">
-        <v>17.96</v>
+        <v>16.15</v>
       </c>
       <c r="N282">
-        <v>0.43</v>
+        <v>0.9</v>
       </c>
       <c r="O282" t="str">
         <v>mudithaj</v>
@@ -13658,22 +13658,22 @@
         <v>847</v>
       </c>
       <c r="B283" t="str">
-        <v>6882T::BL</v>
+        <v>4461T::BL</v>
       </c>
       <c r="C283" t="str">
         <v>Blouse</v>
       </c>
       <c r="D283" t="str">
-        <v>BL::MX RT</v>
+        <v>BL::EU RT</v>
       </c>
       <c r="E283" t="str">
-        <v>Attach cuff</v>
+        <v>Poly bag &amp; pack into carton</v>
       </c>
       <c r="F283" t="str">
-        <v>SNL</v>
+        <v>HELP</v>
       </c>
       <c r="G283" t="str">
-        <v>Sewing</v>
+        <v>Finishing</v>
       </c>
       <c r="H283" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13682,19 +13682,19 @@
         <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-05-20</v>
+        <v>2026-05-13</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-05-22</v>
+        <v>2026-05-14</v>
       </c>
       <c r="L283">
-        <v>2190</v>
+        <v>646</v>
       </c>
       <c r="M283">
-        <v>17.96</v>
+        <v>16.15</v>
       </c>
       <c r="N283">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="O283" t="str">
         <v>mudithaj</v>
@@ -13702,19 +13702,19 @@
     </row>
     <row r="284">
       <c r="A284" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B284" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C284" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D284" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E284" t="str">
-        <v>Attach set band collar</v>
+        <v>Attach waistband - curved</v>
       </c>
       <c r="F284" t="str">
         <v>SNL</v>
@@ -13735,33 +13735,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L284">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M284">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N284">
-        <v>0.68</v>
+        <v>1.2</v>
       </c>
       <c r="O284" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B285" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C285" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D285" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E285" t="str">
-        <v>Attach sleeve</v>
+        <v>Join inseam double stitch</v>
       </c>
       <c r="F285" t="str">
         <v>SNL</v>
@@ -13782,36 +13782,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L285">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M285">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N285">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="O285" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B286" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C286" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D286" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E286" t="str">
-        <v>Attach thearraway to arm hole</v>
+        <v>Outseam overlock &amp; topstitch</v>
       </c>
       <c r="F286" t="str">
-        <v>SNL</v>
+        <v>3O/L</v>
       </c>
       <c r="G286" t="str">
         <v>Sewing</v>
@@ -13829,36 +13829,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L286">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M286">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N286">
-        <v>2</v>
+        <v>0.85</v>
       </c>
       <c r="O286" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B287" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C287" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D287" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E287" t="str">
-        <v>Attach thearraway to hem</v>
+        <v>Attach zipper to fly</v>
       </c>
       <c r="F287" t="str">
-        <v>SNL</v>
+        <v>SNNF</v>
       </c>
       <c r="G287" t="str">
         <v>Sewing</v>
@@ -13876,36 +13876,36 @@
         <v>2026-05-22</v>
       </c>
       <c r="L287">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M287">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N287">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="O287" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B288" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C288" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D288" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E288" t="str">
-        <v>Tag sleeve before attach</v>
+        <v>Hem bottom with blind stitch</v>
       </c>
       <c r="F288" t="str">
-        <v>SNLU</v>
+        <v>SNL</v>
       </c>
       <c r="G288" t="str">
         <v>Sewing</v>
@@ -13923,39 +13923,39 @@
         <v>2026-05-22</v>
       </c>
       <c r="L288">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M288">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N288">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="O288" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B289" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C289" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D289" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E289" t="str">
-        <v>Thread trim &amp; broken stitch check</v>
+        <v>Bartack pocket corners</v>
       </c>
       <c r="F289" t="str">
-        <v>SNL</v>
+        <v>ASNL</v>
       </c>
       <c r="G289" t="str">
-        <v>Finishing</v>
+        <v>Sewing</v>
       </c>
       <c r="H289" t="str">
         <v>STAR GARMENTS (PVT) LIMITED-SGL</v>
@@ -13970,33 +13970,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L289">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M289">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N289">
-        <v>1.5</v>
+        <v>0.45</v>
       </c>
       <c r="O289" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B290" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C290" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D290" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E290" t="str">
-        <v>Button attach (5 buttons)</v>
+        <v>Thread trimming full garment</v>
       </c>
       <c r="F290" t="str">
         <v>SNL</v>
@@ -14017,33 +14017,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L290">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M290">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N290">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="O290" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B291" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C291" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D291" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E291" t="str">
-        <v>Steam press collar &amp; cuff</v>
+        <v>Press leg crease both sides</v>
       </c>
       <c r="F291" t="str">
         <v>VIR</v>
@@ -14064,33 +14064,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L291">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M291">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N291">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="O291" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B292" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C292" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D292" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E292" t="str">
-        <v>Final press body &amp; sleeves</v>
+        <v>Final press &amp; steam waistband</v>
       </c>
       <c r="F292" t="str">
         <v>VIR</v>
@@ -14111,33 +14111,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L292">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M292">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N292">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O292" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B293" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C293" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D293" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E293" t="str">
-        <v>Attach woven label &amp; care label</v>
+        <v>Attach main &amp; care label</v>
       </c>
       <c r="F293" t="str">
         <v>HELP</v>
@@ -14158,33 +14158,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L293">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M293">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N293">
-        <v>0.7</v>
+        <v>0.75</v>
       </c>
       <c r="O293" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B294" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C294" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D294" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E294" t="str">
-        <v>Hang tag attach both sides</v>
+        <v>Measurement check &amp; hang tag</v>
       </c>
       <c r="F294" t="str">
         <v>HELP</v>
@@ -14205,33 +14205,33 @@
         <v>2026-05-22</v>
       </c>
       <c r="L294">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M294">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N294">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="O294" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="str">
-        <v>847</v>
+        <v>910</v>
       </c>
       <c r="B295" t="str">
-        <v>6882T::BL</v>
+        <v>3524P::PN</v>
       </c>
       <c r="C295" t="str">
-        <v>Blouse</v>
+        <v>Pant</v>
       </c>
       <c r="D295" t="str">
-        <v>BL::MX RT</v>
+        <v>PN::EU RT</v>
       </c>
       <c r="E295" t="str">
-        <v>Fold, insert board &amp; poly bag</v>
+        <v>Fold, board insert &amp; poly bag</v>
       </c>
       <c r="F295" t="str">
         <v>HELP</v>
@@ -14252,16 +14252,16 @@
         <v>2026-05-22</v>
       </c>
       <c r="L295">
-        <v>2190</v>
+        <v>1890</v>
       </c>
       <c r="M295">
-        <v>17.96</v>
+        <v>14</v>
       </c>
       <c r="N295">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="O295" t="str">
-        <v>mudithaj</v>
+        <v>priyanthi</v>
       </c>
     </row>
     <row r="296">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -13071,10 +13071,10 @@
         <v>3</v>
       </c>
       <c r="J270" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K270" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L270">
         <v>646</v>
@@ -13118,10 +13118,10 @@
         <v>3</v>
       </c>
       <c r="J271" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K271" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L271">
         <v>646</v>
@@ -13165,10 +13165,10 @@
         <v>3</v>
       </c>
       <c r="J272" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K272" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L272">
         <v>646</v>
@@ -13212,10 +13212,10 @@
         <v>3</v>
       </c>
       <c r="J273" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K273" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L273">
         <v>646</v>
@@ -13259,10 +13259,10 @@
         <v>3</v>
       </c>
       <c r="J274" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K274" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L274">
         <v>646</v>
@@ -13306,10 +13306,10 @@
         <v>3</v>
       </c>
       <c r="J275" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K275" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L275">
         <v>646</v>
@@ -13353,10 +13353,10 @@
         <v>3</v>
       </c>
       <c r="J276" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K276" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L276">
         <v>646</v>
@@ -13400,10 +13400,10 @@
         <v>3</v>
       </c>
       <c r="J277" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K277" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L277">
         <v>646</v>
@@ -13447,10 +13447,10 @@
         <v>3</v>
       </c>
       <c r="J278" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K278" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L278">
         <v>646</v>
@@ -13494,10 +13494,10 @@
         <v>3</v>
       </c>
       <c r="J279" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K279" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L279">
         <v>646</v>
@@ -13541,10 +13541,10 @@
         <v>3</v>
       </c>
       <c r="J280" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K280" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L280">
         <v>646</v>
@@ -13588,10 +13588,10 @@
         <v>3</v>
       </c>
       <c r="J281" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K281" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L281">
         <v>646</v>
@@ -13635,10 +13635,10 @@
         <v>3</v>
       </c>
       <c r="J282" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K282" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L282">
         <v>646</v>
@@ -13682,10 +13682,10 @@
         <v>3</v>
       </c>
       <c r="J283" t="str">
-        <v>2026-05-13</v>
+        <v>2026-05-15</v>
       </c>
       <c r="K283" t="str">
-        <v>2026-05-14</v>
+        <v>2026-05-18</v>
       </c>
       <c r="L283">
         <v>646</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -4290,7 +4290,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>SGL 03</v>
+        <v>SGL 01</v>
       </c>
       <c r="B63">
         <v>847</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>SGL 03</v>
+        <v>SGL 01</v>
       </c>
       <c r="B64">
         <v>847</v>
@@ -4408,7 +4408,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>SGL 08</v>
+        <v>SGL 01</v>
       </c>
       <c r="B65">
         <v>847</v>
@@ -4467,7 +4467,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>SGL 08</v>
+        <v>SGL 01</v>
       </c>
       <c r="B66">
         <v>847</v>
@@ -4526,7 +4526,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>SGL 08</v>
+        <v>SGL 01</v>
       </c>
       <c r="B67">
         <v>847</v>
@@ -4585,7 +4585,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>SGL 08</v>
+        <v>SGL 01</v>
       </c>
       <c r="B68">
         <v>847</v>
@@ -4644,7 +4644,7 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B69">
         <v>847</v>
@@ -4703,7 +4703,7 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B70">
         <v>847</v>
@@ -6778,7 +6778,7 @@
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="B104">
         <v>820</v>
@@ -6846,7 +6846,7 @@
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="B105">
         <v>820</v>
@@ -6914,7 +6914,7 @@
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="C106" t="str">
         <v>BOT12550NA::SGSGBONOB2876::JK</v>
@@ -6941,10 +6941,10 @@
         <v>46191</v>
       </c>
       <c r="S106">
-        <v>46190</v>
+        <v>46193</v>
       </c>
       <c r="T106">
-        <v>46198</v>
+        <v>46203</v>
       </c>
       <c r="V106" t="str">
         <v>460 Minol Ridmaka</v>
@@ -7708,7 +7708,7 @@
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="B119">
         <v>847</v>
@@ -7767,7 +7767,7 @@
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="B120">
         <v>847</v>
@@ -7826,7 +7826,7 @@
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>SGL 08</v>
+        <v>SGL 02</v>
       </c>
       <c r="B121">
         <v>847</v>
@@ -7885,7 +7885,7 @@
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>SGL 08</v>
+        <v>SGL 02</v>
       </c>
       <c r="B122">
         <v>847</v>
@@ -7944,7 +7944,7 @@
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>SGL 08</v>
+        <v>SGL 02</v>
       </c>
       <c r="B123">
         <v>847</v>
@@ -10811,7 +10811,7 @@
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>SGL 08</v>
+        <v>SGL 03</v>
       </c>
       <c r="B172">
         <v>847</v>
@@ -10870,7 +10870,7 @@
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>SGL 08</v>
+        <v>SGL 03</v>
       </c>
       <c r="B173">
         <v>847</v>
@@ -11242,7 +11242,7 @@
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B179">
         <v>539</v>
@@ -11307,7 +11307,7 @@
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B180">
         <v>539</v>
@@ -11372,7 +11372,7 @@
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B181">
         <v>539</v>
@@ -11437,7 +11437,7 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B182">
         <v>539</v>
@@ -11502,7 +11502,7 @@
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B183">
         <v>539</v>
@@ -11567,7 +11567,7 @@
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B184">
         <v>539</v>
@@ -11632,7 +11632,7 @@
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="C185" t="str">
         <v>240754::SGSGMADWL2702::JK</v>
@@ -11662,7 +11662,7 @@
         <v>46174</v>
       </c>
       <c r="T185">
-        <v>46192</v>
+        <v>46193</v>
       </c>
       <c r="W185">
         <v>46181</v>
@@ -14728,7 +14728,7 @@
     </row>
     <row r="245">
       <c r="A245" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="B245">
         <v>547</v>
@@ -14790,7 +14790,7 @@
     </row>
     <row r="246">
       <c r="A246" t="str">
-        <v>SGL 09</v>
+        <v>SGL 04</v>
       </c>
       <c r="C246" t="str">
         <v>558845X::OVOVLE-BO4518::BZ</v>
@@ -14817,10 +14817,10 @@
         <v>46231</v>
       </c>
       <c r="S246">
-        <v>46244</v>
+        <v>46233</v>
       </c>
       <c r="T246">
-        <v>46245</v>
+        <v>46235</v>
       </c>
       <c r="W246">
         <v>46247</v>
@@ -19814,7 +19814,7 @@
     </row>
     <row r="340">
       <c r="A340" t="str">
-        <v>SGL 08</v>
+        <v>SGL 05</v>
       </c>
       <c r="B340">
         <v>847</v>
@@ -19873,7 +19873,7 @@
     </row>
     <row r="341">
       <c r="A341" t="str">
-        <v>SGL 08</v>
+        <v>SGL 05</v>
       </c>
       <c r="B341">
         <v>847</v>
@@ -19932,7 +19932,7 @@
     </row>
     <row r="342">
       <c r="A342" t="str">
-        <v>SGL 08</v>
+        <v>SGL 05</v>
       </c>
       <c r="C342" t="str">
         <v>INQZIM RS27 DRS</v>
@@ -19959,7 +19959,7 @@
         <v>46258</v>
       </c>
       <c r="S342">
-        <v>46288</v>
+        <v>46260</v>
       </c>
       <c r="T342">
         <v>46290</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1370,7 +1370,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1438,7 +1438,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1506,7 +1506,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1574,7 +1574,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1642,7 +1642,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1778,7 +1778,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1846,7 +1846,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2050,7 +2050,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2118,7 +2118,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2213,10 +2213,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46170</v>
+        <v>46204</v>
       </c>
       <c r="T28">
-        <v>46179</v>
+        <v>46213</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -2216,7 +2216,7 @@
         <v>46204</v>
       </c>
       <c r="T28">
-        <v>46213</v>
+        <v>46212</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,8 +32,20 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="13">
+    <numFmt numFmtId="5" formatCode="&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="6" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="8" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="41" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="_(&quot;$&quot;#,##0_);\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="165" formatCode="_(&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+    <numFmt numFmtId="166" formatCode="_(&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="167" formatCode="_(&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1370,7 +1382,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1438,7 +1450,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1506,7 +1518,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1574,7 +1586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1642,7 +1654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1710,7 +1722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1778,7 +1790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1846,7 +1858,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1914,7 +1926,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1982,7 +1994,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2050,7 +2062,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2118,7 +2130,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2186,7 +2198,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2213,10 +2225,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46204</v>
+        <v>46171</v>
       </c>
       <c r="T28">
-        <v>46212</v>
+        <v>46179</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1382,7 +1382,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1518,7 +1518,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1722,7 +1722,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1858,7 +1858,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1926,7 +1926,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1994,7 +1994,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2062,7 +2062,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2130,7 +2130,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2225,10 +2225,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46171</v>
+        <v>46204</v>
       </c>
       <c r="T28">
-        <v>46179</v>
+        <v>46212</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -409,7 +409,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:W526"/>
+  <dimension ref="A1:X526"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -481,6 +481,9 @@
       <c r="W1" t="str">
         <v>Del Date</v>
       </c>
+      <c r="X1" t="str">
+        <v>SGL_MergeGroup</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -1382,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1450,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1518,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1586,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1654,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1722,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1790,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1858,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1926,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1994,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2062,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2130,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2198,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2225,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46204</v>
+        <v>46171</v>
       </c>
       <c r="T28">
-        <v>46212</v>
+        <v>46179</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -30310,7 +30313,7 @@
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:W526"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:X526"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -10997,6 +10997,9 @@
       <c r="W174">
         <v>46205</v>
       </c>
+      <c r="X174" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -11065,6 +11068,9 @@
       <c r="W175">
         <v>46205</v>
       </c>
+      <c r="X175" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -11106,6 +11112,9 @@
       <c r="W176">
         <v>46205</v>
       </c>
+      <c r="X176" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -11174,6 +11183,9 @@
       <c r="W177">
         <v>46205</v>
       </c>
+      <c r="X177" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -11215,6 +11227,9 @@
       <c r="W178">
         <v>46205</v>
       </c>
+      <c r="X178" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -11283,6 +11298,9 @@
       <c r="W179">
         <v>46205</v>
       </c>
+      <c r="X179" t="str">
+        <v>MG-7utvvn</v>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -11323,6 +11341,9 @@
       </c>
       <c r="W180">
         <v>46205</v>
+      </c>
+      <c r="X180" t="str">
+        <v>MG-7utvvn</v>
       </c>
     </row>
     <row r="181">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -10932,7 +10932,7 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="B174">
         <v>212</v>
@@ -10998,12 +10998,12 @@
         <v>46205</v>
       </c>
       <c r="X174" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="B175">
         <v>212</v>
@@ -11069,12 +11069,12 @@
         <v>46205</v>
       </c>
       <c r="X175" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="C176" t="str">
         <v>556959R/R1::OVOVLANED3016::FJK</v>
@@ -11101,10 +11101,10 @@
         <v>46191</v>
       </c>
       <c r="S176">
-        <v>46193</v>
+        <v>46204</v>
       </c>
       <c r="T176">
-        <v>46198</v>
+        <v>46207</v>
       </c>
       <c r="V176" t="str">
         <v>710 Shimara Himahansi</v>
@@ -11113,12 +11113,12 @@
         <v>46205</v>
       </c>
       <c r="X176" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="B177">
         <v>212</v>
@@ -11184,12 +11184,12 @@
         <v>46205</v>
       </c>
       <c r="X177" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="C178" t="str">
         <v>556959S/R1::OVOVLANED3017::FJK</v>
@@ -11216,10 +11216,10 @@
         <v>46196</v>
       </c>
       <c r="S178">
-        <v>46198</v>
+        <v>46209</v>
       </c>
       <c r="T178">
-        <v>46199</v>
+        <v>46209</v>
       </c>
       <c r="V178" t="str">
         <v>710 Shimara Himahansi</v>
@@ -11228,12 +11228,12 @@
         <v>46205</v>
       </c>
       <c r="X178" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="B179">
         <v>212</v>
@@ -11299,12 +11299,12 @@
         <v>46205</v>
       </c>
       <c r="X179" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>SGL 04</v>
+        <v>SGL 02</v>
       </c>
       <c r="C180" t="str">
         <v>556959L/R1::OVOVLANED3018::FJK</v>
@@ -11331,10 +11331,10 @@
         <v>46197</v>
       </c>
       <c r="S180">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="T180">
-        <v>46199</v>
+        <v>46210</v>
       </c>
       <c r="V180" t="str">
         <v>710 Shimara Himahansi</v>
@@ -11343,7 +11343,7 @@
         <v>46205</v>
       </c>
       <c r="X180" t="str">
-        <v>MG-7utvvn</v>
+        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="181">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -10997,9 +10997,6 @@
       <c r="W174">
         <v>46205</v>
       </c>
-      <c r="X174" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -11068,9 +11065,6 @@
       <c r="W175">
         <v>46205</v>
       </c>
-      <c r="X175" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -11112,9 +11106,6 @@
       <c r="W176">
         <v>46205</v>
       </c>
-      <c r="X176" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -11183,9 +11174,6 @@
       <c r="W177">
         <v>46205</v>
       </c>
-      <c r="X177" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -11227,9 +11215,6 @@
       <c r="W178">
         <v>46205</v>
       </c>
-      <c r="X178" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -11298,9 +11283,6 @@
       <c r="W179">
         <v>46205</v>
       </c>
-      <c r="X179" t="str">
-        <v>MG-e8x14v</v>
-      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -11341,9 +11323,6 @@
       </c>
       <c r="W180">
         <v>46205</v>
-      </c>
-      <c r="X180" t="str">
-        <v>MG-e8x14v</v>
       </c>
     </row>
     <row r="181">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46171</v>
+        <v>46211</v>
       </c>
       <c r="T28">
-        <v>46179</v>
+        <v>46219</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46211</v>
+        <v>46171</v>
       </c>
       <c r="T28">
-        <v>46219</v>
+        <v>46179</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46171</v>
+        <v>46210</v>
       </c>
       <c r="T28">
-        <v>46179</v>
+        <v>46218</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46210</v>
+        <v>46171</v>
       </c>
       <c r="T28">
-        <v>46218</v>
+        <v>46179</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -12598,6 +12598,9 @@
       <c r="W205">
         <v>46219</v>
       </c>
+      <c r="X205" t="str">
+        <v>MG-r1bjbb</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -12639,6 +12642,9 @@
       <c r="W206">
         <v>46219</v>
       </c>
+      <c r="X206" t="str">
+        <v>MG-r1bjbb</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -12707,6 +12713,9 @@
       <c r="W207">
         <v>46219</v>
       </c>
+      <c r="X207" t="str">
+        <v>MG-r1bjbb</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -12748,6 +12757,9 @@
       <c r="W208">
         <v>46219</v>
       </c>
+      <c r="X208" t="str">
+        <v>MG-r1bjbb</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -12816,6 +12828,9 @@
       <c r="W209">
         <v>46219</v>
       </c>
+      <c r="X209" t="str">
+        <v>MG-r1bjbb</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -12856,6 +12871,9 @@
       </c>
       <c r="W210">
         <v>46219</v>
+      </c>
+      <c r="X210" t="str">
+        <v>MG-r1bjbb</v>
       </c>
     </row>
     <row r="211">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -12598,9 +12598,6 @@
       <c r="W205">
         <v>46219</v>
       </c>
-      <c r="X205" t="str">
-        <v>MG-r1bjbb</v>
-      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -12642,9 +12639,6 @@
       <c r="W206">
         <v>46219</v>
       </c>
-      <c r="X206" t="str">
-        <v>MG-r1bjbb</v>
-      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -12713,9 +12707,6 @@
       <c r="W207">
         <v>46219</v>
       </c>
-      <c r="X207" t="str">
-        <v>MG-r1bjbb</v>
-      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -12757,9 +12748,6 @@
       <c r="W208">
         <v>46219</v>
       </c>
-      <c r="X208" t="str">
-        <v>MG-r1bjbb</v>
-      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -12828,9 +12816,6 @@
       <c r="W209">
         <v>46219</v>
       </c>
-      <c r="X209" t="str">
-        <v>MG-r1bjbb</v>
-      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -12871,9 +12856,6 @@
       </c>
       <c r="W210">
         <v>46219</v>
-      </c>
-      <c r="X210" t="str">
-        <v>MG-r1bjbb</v>
       </c>
     </row>
     <row r="211">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -12598,6 +12598,9 @@
       <c r="W205">
         <v>46219</v>
       </c>
+      <c r="X205" t="str">
+        <v>MG-0kqtxu</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -12639,6 +12642,9 @@
       <c r="W206">
         <v>46219</v>
       </c>
+      <c r="X206" t="str">
+        <v>MG-0kqtxu</v>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -12707,6 +12713,9 @@
       <c r="W207">
         <v>46219</v>
       </c>
+      <c r="X207" t="str">
+        <v>MG-0kqtxu</v>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -12748,6 +12757,9 @@
       <c r="W208">
         <v>46219</v>
       </c>
+      <c r="X208" t="str">
+        <v>MG-0kqtxu</v>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -12816,6 +12828,9 @@
       <c r="W209">
         <v>46219</v>
       </c>
+      <c r="X209" t="str">
+        <v>MG-0kqtxu</v>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -12856,6 +12871,9 @@
       </c>
       <c r="W210">
         <v>46219</v>
+      </c>
+      <c r="X210" t="str">
+        <v>MG-0kqtxu</v>
       </c>
     </row>
     <row r="211">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46211</v>
+        <v>46170</v>
       </c>
       <c r="T28">
-        <v>46219</v>
+        <v>46178</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1385,7 +1385,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1453,7 +1453,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1521,7 +1521,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1657,7 +1657,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1793,7 +1793,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1861,7 +1861,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1929,7 +1929,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B24">
         <v>847</v>
@@ -1997,7 +1997,7 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B25">
         <v>847</v>
@@ -2065,7 +2065,7 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B26">
         <v>847</v>
@@ -2133,7 +2133,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B27">
         <v>847</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C28" t="str">
         <v>9676T::SGSGZIMER4233::BL</v>
@@ -2228,10 +2228,10 @@
         <v>-</v>
       </c>
       <c r="S28">
-        <v>46170</v>
+        <v>46211</v>
       </c>
       <c r="T28">
-        <v>46178</v>
+        <v>46219</v>
       </c>
       <c r="V28" t="str">
         <v>1675 Dinusha Guantillake</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -21957,10 +21956,10 @@
         <v>46214</v>
       </c>
       <c r="S382">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="T382">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="V382" t="str">
         <v>491 Nilu Udunuwaraarachchi</v>
@@ -22066,10 +22065,10 @@
         <v>46216</v>
       </c>
       <c r="S384">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="T384">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="V384" t="str">
         <v>491 Nilu Udunuwaraarachchi</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,9 +32,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B9">
         <v>847</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B10">
         <v>847</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B11">
         <v>847</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B12">
         <v>847</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B13">
         <v>847</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B14">
         <v>847</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B15">
         <v>847</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C16" t="str">
         <v>0794A::SGSGZIMER5207::SH</v>
@@ -1379,10 +1379,10 @@
         <v>46221</v>
       </c>
       <c r="S16">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="T16">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="V16" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1875,10 +1875,10 @@
         <v>46225</v>
       </c>
       <c r="S24">
+        <v>46225</v>
+      </c>
+      <c r="T24">
         <v>46227</v>
-      </c>
-      <c r="T24">
-        <v>46231</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2664,10 +2664,10 @@
         <v>46223</v>
       </c>
       <c r="S36">
+        <v>46228</v>
+      </c>
+      <c r="T36">
         <v>46231</v>
-      </c>
-      <c r="T36">
-        <v>46234</v>
       </c>
       <c r="V36" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3420,10 +3420,10 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="T48">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="V48" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3591,10 +3591,10 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="T51">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="V51" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3697,10 +3697,10 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="T53">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="V53" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3797,10 +3797,10 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="T55">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="V55" t="str">
         <v>275 Hashan De Mel</v>
@@ -4334,10 +4334,10 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="T64">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="W64">
         <v>46279</v>
@@ -4974,10 +4974,10 @@
         <v>46224</v>
       </c>
       <c r="S75">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="T75">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5763,10 +5763,10 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46230</v>
+        <v>46235</v>
       </c>
       <c r="T87">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="V87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6620,10 +6620,10 @@
         <v>46239</v>
       </c>
       <c r="S100">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="T100">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="V100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7343,10 +7343,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="T112">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -897,7 +897,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B9">
         <v>847</v>
@@ -962,7 +962,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B10">
         <v>847</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B11">
         <v>847</v>
@@ -1092,7 +1092,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B12">
         <v>847</v>
@@ -1157,7 +1157,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B13">
         <v>847</v>
@@ -1222,7 +1222,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B14">
         <v>847</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B15">
         <v>847</v>
@@ -1352,7 +1352,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C16" t="str">
         <v>0794A::SGSGZIMER5207::SH</v>
@@ -1379,10 +1379,10 @@
         <v>46221</v>
       </c>
       <c r="S16">
+        <v>46224</v>
+      </c>
+      <c r="T16">
         <v>46227</v>
-      </c>
-      <c r="T16">
-        <v>46231</v>
       </c>
       <c r="V16" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1875,10 +1875,10 @@
         <v>46225</v>
       </c>
       <c r="S24">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="T24">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2664,10 +2664,10 @@
         <v>46223</v>
       </c>
       <c r="S36">
-        <v>46228</v>
+        <v>46231</v>
       </c>
       <c r="T36">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="V36" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3420,10 +3420,10 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="T48">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="V48" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3591,10 +3591,10 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="T51">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="V51" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3697,10 +3697,10 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="T53">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="V53" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3797,10 +3797,10 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="T55">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="V55" t="str">
         <v>275 Hashan De Mel</v>
@@ -4334,10 +4334,10 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="T64">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="W64">
         <v>46279</v>
@@ -4974,10 +4974,10 @@
         <v>46224</v>
       </c>
       <c r="S75">
-        <v>46232</v>
+        <v>46226</v>
       </c>
       <c r="T75">
-        <v>46234</v>
+        <v>46230</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5763,10 +5763,10 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46235</v>
+        <v>46230</v>
       </c>
       <c r="T87">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="V87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6620,10 +6620,10 @@
         <v>46239</v>
       </c>
       <c r="S100">
-        <v>46247</v>
+        <v>46241</v>
       </c>
       <c r="T100">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="V100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7343,10 +7343,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="T112">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,8 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -10919,6 +10920,9 @@
       <c r="W174">
         <v>46224</v>
       </c>
+      <c r="X174" t="str">
+        <v>MG-unf9oe</v>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -10957,6 +10961,9 @@
       <c r="W175">
         <v>46224</v>
       </c>
+      <c r="X175" t="str">
+        <v>MG-unf9oe</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -11019,6 +11026,9 @@
       <c r="W176">
         <v>46226</v>
       </c>
+      <c r="X176" t="str">
+        <v>MG-unf9oe</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -11056,6 +11066,9 @@
       </c>
       <c r="W177">
         <v>46226</v>
+      </c>
+      <c r="X177" t="str">
+        <v>MG-unf9oe</v>
       </c>
     </row>
     <row r="178">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -10920,9 +10920,6 @@
       <c r="W174">
         <v>46224</v>
       </c>
-      <c r="X174" t="str">
-        <v>MG-unf9oe</v>
-      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -10961,9 +10958,6 @@
       <c r="W175">
         <v>46224</v>
       </c>
-      <c r="X175" t="str">
-        <v>MG-unf9oe</v>
-      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -11026,9 +11020,6 @@
       <c r="W176">
         <v>46226</v>
       </c>
-      <c r="X176" t="str">
-        <v>MG-unf9oe</v>
-      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -11066,9 +11057,6 @@
       </c>
       <c r="W177">
         <v>46226</v>
-      </c>
-      <c r="X177" t="str">
-        <v>MG-unf9oe</v>
       </c>
     </row>
     <row r="178">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B9">
         <v>847</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B10">
         <v>847</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B11">
         <v>847</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B12">
         <v>847</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B13">
         <v>847</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B14">
         <v>847</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B15">
         <v>847</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C16" t="str">
         <v>0794A::SGSGZIMER5207::SH</v>
@@ -1380,10 +1380,10 @@
         <v>46221</v>
       </c>
       <c r="S16">
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="T16">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="V16" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1876,10 +1876,10 @@
         <v>46225</v>
       </c>
       <c r="S24">
+        <v>46225</v>
+      </c>
+      <c r="T24">
         <v>46227</v>
-      </c>
-      <c r="T24">
-        <v>46231</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2665,10 +2665,10 @@
         <v>46223</v>
       </c>
       <c r="S36">
+        <v>46228</v>
+      </c>
+      <c r="T36">
         <v>46231</v>
-      </c>
-      <c r="T36">
-        <v>46234</v>
       </c>
       <c r="V36" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3421,10 +3421,10 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46234</v>
+        <v>46232</v>
       </c>
       <c r="T48">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="V48" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3592,10 +3592,10 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46241</v>
+        <v>46239</v>
       </c>
       <c r="T51">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="V51" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3698,10 +3698,10 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46248</v>
+        <v>46246</v>
       </c>
       <c r="T53">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="V53" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3798,10 +3798,10 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46251</v>
+        <v>46248</v>
       </c>
       <c r="T55">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="V55" t="str">
         <v>275 Hashan De Mel</v>
@@ -4335,10 +4335,10 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46258</v>
+        <v>46255</v>
       </c>
       <c r="T64">
-        <v>46265</v>
+        <v>46261</v>
       </c>
       <c r="W64">
         <v>46279</v>
@@ -4975,10 +4975,10 @@
         <v>46224</v>
       </c>
       <c r="S75">
-        <v>46226</v>
+        <v>46232</v>
       </c>
       <c r="T75">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5764,10 +5764,10 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46230</v>
+        <v>46235</v>
       </c>
       <c r="T87">
-        <v>46241</v>
+        <v>46246</v>
       </c>
       <c r="V87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6621,10 +6621,10 @@
         <v>46239</v>
       </c>
       <c r="S100">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="T100">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="V100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7344,10 +7344,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="T112">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -898,7 +898,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B9">
         <v>847</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B10">
         <v>847</v>
@@ -1028,7 +1028,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B11">
         <v>847</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B12">
         <v>847</v>
@@ -1158,7 +1158,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B13">
         <v>847</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B14">
         <v>847</v>
@@ -1288,7 +1288,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B15">
         <v>847</v>
@@ -1353,7 +1353,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C16" t="str">
         <v>0794A::SGSGZIMER5207::SH</v>
@@ -1380,10 +1380,10 @@
         <v>46221</v>
       </c>
       <c r="S16">
+        <v>46224</v>
+      </c>
+      <c r="T16">
         <v>46227</v>
-      </c>
-      <c r="T16">
-        <v>46231</v>
       </c>
       <c r="V16" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1876,10 +1876,10 @@
         <v>46225</v>
       </c>
       <c r="S24">
-        <v>46225</v>
+        <v>46228</v>
       </c>
       <c r="T24">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2665,10 +2665,10 @@
         <v>46223</v>
       </c>
       <c r="S36">
-        <v>46228</v>
+        <v>46237</v>
       </c>
       <c r="T36">
-        <v>46231</v>
+        <v>46239</v>
       </c>
       <c r="V36" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3421,10 +3421,10 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46232</v>
+        <v>46240</v>
       </c>
       <c r="T48">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="V48" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3592,10 +3592,10 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46239</v>
+        <v>46247</v>
       </c>
       <c r="T51">
-        <v>46245</v>
+        <v>46253</v>
       </c>
       <c r="V51" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3698,10 +3698,10 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="T53">
-        <v>46247</v>
+        <v>46255</v>
       </c>
       <c r="V53" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3798,10 +3798,10 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46248</v>
+        <v>46256</v>
       </c>
       <c r="T55">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="V55" t="str">
         <v>275 Hashan De Mel</v>
@@ -4335,10 +4335,10 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46255</v>
+        <v>46263</v>
       </c>
       <c r="T64">
-        <v>46261</v>
+        <v>46269</v>
       </c>
       <c r="W64">
         <v>46279</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B72">
         <v>847</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B73">
         <v>847</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B74">
         <v>847</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C75" t="str">
         <v>3497A::SGSGZIMER5060::SH</v>
@@ -4978,7 +4978,7 @@
         <v>46232</v>
       </c>
       <c r="T75">
-        <v>46234</v>
+        <v>46235</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5764,10 +5764,10 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46235</v>
+        <v>46227</v>
       </c>
       <c r="T87">
-        <v>46246</v>
+        <v>46238</v>
       </c>
       <c r="V87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6621,10 +6621,10 @@
         <v>46239</v>
       </c>
       <c r="S100">
+        <v>46239</v>
+      </c>
+      <c r="T100">
         <v>46247</v>
-      </c>
-      <c r="T100">
-        <v>46255</v>
       </c>
       <c r="V100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7344,10 +7344,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46256</v>
+        <v>46248</v>
       </c>
       <c r="T112">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1394,7 +1394,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1719,7 +1719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C24" t="str">
         <v>0795T::SGSGZIMER5208::BL</v>
@@ -1876,10 +1876,10 @@
         <v>46225</v>
       </c>
       <c r="S24">
-        <v>46228</v>
+        <v>46227</v>
       </c>
       <c r="T24">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2665,10 +2665,10 @@
         <v>46223</v>
       </c>
       <c r="S36">
-        <v>46237</v>
+        <v>46232</v>
       </c>
       <c r="T36">
-        <v>46239</v>
+        <v>46234</v>
       </c>
       <c r="V36" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3421,10 +3421,10 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46240</v>
+        <v>46235</v>
       </c>
       <c r="T48">
-        <v>46246</v>
+        <v>46241</v>
       </c>
       <c r="V48" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -3592,10 +3592,10 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46247</v>
+        <v>46242</v>
       </c>
       <c r="T51">
-        <v>46253</v>
+        <v>46248</v>
       </c>
       <c r="V51" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3698,10 +3698,10 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46254</v>
+        <v>46249</v>
       </c>
       <c r="T53">
-        <v>46255</v>
+        <v>46251</v>
       </c>
       <c r="V53" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3798,10 +3798,10 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="T55">
-        <v>46262</v>
+        <v>46258</v>
       </c>
       <c r="V55" t="str">
         <v>275 Hashan De Mel</v>
@@ -4335,10 +4335,10 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46263</v>
+        <v>46259</v>
       </c>
       <c r="T64">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="W64">
         <v>46279</v>
@@ -4975,10 +4975,10 @@
         <v>46224</v>
       </c>
       <c r="S75">
-        <v>46232</v>
+        <v>46228</v>
       </c>
       <c r="T75">
-        <v>46235</v>
+        <v>46231</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5764,10 +5764,10 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="T87">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="V87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6621,10 +6621,10 @@
         <v>46239</v>
       </c>
       <c r="S100">
-        <v>46239</v>
+        <v>46242</v>
       </c>
       <c r="T100">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="V100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7344,10 +7344,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="T112">
-        <v>46258</v>
+        <v>46261</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -1394,7 +1394,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1524,7 +1524,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1589,7 +1589,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1654,7 +1654,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B21">
         <v>847</v>
@@ -1719,7 +1719,7 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B22">
         <v>847</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B23">
         <v>847</v>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C24" t="str">
         <v>0795T::SGSGZIMER5208::BL</v>
@@ -1879,7 +1879,7 @@
         <v>46227</v>
       </c>
       <c r="T24">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="V24" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -2665,7 +2665,7 @@
         <v>46223</v>
       </c>
       <c r="S36">
-        <v>46232</v>
+        <v>46231</v>
       </c>
       <c r="T36">
         <v>46234</v>
@@ -3421,7 +3421,7 @@
         <v>46226</v>
       </c>
       <c r="S48">
-        <v>46235</v>
+        <v>46234</v>
       </c>
       <c r="T48">
         <v>46241</v>
@@ -3592,7 +3592,7 @@
         <v>46239</v>
       </c>
       <c r="S51">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="T51">
         <v>46248</v>
@@ -3698,7 +3698,7 @@
         <v>46246</v>
       </c>
       <c r="S53">
-        <v>46249</v>
+        <v>46248</v>
       </c>
       <c r="T53">
         <v>46251</v>
@@ -3798,7 +3798,7 @@
         <v>46248</v>
       </c>
       <c r="S55">
-        <v>46252</v>
+        <v>46251</v>
       </c>
       <c r="T55">
         <v>46258</v>
@@ -4335,7 +4335,7 @@
         <v>46255</v>
       </c>
       <c r="S64">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="T64">
         <v>46265</v>
@@ -4753,7 +4753,7 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B72">
         <v>847</v>
@@ -4818,7 +4818,7 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B73">
         <v>847</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B74">
         <v>847</v>
@@ -4948,7 +4948,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C75" t="str">
         <v>3497A::SGSGZIMER5060::SH</v>
@@ -4975,10 +4975,10 @@
         <v>46224</v>
       </c>
       <c r="S75">
-        <v>46228</v>
+        <v>46226</v>
       </c>
       <c r="T75">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="V75" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -5764,7 +5764,7 @@
         <v>46227</v>
       </c>
       <c r="S87">
-        <v>46231</v>
+        <v>46230</v>
       </c>
       <c r="T87">
         <v>46241</v>
@@ -6621,7 +6621,7 @@
         <v>46239</v>
       </c>
       <c r="S100">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="T100">
         <v>46251</v>
@@ -7344,10 +7344,10 @@
         <v>46251</v>
       </c>
       <c r="S112">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="T112">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="W112">
         <v>46275</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -17698,6 +17698,9 @@
       <c r="W302">
         <v>46240</v>
       </c>
+      <c r="X302" t="str">
+        <v>MG-4628g0</v>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="str">
@@ -17736,6 +17739,9 @@
       <c r="W303">
         <v>46240</v>
       </c>
+      <c r="X303" t="str">
+        <v>MG-4628g0</v>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="str">
@@ -17801,6 +17807,9 @@
       <c r="W304">
         <v>46240</v>
       </c>
+      <c r="X304" t="str">
+        <v>MG-4628g0</v>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="str">
@@ -17838,6 +17847,9 @@
       </c>
       <c r="W305">
         <v>46240</v>
+      </c>
+      <c r="X305" t="str">
+        <v>MG-4628g0</v>
       </c>
     </row>
     <row r="306">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,10 +32,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -5228,7 +5227,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="B74">
         <v>847</v>
@@ -5282,13 +5281,13 @@
         <v>46295</v>
       </c>
       <c r="T74" s="2">
-        <v>0.2986111111111111</v>
+        <v>0.6104166666666667</v>
       </c>
       <c r="U74" s="1">
         <v>46296</v>
       </c>
       <c r="V74" s="2">
-        <v>0.6715277777777777</v>
+        <v>0.5041666666666667</v>
       </c>
       <c r="Y74" s="1">
         <v>46317</v>
@@ -5296,7 +5295,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>SGL 02</v>
+        <v>SGL 01</v>
       </c>
       <c r="C75" t="str">
         <v>3573T/R1-A1::SGSGZIMER6486::BL</v>
@@ -5323,10 +5322,10 @@
         <v>46293</v>
       </c>
       <c r="S75" s="1">
-        <v>46293</v>
+        <v>46295</v>
       </c>
       <c r="U75" s="1">
-        <v>46294</v>
+        <v>46297</v>
       </c>
       <c r="Y75" s="1">
         <v>46317</v>
@@ -8493,7 +8492,7 @@
         <v>46283</v>
       </c>
       <c r="T121" s="2">
-        <v>0.30416666666666664</v>
+        <v>0.5673611111111111</v>
       </c>
       <c r="U121" s="1">
         <v>46283</v>
@@ -8635,7 +8634,7 @@
         <v>46293</v>
       </c>
       <c r="V123" s="2">
-        <v>0.29791666666666666</v>
+        <v>0.5611111111111111</v>
       </c>
       <c r="Y123" s="1">
         <v>46305</v>
@@ -8670,10 +8669,10 @@
         <v>46281</v>
       </c>
       <c r="S124" s="1">
-        <v>46283</v>
+        <v>46266</v>
       </c>
       <c r="U124" s="1">
-        <v>46293</v>
+        <v>46275</v>
       </c>
       <c r="Y124" s="1">
         <v>46305</v>
@@ -8738,13 +8737,13 @@
         <v>46293</v>
       </c>
       <c r="T125" s="2">
-        <v>0.6722222222222223</v>
+        <v>0.5618055555555556</v>
       </c>
       <c r="U125" s="1">
         <v>46301</v>
       </c>
       <c r="V125" s="2">
-        <v>0.38333333333333336</v>
+        <v>0.7520833333333333</v>
       </c>
       <c r="Y125" s="1">
         <v>46305</v>
@@ -8779,10 +8778,10 @@
         <v>46290</v>
       </c>
       <c r="S126" s="1">
-        <v>46294</v>
+        <v>46275</v>
       </c>
       <c r="U126" s="1">
-        <v>46303</v>
+        <v>46283</v>
       </c>
       <c r="Y126" s="1">
         <v>46305</v>
@@ -11640,7 +11639,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="B169">
         <v>547</v>
@@ -11697,13 +11696,13 @@
         <v>46265</v>
       </c>
       <c r="T169" s="2">
-        <v>0.3548611111111111</v>
+        <v>0.42777777777777776</v>
       </c>
       <c r="U169" s="1">
         <v>46266</v>
       </c>
       <c r="V169" s="2">
-        <v>0.49375</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="Y169" s="1">
         <v>46247</v>
@@ -11711,7 +11710,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SGL 03</v>
+        <v>SGL 02</v>
       </c>
       <c r="C170" t="str">
         <v>559784P::OVOVLE-BO4466::BZ</v>
@@ -11806,13 +11805,13 @@
         <v>46266</v>
       </c>
       <c r="T171" s="2">
-        <v>0.49444444444444446</v>
+        <v>0.3548611111111111</v>
       </c>
       <c r="U171" s="1">
         <v>46269</v>
       </c>
       <c r="V171" s="2">
-        <v>0.3819444444444444</v>
+        <v>0.7215277777777778</v>
       </c>
       <c r="Y171" s="1">
         <v>46247</v>
@@ -11847,10 +11846,10 @@
         <v>46263</v>
       </c>
       <c r="S172" s="1">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="U172" s="1">
-        <v>46269</v>
+        <v>46267</v>
       </c>
       <c r="Y172" s="1">
         <v>46247</v>
@@ -11915,13 +11914,13 @@
         <v>46269</v>
       </c>
       <c r="T173" s="2">
-        <v>0.38263888888888886</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="U173" s="1">
         <v>46272</v>
       </c>
       <c r="V173" s="2">
-        <v>0.3215277777777778</v>
+        <v>0.6611111111111111</v>
       </c>
       <c r="Y173" s="1">
         <v>46247</v>
@@ -11956,10 +11955,10 @@
         <v>46267</v>
       </c>
       <c r="S174" s="1">
+        <v>46267</v>
+      </c>
+      <c r="U174" s="1">
         <v>46269</v>
-      </c>
-      <c r="U174" s="1">
-        <v>46272</v>
       </c>
       <c r="Y174" s="1">
         <v>46247</v>
@@ -12021,13 +12020,13 @@
         <v>46283</v>
       </c>
       <c r="T175" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.6618055555555555</v>
       </c>
       <c r="U175" s="1">
         <v>46284</v>
       </c>
       <c r="V175" s="2">
-        <v>0.4388888888888889</v>
+        <v>0.3298611111111111</v>
       </c>
       <c r="X175" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12065,10 +12064,10 @@
         <v>46281</v>
       </c>
       <c r="S176" s="1">
-        <v>46283</v>
+        <v>46269</v>
       </c>
       <c r="U176" s="1">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="X176" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12133,7 +12132,7 @@
         <v>46284</v>
       </c>
       <c r="T177" s="2">
-        <v>0.4395833333333333</v>
+        <v>0.33055555555555555</v>
       </c>
       <c r="U177" s="1">
         <v>46286</v>
@@ -12207,7 +12206,7 @@
         <v>46298</v>
       </c>
       <c r="V178" s="2">
-        <v>0.3736111111111111</v>
+        <v>0.74375</v>
       </c>
       <c r="Y178" s="1">
         <v>46305</v>
@@ -12242,10 +12241,10 @@
         <v>46282</v>
       </c>
       <c r="S179" s="1">
-        <v>46284</v>
+        <v>46272</v>
       </c>
       <c r="U179" s="1">
-        <v>46301</v>
+        <v>46287</v>
       </c>
       <c r="Y179" s="1">
         <v>46305</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -8492,7 +8492,7 @@
         <v>46283</v>
       </c>
       <c r="T121" s="2">
-        <v>0.5673611111111111</v>
+        <v>0.30416666666666664</v>
       </c>
       <c r="U121" s="1">
         <v>46283</v>
@@ -8634,7 +8634,7 @@
         <v>46293</v>
       </c>
       <c r="V123" s="2">
-        <v>0.5611111111111111</v>
+        <v>0.29791666666666666</v>
       </c>
       <c r="Y123" s="1">
         <v>46305</v>
@@ -8669,10 +8669,10 @@
         <v>46281</v>
       </c>
       <c r="S124" s="1">
-        <v>46266</v>
+        <v>46283</v>
       </c>
       <c r="U124" s="1">
-        <v>46275</v>
+        <v>46293</v>
       </c>
       <c r="Y124" s="1">
         <v>46305</v>
@@ -8737,13 +8737,13 @@
         <v>46293</v>
       </c>
       <c r="T125" s="2">
-        <v>0.5618055555555556</v>
+        <v>0.2986111111111111</v>
       </c>
       <c r="U125" s="1">
         <v>46301</v>
       </c>
       <c r="V125" s="2">
-        <v>0.7520833333333333</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="Y125" s="1">
         <v>46305</v>
@@ -8778,10 +8778,10 @@
         <v>46290</v>
       </c>
       <c r="S126" s="1">
-        <v>46275</v>
+        <v>46293</v>
       </c>
       <c r="U126" s="1">
-        <v>46283</v>
+        <v>46301</v>
       </c>
       <c r="Y126" s="1">
         <v>46305</v>
@@ -11639,7 +11639,7 @@
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>SGL 02</v>
+        <v>SGL 03</v>
       </c>
       <c r="B169">
         <v>547</v>
@@ -11696,13 +11696,13 @@
         <v>46265</v>
       </c>
       <c r="T169" s="2">
-        <v>0.42777777777777776</v>
+        <v>0.3548611111111111</v>
       </c>
       <c r="U169" s="1">
         <v>46266</v>
       </c>
       <c r="V169" s="2">
-        <v>0.5666666666666667</v>
+        <v>0.49375</v>
       </c>
       <c r="Y169" s="1">
         <v>46247</v>
@@ -11710,7 +11710,7 @@
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>SGL 02</v>
+        <v>SGL 03</v>
       </c>
       <c r="C170" t="str">
         <v>559784P::OVOVLE-BO4466::BZ</v>
@@ -11805,13 +11805,13 @@
         <v>46266</v>
       </c>
       <c r="T171" s="2">
-        <v>0.3548611111111111</v>
+        <v>0.49444444444444446</v>
       </c>
       <c r="U171" s="1">
         <v>46269</v>
       </c>
       <c r="V171" s="2">
-        <v>0.7215277777777778</v>
+        <v>0.3819444444444444</v>
       </c>
       <c r="Y171" s="1">
         <v>46247</v>
@@ -11846,10 +11846,10 @@
         <v>46263</v>
       </c>
       <c r="S172" s="1">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="U172" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="Y172" s="1">
         <v>46247</v>
@@ -11914,13 +11914,13 @@
         <v>46269</v>
       </c>
       <c r="T173" s="2">
-        <v>0.7222222222222222</v>
+        <v>0.38263888888888886</v>
       </c>
       <c r="U173" s="1">
         <v>46272</v>
       </c>
       <c r="V173" s="2">
-        <v>0.6611111111111111</v>
+        <v>0.3215277777777778</v>
       </c>
       <c r="Y173" s="1">
         <v>46247</v>
@@ -11955,10 +11955,10 @@
         <v>46267</v>
       </c>
       <c r="S174" s="1">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="U174" s="1">
-        <v>46269</v>
+        <v>46272</v>
       </c>
       <c r="Y174" s="1">
         <v>46247</v>
@@ -12020,13 +12020,13 @@
         <v>46283</v>
       </c>
       <c r="T175" s="2">
-        <v>0.6618055555555555</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="U175" s="1">
         <v>46284</v>
       </c>
       <c r="V175" s="2">
-        <v>0.3298611111111111</v>
+        <v>0.4388888888888889</v>
       </c>
       <c r="X175" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12064,10 +12064,10 @@
         <v>46281</v>
       </c>
       <c r="S176" s="1">
-        <v>46269</v>
+        <v>46283</v>
       </c>
       <c r="U176" s="1">
-        <v>46272</v>
+        <v>46284</v>
       </c>
       <c r="X176" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12132,7 +12132,7 @@
         <v>46284</v>
       </c>
       <c r="T177" s="2">
-        <v>0.33055555555555555</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="U177" s="1">
         <v>46286</v>
@@ -12206,7 +12206,7 @@
         <v>46298</v>
       </c>
       <c r="V178" s="2">
-        <v>0.74375</v>
+        <v>0.3736111111111111</v>
       </c>
       <c r="Y178" s="1">
         <v>46305</v>
@@ -12241,10 +12241,10 @@
         <v>46282</v>
       </c>
       <c r="S179" s="1">
-        <v>46272</v>
+        <v>46284</v>
       </c>
       <c r="U179" s="1">
-        <v>46287</v>
+        <v>46301</v>
       </c>
       <c r="Y179" s="1">
         <v>46305</v>
@@ -17748,7 +17748,7 @@
         <v>1515 Sanjaya Mihiran</v>
       </c>
       <c r="Y276" s="1">
-        <v>46219</v>
+        <v>46254</v>
       </c>
     </row>
     <row r="277">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -32,9 +32,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
     <numFmt numFmtId="60" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="M/d/yyyy"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -1010,7 +1011,7 @@
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B10">
         <v>847</v>
@@ -1067,7 +1068,7 @@
         <v>46241</v>
       </c>
       <c r="T10" s="2">
-        <v>0.2951388888888889</v>
+        <v>0.5770833333333333</v>
       </c>
       <c r="U10" s="1">
         <v>46241</v>
@@ -1084,7 +1085,7 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B11">
         <v>847</v>
@@ -1158,7 +1159,7 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B12">
         <v>847</v>
@@ -1232,7 +1233,7 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B13">
         <v>847</v>
@@ -1306,7 +1307,7 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B14">
         <v>847</v>
@@ -1380,7 +1381,7 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B15">
         <v>847</v>
@@ -1454,7 +1455,7 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B16">
         <v>847</v>
@@ -1528,7 +1529,7 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B17">
         <v>847</v>
@@ -1602,7 +1603,7 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B18">
         <v>847</v>
@@ -1676,7 +1677,7 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B19">
         <v>847</v>
@@ -1750,7 +1751,7 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B20">
         <v>847</v>
@@ -1813,7 +1814,7 @@
         <v>46245</v>
       </c>
       <c r="V20" s="2">
-        <v>0.325</v>
+        <v>0.6069444444444444</v>
       </c>
       <c r="X20" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1824,7 +1825,7 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C21" t="str">
         <v>1500P/R1::SGSGZIMER5206::PN</v>
@@ -1851,10 +1852,10 @@
         <v>-</v>
       </c>
       <c r="S21" s="1">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="U21" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="X21" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1922,7 +1923,7 @@
         <v>46245</v>
       </c>
       <c r="T22" s="2">
-        <v>0.32569444444444445</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="U22" s="1">
         <v>46245</v>
@@ -3038,7 +3039,7 @@
         <v>46251</v>
       </c>
       <c r="V37" s="2">
-        <v>0.6930555555555555</v>
+        <v>0.6625</v>
       </c>
       <c r="X37" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3076,10 +3077,10 @@
         <v>46242</v>
       </c>
       <c r="S38" s="1">
-        <v>46245</v>
+        <v>46241</v>
       </c>
       <c r="U38" s="1">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="X38" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3147,7 +3148,7 @@
         <v>46251</v>
       </c>
       <c r="T39" s="2">
-        <v>0.69375</v>
+        <v>0.6631944444444444</v>
       </c>
       <c r="U39" s="1">
         <v>46255</v>
@@ -3650,7 +3651,7 @@
         <v>46259</v>
       </c>
       <c r="V46" s="2">
-        <v>0.5284722222222222</v>
+        <v>0.4979166666666667</v>
       </c>
       <c r="Y46" s="1">
         <v>46266</v>
@@ -3685,10 +3686,10 @@
         <v>46248</v>
       </c>
       <c r="S47" s="1">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="U47" s="1">
-        <v>46259</v>
+        <v>46255</v>
       </c>
       <c r="Y47" s="1">
         <v>46266</v>
@@ -3750,13 +3751,13 @@
         <v>46259</v>
       </c>
       <c r="T48" s="2">
-        <v>0.5291666666666667</v>
+        <v>0.4986111111111111</v>
       </c>
       <c r="U48" s="1">
         <v>46262</v>
       </c>
       <c r="V48" s="2">
-        <v>0.6326388888888889</v>
+        <v>0.6020833333333333</v>
       </c>
       <c r="Y48" s="1">
         <v>46265</v>
@@ -3791,10 +3792,10 @@
         <v>46256</v>
       </c>
       <c r="S49" s="1">
+        <v>46255</v>
+      </c>
+      <c r="U49" s="1">
         <v>46259</v>
-      </c>
-      <c r="U49" s="1">
-        <v>46262</v>
       </c>
       <c r="Y49" s="1">
         <v>46265</v>
@@ -3859,7 +3860,7 @@
         <v>46262</v>
       </c>
       <c r="T50" s="2">
-        <v>0.6333333333333333</v>
+        <v>0.6027777777777777</v>
       </c>
       <c r="U50" s="1">
         <v>46263</v>
@@ -4235,7 +4236,7 @@
         <v>46266</v>
       </c>
       <c r="V55" s="2">
-        <v>0.6055555555555555</v>
+        <v>0.575</v>
       </c>
       <c r="X55" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4273,10 +4274,10 @@
         <v>46260</v>
       </c>
       <c r="S56" s="1">
+        <v>46259</v>
+      </c>
+      <c r="U56" s="1">
         <v>46262</v>
-      </c>
-      <c r="U56" s="1">
-        <v>46266</v>
       </c>
       <c r="X56" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4344,13 +4345,13 @@
         <v>46266</v>
       </c>
       <c r="T57" s="2">
-        <v>0.60625</v>
+        <v>0.5756944444444444</v>
       </c>
       <c r="U57" s="1">
         <v>46267</v>
       </c>
       <c r="V57" s="2">
-        <v>0.48055555555555557</v>
+        <v>0.45</v>
       </c>
       <c r="X57" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4388,10 +4389,10 @@
         <v>46263</v>
       </c>
       <c r="S58" s="1">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="U58" s="1">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="X58" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4456,13 +4457,13 @@
         <v>46267</v>
       </c>
       <c r="T59" s="2">
-        <v>0.48125</v>
+        <v>0.45069444444444445</v>
       </c>
       <c r="U59" s="1">
         <v>46269</v>
       </c>
       <c r="V59" s="2">
-        <v>0.34652777777777777</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="Y59" s="1">
         <v>46277</v>
@@ -4497,10 +4498,10 @@
         <v>46265</v>
       </c>
       <c r="S60" s="1">
-        <v>46267</v>
+        <v>46263</v>
       </c>
       <c r="U60" s="1">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="Y60" s="1">
         <v>46277</v>
@@ -4565,13 +4566,13 @@
         <v>46269</v>
       </c>
       <c r="T61" s="2">
-        <v>0.34791666666666665</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="U61" s="1">
         <v>46276</v>
       </c>
       <c r="V61" s="2">
-        <v>0.3263888888888889</v>
+        <v>0.2951388888888889</v>
       </c>
       <c r="X61" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4609,10 +4610,10 @@
         <v>46267</v>
       </c>
       <c r="S62" s="1">
-        <v>46269</v>
+        <v>46266</v>
       </c>
       <c r="U62" s="1">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="X62" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4680,7 +4681,7 @@
         <v>46276</v>
       </c>
       <c r="T63" s="2">
-        <v>0.32708333333333334</v>
+        <v>0.29583333333333334</v>
       </c>
       <c r="U63" s="1">
         <v>46276</v>
@@ -4757,7 +4758,7 @@
         <v>46279</v>
       </c>
       <c r="V64" s="2">
-        <v>0.33055555555555555</v>
+        <v>0.29930555555555555</v>
       </c>
       <c r="Y64" s="1">
         <v>46298</v>
@@ -4792,10 +4793,10 @@
         <v>46274</v>
       </c>
       <c r="S65" s="1">
-        <v>46276</v>
+        <v>46273</v>
       </c>
       <c r="U65" s="1">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="Y65" s="1">
         <v>46298</v>
@@ -4857,13 +4858,13 @@
         <v>46279</v>
       </c>
       <c r="T66" s="2">
-        <v>0.33125</v>
+        <v>0.3</v>
       </c>
       <c r="U66" s="1">
         <v>46283</v>
       </c>
       <c r="V66" s="2">
-        <v>0.4625</v>
+        <v>0.43125</v>
       </c>
       <c r="Y66" s="1">
         <v>46301</v>
@@ -4898,10 +4899,10 @@
         <v>46276</v>
       </c>
       <c r="S67" s="1">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="U67" s="1">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="Y67" s="1">
         <v>46301</v>
@@ -4963,13 +4964,13 @@
         <v>46283</v>
       </c>
       <c r="T68" s="2">
-        <v>0.46319444444444446</v>
+        <v>0.43194444444444446</v>
       </c>
       <c r="U68" s="1">
         <v>46286</v>
       </c>
       <c r="V68" s="2">
-        <v>0.5381944444444444</v>
+        <v>0.5069444444444444</v>
       </c>
       <c r="Y68" s="1">
         <v>46304</v>
@@ -5004,10 +5005,10 @@
         <v>46281</v>
       </c>
       <c r="S69" s="1">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="U69" s="1">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="Y69" s="1">
         <v>46304</v>
@@ -5069,13 +5070,13 @@
         <v>46286</v>
       </c>
       <c r="T70" s="2">
-        <v>0.5388888888888889</v>
+        <v>0.5076388888888889</v>
       </c>
       <c r="U70" s="1">
         <v>46293</v>
       </c>
       <c r="V70" s="2">
-        <v>0.49444444444444446</v>
+        <v>0.46319444444444446</v>
       </c>
       <c r="Y70" s="1">
         <v>46301</v>
@@ -5110,10 +5111,10 @@
         <v>46283</v>
       </c>
       <c r="S71" s="1">
-        <v>46286</v>
+        <v>46282</v>
       </c>
       <c r="U71" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="Y71" s="1">
         <v>46301</v>
@@ -5175,13 +5176,13 @@
         <v>46293</v>
       </c>
       <c r="T72" s="2">
-        <v>0.4951388888888889</v>
+        <v>0.4638888888888889</v>
       </c>
       <c r="U72" s="1">
         <v>46295</v>
       </c>
       <c r="V72" s="2">
-        <v>0.6097222222222223</v>
+        <v>0.5784722222222223</v>
       </c>
       <c r="Y72" s="1">
         <v>46304</v>
@@ -5216,10 +5217,10 @@
         <v>46290</v>
       </c>
       <c r="S73" s="1">
-        <v>46293</v>
+        <v>46289</v>
       </c>
       <c r="U73" s="1">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="Y73" s="1">
         <v>46304</v>
@@ -5281,13 +5282,13 @@
         <v>46295</v>
       </c>
       <c r="T74" s="2">
-        <v>0.6104166666666667</v>
+        <v>0.5791666666666667</v>
       </c>
       <c r="U74" s="1">
         <v>46296</v>
       </c>
       <c r="V74" s="2">
-        <v>0.5041666666666667</v>
+        <v>0.47291666666666665</v>
       </c>
       <c r="Y74" s="1">
         <v>46317</v>
@@ -5322,10 +5323,10 @@
         <v>46293</v>
       </c>
       <c r="S75" s="1">
-        <v>46295</v>
+        <v>46291</v>
       </c>
       <c r="U75" s="1">
-        <v>46297</v>
+        <v>46294</v>
       </c>
       <c r="Y75" s="1">
         <v>46317</v>
@@ -6245,7 +6246,7 @@
         <v>46244</v>
       </c>
       <c r="T88" s="2">
-        <v>0.5770833333333333</v>
+        <v>0.6076388888888888</v>
       </c>
       <c r="U88" s="1">
         <v>46245</v>
@@ -7065,7 +7066,7 @@
         <v>46253</v>
       </c>
       <c r="V99" s="2">
-        <v>0.6222222222222222</v>
+        <v>0.6527777777777778</v>
       </c>
       <c r="X99" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7103,10 +7104,10 @@
         <v>46241</v>
       </c>
       <c r="S100" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="U100" s="1">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="X100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7171,7 +7172,7 @@
         <v>46253</v>
       </c>
       <c r="T101" s="2">
-        <v>0.6229166666666667</v>
+        <v>0.6534722222222222</v>
       </c>
       <c r="U101" s="1">
         <v>46254</v>
@@ -7461,7 +7462,7 @@
         <v>46255</v>
       </c>
       <c r="V105" s="2">
-        <v>0.5631944444444444</v>
+        <v>0.59375</v>
       </c>
       <c r="X105" t="str">
         <v>1702 Piyumi Perera</v>
@@ -7499,10 +7500,10 @@
         <v>46251</v>
       </c>
       <c r="S106" s="1">
-        <v>46253</v>
+        <v>46256</v>
       </c>
       <c r="U106" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="X106" t="str">
         <v>1702 Piyumi Perera</v>
@@ -7567,13 +7568,13 @@
         <v>46255</v>
       </c>
       <c r="T107" s="2">
-        <v>0.5638888888888889</v>
+        <v>0.5944444444444444</v>
       </c>
       <c r="U107" s="1">
         <v>46259</v>
       </c>
       <c r="V107" s="2">
-        <v>0.5270833333333333</v>
+        <v>0.5576388888888889</v>
       </c>
       <c r="Y107" s="1">
         <v>46265</v>
@@ -7608,10 +7609,10 @@
         <v>46253</v>
       </c>
       <c r="S108" s="1">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="U108" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="Y108" s="1">
         <v>46265</v>
@@ -7676,7 +7677,7 @@
         <v>46259</v>
       </c>
       <c r="T109" s="2">
-        <v>0.5277777777777778</v>
+        <v>0.5583333333333333</v>
       </c>
       <c r="U109" s="1">
         <v>46262</v>
@@ -8392,7 +8393,7 @@
         <v>46265</v>
       </c>
       <c r="V119" s="2">
-        <v>0.4270833333333333</v>
+        <v>0.4576388888888889</v>
       </c>
       <c r="Y119" s="1">
         <v>46275</v>
@@ -8427,10 +8428,10 @@
         <v>46256</v>
       </c>
       <c r="S120" s="1">
-        <v>46259</v>
+        <v>46262</v>
       </c>
       <c r="U120" s="1">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="Y120" s="1">
         <v>46275</v>
@@ -8492,7 +8493,7 @@
         <v>46283</v>
       </c>
       <c r="T121" s="2">
-        <v>0.30416666666666664</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="U121" s="1">
         <v>46283</v>
@@ -8634,7 +8635,7 @@
         <v>46293</v>
       </c>
       <c r="V123" s="2">
-        <v>0.29791666666666666</v>
+        <v>0.45208333333333334</v>
       </c>
       <c r="Y123" s="1">
         <v>46305</v>
@@ -8669,10 +8670,10 @@
         <v>46281</v>
       </c>
       <c r="S124" s="1">
-        <v>46283</v>
+        <v>46268</v>
       </c>
       <c r="U124" s="1">
-        <v>46293</v>
+        <v>46277</v>
       </c>
       <c r="Y124" s="1">
         <v>46305</v>
@@ -8737,13 +8738,13 @@
         <v>46293</v>
       </c>
       <c r="T125" s="2">
-        <v>0.2986111111111111</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="U125" s="1">
         <v>46301</v>
       </c>
       <c r="V125" s="2">
-        <v>0.4888888888888889</v>
+        <v>0.6430555555555556</v>
       </c>
       <c r="Y125" s="1">
         <v>46305</v>
@@ -8778,10 +8779,10 @@
         <v>46290</v>
       </c>
       <c r="S126" s="1">
-        <v>46293</v>
+        <v>46277</v>
       </c>
       <c r="U126" s="1">
-        <v>46301</v>
+        <v>46286</v>
       </c>
       <c r="Y126" s="1">
         <v>46305</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -13651,6 +13651,9 @@
       <c r="Y203" s="1">
         <v>46254</v>
       </c>
+      <c r="Z203" t="str">
+        <v>MG-k0t91m</v>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -13692,6 +13695,9 @@
       <c r="Y204" s="1">
         <v>46254</v>
       </c>
+      <c r="Z204" t="str">
+        <v>MG-k0t91m</v>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -13766,6 +13772,9 @@
       <c r="Y205" s="1">
         <v>46254</v>
       </c>
+      <c r="Z205" t="str">
+        <v>MG-k0t91m</v>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -13806,6 +13815,9 @@
       </c>
       <c r="Y206" s="1">
         <v>46254</v>
+      </c>
+      <c r="Z206" t="str">
+        <v>MG-k0t91m</v>
       </c>
     </row>
     <row r="207">

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B6">
         <v>847</v>
@@ -805,7 +805,7 @@
         <v>46238</v>
       </c>
       <c r="T6" s="2">
-        <v>0.4486111111111111</v>
+        <v>0.4395833333333333</v>
       </c>
       <c r="U6" s="1">
         <v>46240</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B7">
         <v>847</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="B8">
         <v>847</v>
@@ -959,7 +959,7 @@
         <v>46241</v>
       </c>
       <c r="V8" s="2">
-        <v>0.29444444444444445</v>
+        <v>0.7645833333333333</v>
       </c>
       <c r="X8" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 01</v>
+        <v>SGL 02</v>
       </c>
       <c r="C9" t="str">
         <v>3497A::SGSGZIMER5060::SH</v>
@@ -997,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="U9" s="1">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="X9" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1068,7 +1068,7 @@
         <v>46241</v>
       </c>
       <c r="T10" s="2">
-        <v>0.5770833333333333</v>
+        <v>0.7652777777777777</v>
       </c>
       <c r="U10" s="1">
         <v>46241</v>
@@ -1814,7 +1814,7 @@
         <v>46245</v>
       </c>
       <c r="V20" s="2">
-        <v>0.6069444444444444</v>
+        <v>0.3159722222222222</v>
       </c>
       <c r="X20" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1852,10 +1852,10 @@
         <v>-</v>
       </c>
       <c r="S21" s="1">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="U21" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="X21" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1923,7 +1923,7 @@
         <v>46245</v>
       </c>
       <c r="T22" s="2">
-        <v>0.2951388888888889</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="U22" s="1">
         <v>46245</v>
@@ -3039,7 +3039,7 @@
         <v>46251</v>
       </c>
       <c r="V37" s="2">
-        <v>0.6625</v>
+        <v>0.3368055555555556</v>
       </c>
       <c r="X37" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3077,10 +3077,10 @@
         <v>46242</v>
       </c>
       <c r="S38" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="U38" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="X38" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3148,7 +3148,7 @@
         <v>46251</v>
       </c>
       <c r="T39" s="2">
-        <v>0.6631944444444444</v>
+        <v>0.3375</v>
       </c>
       <c r="U39" s="1">
         <v>46255</v>
@@ -3651,7 +3651,7 @@
         <v>46259</v>
       </c>
       <c r="V46" s="2">
-        <v>0.4979166666666667</v>
+        <v>0.6513888888888889</v>
       </c>
       <c r="Y46" s="1">
         <v>46266</v>
@@ -3686,10 +3686,10 @@
         <v>46248</v>
       </c>
       <c r="S47" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="U47" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="Y47" s="1">
         <v>46266</v>
@@ -3751,13 +3751,13 @@
         <v>46259</v>
       </c>
       <c r="T48" s="2">
-        <v>0.4986111111111111</v>
+        <v>0.6520833333333333</v>
       </c>
       <c r="U48" s="1">
         <v>46262</v>
       </c>
       <c r="V48" s="2">
-        <v>0.6020833333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="Y48" s="1">
         <v>46265</v>
@@ -3792,10 +3792,10 @@
         <v>46256</v>
       </c>
       <c r="S49" s="1">
+        <v>46252</v>
+      </c>
+      <c r="U49" s="1">
         <v>46255</v>
-      </c>
-      <c r="U49" s="1">
-        <v>46259</v>
       </c>
       <c r="Y49" s="1">
         <v>46265</v>
@@ -3860,7 +3860,7 @@
         <v>46262</v>
       </c>
       <c r="T50" s="2">
-        <v>0.6027777777777777</v>
+        <v>0.75625</v>
       </c>
       <c r="U50" s="1">
         <v>46263</v>
@@ -4236,7 +4236,7 @@
         <v>46266</v>
       </c>
       <c r="V55" s="2">
-        <v>0.575</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="X55" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4274,10 +4274,10 @@
         <v>46260</v>
       </c>
       <c r="S56" s="1">
+        <v>46255</v>
+      </c>
+      <c r="U56" s="1">
         <v>46259</v>
-      </c>
-      <c r="U56" s="1">
-        <v>46262</v>
       </c>
       <c r="X56" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4345,13 +4345,13 @@
         <v>46266</v>
       </c>
       <c r="T57" s="2">
-        <v>0.5756944444444444</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="U57" s="1">
         <v>46267</v>
       </c>
       <c r="V57" s="2">
-        <v>0.45</v>
+        <v>0.6034722222222222</v>
       </c>
       <c r="X57" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4389,10 +4389,10 @@
         <v>46263</v>
       </c>
       <c r="S58" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="U58" s="1">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="X58" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4457,13 +4457,13 @@
         <v>46267</v>
       </c>
       <c r="T59" s="2">
-        <v>0.45069444444444445</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="U59" s="1">
         <v>46269</v>
       </c>
       <c r="V59" s="2">
-        <v>0.3159722222222222</v>
+        <v>0.46944444444444444</v>
       </c>
       <c r="Y59" s="1">
         <v>46277</v>
@@ -4498,10 +4498,10 @@
         <v>46265</v>
       </c>
       <c r="S60" s="1">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="U60" s="1">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="Y60" s="1">
         <v>46277</v>
@@ -4566,13 +4566,13 @@
         <v>46269</v>
       </c>
       <c r="T61" s="2">
-        <v>0.31666666666666665</v>
+        <v>0.4701388888888889</v>
       </c>
       <c r="U61" s="1">
         <v>46276</v>
       </c>
       <c r="V61" s="2">
-        <v>0.2951388888888889</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="X61" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4610,10 +4610,10 @@
         <v>46267</v>
       </c>
       <c r="S62" s="1">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="U62" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="X62" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4681,7 +4681,7 @@
         <v>46276</v>
       </c>
       <c r="T63" s="2">
-        <v>0.29583333333333334</v>
+        <v>0.44930555555555557</v>
       </c>
       <c r="U63" s="1">
         <v>46276</v>
@@ -4758,7 +4758,7 @@
         <v>46279</v>
       </c>
       <c r="V64" s="2">
-        <v>0.29930555555555555</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="Y64" s="1">
         <v>46298</v>
@@ -4793,10 +4793,10 @@
         <v>46274</v>
       </c>
       <c r="S65" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="U65" s="1">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="Y65" s="1">
         <v>46298</v>
@@ -4858,13 +4858,13 @@
         <v>46279</v>
       </c>
       <c r="T66" s="2">
-        <v>0.3</v>
+        <v>0.4534722222222222</v>
       </c>
       <c r="U66" s="1">
         <v>46283</v>
       </c>
       <c r="V66" s="2">
-        <v>0.43125</v>
+        <v>0.5847222222222223</v>
       </c>
       <c r="Y66" s="1">
         <v>46301</v>
@@ -4899,10 +4899,10 @@
         <v>46276</v>
       </c>
       <c r="S67" s="1">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="U67" s="1">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="Y67" s="1">
         <v>46301</v>
@@ -4964,13 +4964,13 @@
         <v>46283</v>
       </c>
       <c r="T68" s="2">
-        <v>0.43194444444444446</v>
+        <v>0.5854166666666667</v>
       </c>
       <c r="U68" s="1">
         <v>46286</v>
       </c>
       <c r="V68" s="2">
-        <v>0.5069444444444444</v>
+        <v>0.6604166666666667</v>
       </c>
       <c r="Y68" s="1">
         <v>46304</v>
@@ -5005,10 +5005,10 @@
         <v>46281</v>
       </c>
       <c r="S69" s="1">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="U69" s="1">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="Y69" s="1">
         <v>46304</v>
@@ -5070,13 +5070,13 @@
         <v>46286</v>
       </c>
       <c r="T70" s="2">
-        <v>0.5076388888888889</v>
+        <v>0.6611111111111111</v>
       </c>
       <c r="U70" s="1">
         <v>46293</v>
       </c>
       <c r="V70" s="2">
-        <v>0.46319444444444446</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="Y70" s="1">
         <v>46301</v>
@@ -5111,10 +5111,10 @@
         <v>46283</v>
       </c>
       <c r="S71" s="1">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="U71" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="Y71" s="1">
         <v>46301</v>
@@ -5176,13 +5176,13 @@
         <v>46293</v>
       </c>
       <c r="T72" s="2">
-        <v>0.4638888888888889</v>
+        <v>0.6173611111111111</v>
       </c>
       <c r="U72" s="1">
         <v>46295</v>
       </c>
       <c r="V72" s="2">
-        <v>0.5784722222222223</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="Y72" s="1">
         <v>46304</v>
@@ -5217,10 +5217,10 @@
         <v>46290</v>
       </c>
       <c r="S73" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="U73" s="1">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="Y73" s="1">
         <v>46304</v>
@@ -5282,13 +5282,13 @@
         <v>46295</v>
       </c>
       <c r="T74" s="2">
-        <v>0.5791666666666667</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="U74" s="1">
         <v>46296</v>
       </c>
       <c r="V74" s="2">
-        <v>0.47291666666666665</v>
+        <v>0.6263888888888889</v>
       </c>
       <c r="Y74" s="1">
         <v>46317</v>
@@ -5323,10 +5323,10 @@
         <v>46293</v>
       </c>
       <c r="S75" s="1">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="U75" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="Y75" s="1">
         <v>46317</v>
@@ -6137,7 +6137,7 @@
         <v>46244</v>
       </c>
       <c r="V86" s="2">
-        <v>0.5763888888888888</v>
+        <v>0.4388888888888889</v>
       </c>
       <c r="X86" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6178,7 +6178,7 @@
         <v>46235</v>
       </c>
       <c r="U87" s="1">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="X87" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6246,7 +6246,7 @@
         <v>46244</v>
       </c>
       <c r="T88" s="2">
-        <v>0.6076388888888888</v>
+        <v>0.31666666666666665</v>
       </c>
       <c r="U88" s="1">
         <v>46245</v>
@@ -7066,7 +7066,7 @@
         <v>46253</v>
       </c>
       <c r="V99" s="2">
-        <v>0.6527777777777778</v>
+        <v>0.36180555555555555</v>
       </c>
       <c r="X99" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7104,10 +7104,10 @@
         <v>46241</v>
       </c>
       <c r="S100" s="1">
-        <v>46247</v>
+        <v>46252</v>
       </c>
       <c r="U100" s="1">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="X100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7172,7 +7172,7 @@
         <v>46253</v>
       </c>
       <c r="T101" s="2">
-        <v>0.6534722222222222</v>
+        <v>0.3625</v>
       </c>
       <c r="U101" s="1">
         <v>46254</v>
@@ -7462,7 +7462,7 @@
         <v>46255</v>
       </c>
       <c r="V105" s="2">
-        <v>0.59375</v>
+        <v>0.30277777777777776</v>
       </c>
       <c r="X105" t="str">
         <v>1702 Piyumi Perera</v>
@@ -7500,10 +7500,10 @@
         <v>46251</v>
       </c>
       <c r="S106" s="1">
-        <v>46256</v>
+        <v>46261</v>
       </c>
       <c r="U106" s="1">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="X106" t="str">
         <v>1702 Piyumi Perera</v>
@@ -7568,13 +7568,13 @@
         <v>46255</v>
       </c>
       <c r="T107" s="2">
-        <v>0.5944444444444444</v>
+        <v>0.3034722222222222</v>
       </c>
       <c r="U107" s="1">
         <v>46259</v>
       </c>
       <c r="V107" s="2">
-        <v>0.5576388888888889</v>
+        <v>0.7458333333333333</v>
       </c>
       <c r="Y107" s="1">
         <v>46265</v>
@@ -7609,10 +7609,10 @@
         <v>46253</v>
       </c>
       <c r="S108" s="1">
-        <v>46259</v>
+        <v>46263</v>
       </c>
       <c r="U108" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="Y108" s="1">
         <v>46265</v>
@@ -7677,7 +7677,7 @@
         <v>46259</v>
       </c>
       <c r="T109" s="2">
-        <v>0.5583333333333333</v>
+        <v>0.7465277777777778</v>
       </c>
       <c r="U109" s="1">
         <v>46262</v>
@@ -8393,7 +8393,7 @@
         <v>46265</v>
       </c>
       <c r="V119" s="2">
-        <v>0.4576388888888889</v>
+        <v>0.6458333333333334</v>
       </c>
       <c r="Y119" s="1">
         <v>46275</v>
@@ -8428,10 +8428,10 @@
         <v>46256</v>
       </c>
       <c r="S120" s="1">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="U120" s="1">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="Y120" s="1">
         <v>46275</v>
@@ -8493,7 +8493,7 @@
         <v>46283</v>
       </c>
       <c r="T121" s="2">
-        <v>0.4583333333333333</v>
+        <v>0.6465277777777778</v>
       </c>
       <c r="U121" s="1">
         <v>46283</v>
@@ -8635,7 +8635,7 @@
         <v>46293</v>
       </c>
       <c r="V123" s="2">
-        <v>0.45208333333333334</v>
+        <v>0.6402777777777777</v>
       </c>
       <c r="Y123" s="1">
         <v>46305</v>
@@ -8670,10 +8670,10 @@
         <v>46281</v>
       </c>
       <c r="S124" s="1">
-        <v>46268</v>
+        <v>46272</v>
       </c>
       <c r="U124" s="1">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="Y124" s="1">
         <v>46305</v>
@@ -8738,13 +8738,13 @@
         <v>46293</v>
       </c>
       <c r="T125" s="2">
-        <v>0.4527777777777778</v>
+        <v>0.6409722222222223</v>
       </c>
       <c r="U125" s="1">
         <v>46301</v>
       </c>
       <c r="V125" s="2">
-        <v>0.6430555555555556</v>
+        <v>0.35208333333333336</v>
       </c>
       <c r="Y125" s="1">
         <v>46305</v>
@@ -8779,10 +8779,10 @@
         <v>46290</v>
       </c>
       <c r="S126" s="1">
-        <v>46277</v>
+        <v>46281</v>
       </c>
       <c r="U126" s="1">
-        <v>46286</v>
+        <v>46290</v>
       </c>
       <c r="Y126" s="1">
         <v>46305</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -748,7 +748,7 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>SGL 01</v>
+        <v>SGL 03</v>
       </c>
       <c r="B6">
         <v>847</v>
@@ -805,7 +805,7 @@
         <v>46238</v>
       </c>
       <c r="T6" s="2">
-        <v>0.4486111111111111</v>
+        <v>0.39166666666666666</v>
       </c>
       <c r="U6" s="1">
         <v>46240</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>SGL 01</v>
+        <v>SGL 03</v>
       </c>
       <c r="B7">
         <v>847</v>
@@ -896,7 +896,7 @@
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>SGL 01</v>
+        <v>SGL 03</v>
       </c>
       <c r="B8">
         <v>847</v>
@@ -959,7 +959,7 @@
         <v>46241</v>
       </c>
       <c r="V8" s="2">
-        <v>0.29444444444444445</v>
+        <v>0.7166666666666667</v>
       </c>
       <c r="X8" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -970,7 +970,7 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>SGL 01</v>
+        <v>SGL 03</v>
       </c>
       <c r="C9" t="str">
         <v>3497A::SGSGZIMER5060::SH</v>
@@ -997,10 +997,10 @@
         <v>0</v>
       </c>
       <c r="S9" s="1">
-        <v>46238</v>
+        <v>46245</v>
       </c>
       <c r="U9" s="1">
-        <v>46241</v>
+        <v>46247</v>
       </c>
       <c r="X9" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -1923,7 +1923,7 @@
         <v>46245</v>
       </c>
       <c r="T22" s="2">
-        <v>0.2951388888888889</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="U22" s="1">
         <v>46245</v>
@@ -3039,7 +3039,7 @@
         <v>46251</v>
       </c>
       <c r="V37" s="2">
-        <v>0.6625</v>
+        <v>0.3368055555555556</v>
       </c>
       <c r="X37" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3077,10 +3077,10 @@
         <v>46242</v>
       </c>
       <c r="S38" s="1">
-        <v>46241</v>
+        <v>46238</v>
       </c>
       <c r="U38" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="X38" t="str">
         <v>1702 Piyumi Perera</v>
@@ -3148,7 +3148,7 @@
         <v>46251</v>
       </c>
       <c r="T39" s="2">
-        <v>0.6631944444444444</v>
+        <v>0.3375</v>
       </c>
       <c r="U39" s="1">
         <v>46255</v>
@@ -3651,7 +3651,7 @@
         <v>46259</v>
       </c>
       <c r="V46" s="2">
-        <v>0.4979166666666667</v>
+        <v>0.6513888888888889</v>
       </c>
       <c r="Y46" s="1">
         <v>46266</v>
@@ -3686,10 +3686,10 @@
         <v>46248</v>
       </c>
       <c r="S47" s="1">
-        <v>46247</v>
+        <v>46245</v>
       </c>
       <c r="U47" s="1">
-        <v>46255</v>
+        <v>46252</v>
       </c>
       <c r="Y47" s="1">
         <v>46266</v>
@@ -3751,13 +3751,13 @@
         <v>46259</v>
       </c>
       <c r="T48" s="2">
-        <v>0.4986111111111111</v>
+        <v>0.6520833333333333</v>
       </c>
       <c r="U48" s="1">
         <v>46262</v>
       </c>
       <c r="V48" s="2">
-        <v>0.6020833333333333</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="Y48" s="1">
         <v>46265</v>
@@ -3792,10 +3792,10 @@
         <v>46256</v>
       </c>
       <c r="S49" s="1">
+        <v>46252</v>
+      </c>
+      <c r="U49" s="1">
         <v>46255</v>
-      </c>
-      <c r="U49" s="1">
-        <v>46259</v>
       </c>
       <c r="Y49" s="1">
         <v>46265</v>
@@ -3860,7 +3860,7 @@
         <v>46262</v>
       </c>
       <c r="T50" s="2">
-        <v>0.6027777777777777</v>
+        <v>0.75625</v>
       </c>
       <c r="U50" s="1">
         <v>46263</v>
@@ -4236,7 +4236,7 @@
         <v>46266</v>
       </c>
       <c r="V55" s="2">
-        <v>0.575</v>
+        <v>0.7284722222222222</v>
       </c>
       <c r="X55" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4274,10 +4274,10 @@
         <v>46260</v>
       </c>
       <c r="S56" s="1">
+        <v>46255</v>
+      </c>
+      <c r="U56" s="1">
         <v>46259</v>
-      </c>
-      <c r="U56" s="1">
-        <v>46262</v>
       </c>
       <c r="X56" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4345,13 +4345,13 @@
         <v>46266</v>
       </c>
       <c r="T57" s="2">
-        <v>0.5756944444444444</v>
+        <v>0.7291666666666666</v>
       </c>
       <c r="U57" s="1">
         <v>46267</v>
       </c>
       <c r="V57" s="2">
-        <v>0.45</v>
+        <v>0.6034722222222222</v>
       </c>
       <c r="X57" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4389,10 +4389,10 @@
         <v>46263</v>
       </c>
       <c r="S58" s="1">
-        <v>46262</v>
+        <v>46259</v>
       </c>
       <c r="U58" s="1">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="X58" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4457,13 +4457,13 @@
         <v>46267</v>
       </c>
       <c r="T59" s="2">
-        <v>0.45069444444444445</v>
+        <v>0.6041666666666666</v>
       </c>
       <c r="U59" s="1">
         <v>46269</v>
       </c>
       <c r="V59" s="2">
-        <v>0.3159722222222222</v>
+        <v>0.46944444444444444</v>
       </c>
       <c r="Y59" s="1">
         <v>46277</v>
@@ -4498,10 +4498,10 @@
         <v>46265</v>
       </c>
       <c r="S60" s="1">
-        <v>46263</v>
+        <v>46260</v>
       </c>
       <c r="U60" s="1">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="Y60" s="1">
         <v>46277</v>
@@ -4566,13 +4566,13 @@
         <v>46269</v>
       </c>
       <c r="T61" s="2">
-        <v>0.31666666666666665</v>
+        <v>0.4701388888888889</v>
       </c>
       <c r="U61" s="1">
         <v>46276</v>
       </c>
       <c r="V61" s="2">
-        <v>0.2951388888888889</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="X61" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4610,10 +4610,10 @@
         <v>46267</v>
       </c>
       <c r="S62" s="1">
-        <v>46266</v>
+        <v>46262</v>
       </c>
       <c r="U62" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="X62" t="str">
         <v>1702 Piyumi Perera</v>
@@ -4681,7 +4681,7 @@
         <v>46276</v>
       </c>
       <c r="T63" s="2">
-        <v>0.29583333333333334</v>
+        <v>0.44930555555555557</v>
       </c>
       <c r="U63" s="1">
         <v>46276</v>
@@ -4758,7 +4758,7 @@
         <v>46279</v>
       </c>
       <c r="V64" s="2">
-        <v>0.29930555555555555</v>
+        <v>0.4527777777777778</v>
       </c>
       <c r="Y64" s="1">
         <v>46298</v>
@@ -4793,10 +4793,10 @@
         <v>46274</v>
       </c>
       <c r="S65" s="1">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="U65" s="1">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="Y65" s="1">
         <v>46298</v>
@@ -4858,13 +4858,13 @@
         <v>46279</v>
       </c>
       <c r="T66" s="2">
-        <v>0.3</v>
+        <v>0.4534722222222222</v>
       </c>
       <c r="U66" s="1">
         <v>46283</v>
       </c>
       <c r="V66" s="2">
-        <v>0.43125</v>
+        <v>0.5847222222222223</v>
       </c>
       <c r="Y66" s="1">
         <v>46301</v>
@@ -4899,10 +4899,10 @@
         <v>46276</v>
       </c>
       <c r="S67" s="1">
-        <v>46275</v>
+        <v>46272</v>
       </c>
       <c r="U67" s="1">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="Y67" s="1">
         <v>46301</v>
@@ -4964,13 +4964,13 @@
         <v>46283</v>
       </c>
       <c r="T68" s="2">
-        <v>0.43194444444444446</v>
+        <v>0.5854166666666667</v>
       </c>
       <c r="U68" s="1">
         <v>46286</v>
       </c>
       <c r="V68" s="2">
-        <v>0.5069444444444444</v>
+        <v>0.6604166666666667</v>
       </c>
       <c r="Y68" s="1">
         <v>46304</v>
@@ -5005,10 +5005,10 @@
         <v>46281</v>
       </c>
       <c r="S69" s="1">
-        <v>46280</v>
+        <v>46276</v>
       </c>
       <c r="U69" s="1">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="Y69" s="1">
         <v>46304</v>
@@ -5070,13 +5070,13 @@
         <v>46286</v>
       </c>
       <c r="T70" s="2">
-        <v>0.5076388888888889</v>
+        <v>0.6611111111111111</v>
       </c>
       <c r="U70" s="1">
         <v>46293</v>
       </c>
       <c r="V70" s="2">
-        <v>0.46319444444444446</v>
+        <v>0.6166666666666667</v>
       </c>
       <c r="Y70" s="1">
         <v>46301</v>
@@ -5111,10 +5111,10 @@
         <v>46283</v>
       </c>
       <c r="S71" s="1">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="U71" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="Y71" s="1">
         <v>46301</v>
@@ -5176,13 +5176,13 @@
         <v>46293</v>
       </c>
       <c r="T72" s="2">
-        <v>0.4638888888888889</v>
+        <v>0.6173611111111111</v>
       </c>
       <c r="U72" s="1">
         <v>46295</v>
       </c>
       <c r="V72" s="2">
-        <v>0.5784722222222223</v>
+        <v>0.7319444444444444</v>
       </c>
       <c r="Y72" s="1">
         <v>46304</v>
@@ -5217,10 +5217,10 @@
         <v>46290</v>
       </c>
       <c r="S73" s="1">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="U73" s="1">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="Y73" s="1">
         <v>46304</v>
@@ -5282,13 +5282,13 @@
         <v>46295</v>
       </c>
       <c r="T74" s="2">
-        <v>0.5791666666666667</v>
+        <v>0.7326388888888888</v>
       </c>
       <c r="U74" s="1">
         <v>46296</v>
       </c>
       <c r="V74" s="2">
-        <v>0.47291666666666665</v>
+        <v>0.6263888888888889</v>
       </c>
       <c r="Y74" s="1">
         <v>46317</v>
@@ -5323,10 +5323,10 @@
         <v>46293</v>
       </c>
       <c r="S75" s="1">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="U75" s="1">
-        <v>46294</v>
+        <v>46290</v>
       </c>
       <c r="Y75" s="1">
         <v>46317</v>
@@ -9705,7 +9705,7 @@
         <v>46245</v>
       </c>
       <c r="V139" s="2">
-        <v>0.3236111111111111</v>
+        <v>0.3909722222222222</v>
       </c>
       <c r="X139" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -9814,7 +9814,7 @@
         <v>46245</v>
       </c>
       <c r="T141" s="2">
-        <v>0.32430555555555557</v>
+        <v>0.7173611111111111</v>
       </c>
       <c r="U141" s="1">
         <v>46245</v>
@@ -10338,7 +10338,7 @@
         <v>46249</v>
       </c>
       <c r="V148" s="2">
-        <v>0.30694444444444446</v>
+        <v>0.7</v>
       </c>
       <c r="X148" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -10376,10 +10376,10 @@
         <v>46242</v>
       </c>
       <c r="S149" s="1">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="U149" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="X149" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -10447,7 +10447,7 @@
         <v>46249</v>
       </c>
       <c r="T150" s="2">
-        <v>0.3076388888888889</v>
+        <v>0.7006944444444444</v>
       </c>
       <c r="U150" s="1">
         <v>46251</v>
@@ -10524,7 +10524,7 @@
         <v>46251</v>
       </c>
       <c r="V151" s="2">
-        <v>0.4125</v>
+        <v>0.3263888888888889</v>
       </c>
       <c r="Y151" s="1">
         <v>46255</v>
@@ -10559,10 +10559,10 @@
         <v>46247</v>
       </c>
       <c r="S152" s="1">
-        <v>46249</v>
+        <v>46252</v>
       </c>
       <c r="U152" s="1">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="Y152" s="1">
         <v>46255</v>
@@ -10627,7 +10627,7 @@
         <v>46251</v>
       </c>
       <c r="T153" s="2">
-        <v>0.4131944444444444</v>
+        <v>0.32708333333333334</v>
       </c>
       <c r="U153" s="1">
         <v>46251</v>
@@ -10704,7 +10704,7 @@
         <v>46251</v>
       </c>
       <c r="V154" s="2">
-        <v>0.5423611111111111</v>
+        <v>0.45625</v>
       </c>
       <c r="Y154" s="1">
         <v>46226</v>
@@ -10739,10 +10739,10 @@
         <v>46242</v>
       </c>
       <c r="S155" s="1">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="U155" s="1">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="Y155" s="1">
         <v>46226</v>
@@ -10807,7 +10807,7 @@
         <v>46251</v>
       </c>
       <c r="T156" s="2">
-        <v>0.5430555555555555</v>
+        <v>0.45694444444444443</v>
       </c>
       <c r="U156" s="1">
         <v>46256</v>
@@ -11594,7 +11594,7 @@
         <v>46265</v>
       </c>
       <c r="V167" s="2">
-        <v>0.3541666666666667</v>
+        <v>0.7472222222222222</v>
       </c>
       <c r="Y167" s="1">
         <v>46270</v>
@@ -11629,10 +11629,10 @@
         <v>46248</v>
       </c>
       <c r="S168" s="1">
-        <v>46251</v>
+        <v>46254</v>
       </c>
       <c r="U168" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="Y168" s="1">
         <v>46270</v>
@@ -11697,13 +11697,13 @@
         <v>46265</v>
       </c>
       <c r="T169" s="2">
-        <v>0.3548611111111111</v>
+        <v>0.7479166666666667</v>
       </c>
       <c r="U169" s="1">
         <v>46266</v>
       </c>
       <c r="V169" s="2">
-        <v>0.49375</v>
+        <v>0.4076388888888889</v>
       </c>
       <c r="Y169" s="1">
         <v>46247</v>
@@ -11738,10 +11738,10 @@
         <v>46262</v>
       </c>
       <c r="S170" s="1">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="U170" s="1">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="Y170" s="1">
         <v>46247</v>
@@ -11806,13 +11806,13 @@
         <v>46266</v>
       </c>
       <c r="T171" s="2">
-        <v>0.49444444444444446</v>
+        <v>0.4083333333333333</v>
       </c>
       <c r="U171" s="1">
         <v>46269</v>
       </c>
       <c r="V171" s="2">
-        <v>0.3819444444444444</v>
+        <v>0.29583333333333334</v>
       </c>
       <c r="Y171" s="1">
         <v>46247</v>
@@ -11847,10 +11847,10 @@
         <v>46263</v>
       </c>
       <c r="S172" s="1">
-        <v>46266</v>
+        <v>46269</v>
       </c>
       <c r="U172" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="Y172" s="1">
         <v>46247</v>
@@ -11915,13 +11915,13 @@
         <v>46269</v>
       </c>
       <c r="T173" s="2">
-        <v>0.38263888888888886</v>
+        <v>0.2965277777777778</v>
       </c>
       <c r="U173" s="1">
         <v>46272</v>
       </c>
       <c r="V173" s="2">
-        <v>0.3215277777777778</v>
+        <v>0.7145833333333333</v>
       </c>
       <c r="Y173" s="1">
         <v>46247</v>
@@ -11956,10 +11956,10 @@
         <v>46267</v>
       </c>
       <c r="S174" s="1">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="U174" s="1">
-        <v>46272</v>
+        <v>46274</v>
       </c>
       <c r="Y174" s="1">
         <v>46247</v>
@@ -12021,13 +12021,13 @@
         <v>46283</v>
       </c>
       <c r="T175" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.7152777777777778</v>
       </c>
       <c r="U175" s="1">
         <v>46284</v>
       </c>
       <c r="V175" s="2">
-        <v>0.4388888888888889</v>
+        <v>0.38333333333333336</v>
       </c>
       <c r="X175" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12065,10 +12065,10 @@
         <v>46281</v>
       </c>
       <c r="S176" s="1">
-        <v>46283</v>
+        <v>46274</v>
       </c>
       <c r="U176" s="1">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="X176" t="str">
         <v>1702 Piyumi Perera</v>
@@ -12133,7 +12133,7 @@
         <v>46284</v>
       </c>
       <c r="T177" s="2">
-        <v>0.4395833333333333</v>
+        <v>0.3840277777777778</v>
       </c>
       <c r="U177" s="1">
         <v>46286</v>
@@ -12207,7 +12207,7 @@
         <v>46298</v>
       </c>
       <c r="V178" s="2">
-        <v>0.3736111111111111</v>
+        <v>0.31805555555555554</v>
       </c>
       <c r="Y178" s="1">
         <v>46305</v>
@@ -12242,10 +12242,10 @@
         <v>46282</v>
       </c>
       <c r="S179" s="1">
-        <v>46284</v>
+        <v>46276</v>
       </c>
       <c r="U179" s="1">
-        <v>46301</v>
+        <v>46293</v>
       </c>
       <c r="Y179" s="1">
         <v>46305</v>

--- a/Production_Plan.xlsx
+++ b/Production_Plan.xlsx
@@ -6499,7 +6499,7 @@
         <v>46274</v>
       </c>
       <c r="V96" s="2">
-        <v>0.5847222222222223</v>
+        <v>0.7597222222222222</v>
       </c>
       <c r="Y96" s="1">
         <v>46282</v>
@@ -6602,7 +6602,7 @@
         <v>46275</v>
       </c>
       <c r="T98" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.7604166666666666</v>
       </c>
       <c r="U98" s="1">
         <v>46277</v>
@@ -6682,7 +6682,7 @@
         <v>46279</v>
       </c>
       <c r="V99" s="2">
-        <v>0.3020833333333333</v>
+        <v>0.7708333333333334</v>
       </c>
       <c r="X99" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6720,10 +6720,10 @@
         <v>46272</v>
       </c>
       <c r="S100" s="1">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="U100" s="1">
-        <v>46279</v>
+        <v>46277</v>
       </c>
       <c r="X100" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -6791,13 +6791,13 @@
         <v>46279</v>
       </c>
       <c r="T101" s="2">
-        <v>0.31666666666666665</v>
+        <v>0.2916666666666667</v>
       </c>
       <c r="U101" s="1">
         <v>46286</v>
       </c>
       <c r="V101" s="2">
-        <v>0.34305555555555556</v>
+        <v>0.31805555555555554</v>
       </c>
       <c r="X101" t="str">
         <v>1553 Niwya Diwanjana</v>
@@ -6906,7 +6906,7 @@
         <v>46286</v>
       </c>
       <c r="T103" s="2">
-        <v>0.34375</v>
+        <v>0.31875</v>
       </c>
       <c r="U103" s="1">
         <v>46286</v>
@@ -7134,7 +7134,7 @@
         <v>46300</v>
       </c>
       <c r="V106" s="2">
-        <v>0.29930555555555555</v>
+        <v>0.7534722222222222</v>
       </c>
       <c r="X106" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7175,7 +7175,7 @@
         <v>46286</v>
       </c>
       <c r="U107" s="1">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="X107" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7243,7 +7243,7 @@
         <v>46300</v>
       </c>
       <c r="T108" s="2">
-        <v>0.3</v>
+        <v>0.7541666666666667</v>
       </c>
       <c r="U108" s="1">
         <v>46303</v>
@@ -7323,7 +7323,7 @@
         <v>46304</v>
       </c>
       <c r="V109" s="2">
-        <v>0.38263888888888886</v>
+        <v>0.3576388888888889</v>
       </c>
       <c r="X109" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -7361,7 +7361,7 @@
         <v>46297</v>
       </c>
       <c r="S110" s="1">
-        <v>46300</v>
+        <v>46298</v>
       </c>
       <c r="U110" s="1">
         <v>46304</v>
@@ -7432,13 +7432,13 @@
         <v>46317</v>
       </c>
       <c r="T111" s="2">
-        <v>0.46458333333333335</v>
+        <v>0.35833333333333334</v>
       </c>
       <c r="U111" s="1">
         <v>46322</v>
       </c>
       <c r="V111" s="2">
-        <v>0.29375</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="Y111" s="1">
         <v>46338</v>
@@ -7473,10 +7473,10 @@
         <v>46315</v>
       </c>
       <c r="S112" s="1">
-        <v>46317</v>
+        <v>46304</v>
       </c>
       <c r="U112" s="1">
-        <v>46322</v>
+        <v>46308</v>
       </c>
       <c r="Y112" s="1">
         <v>46338</v>
@@ -7541,7 +7541,7 @@
         <v>46322</v>
       </c>
       <c r="T113" s="2">
-        <v>0.29444444444444445</v>
+        <v>0.6673611111111111</v>
       </c>
       <c r="U113" s="1">
         <v>46323</v>
@@ -7618,7 +7618,7 @@
         <v>46324</v>
       </c>
       <c r="V114" s="2">
-        <v>0.6513888888888889</v>
+        <v>0.5451388888888888</v>
       </c>
       <c r="Y114" s="1">
         <v>46338</v>
@@ -7653,10 +7653,10 @@
         <v>46319</v>
       </c>
       <c r="S115" s="1">
-        <v>46322</v>
+        <v>46308</v>
       </c>
       <c r="U115" s="1">
-        <v>46324</v>
+        <v>46311</v>
       </c>
       <c r="Y115" s="1">
         <v>46338</v>
@@ -7721,13 +7721,13 @@
         <v>46324</v>
       </c>
       <c r="T116" s="2">
-        <v>0.6520833333333333</v>
+        <v>0.5458333333333333</v>
       </c>
       <c r="U116" s="1">
         <v>46325</v>
       </c>
       <c r="V116" s="2">
-        <v>0.45625</v>
+        <v>0.35</v>
       </c>
       <c r="Y116" s="1">
         <v>46338</v>
@@ -7762,10 +7762,10 @@
         <v>46322</v>
       </c>
       <c r="S117" s="1">
-        <v>46324</v>
+        <v>46311</v>
       </c>
       <c r="U117" s="1">
-        <v>46325</v>
+        <v>46312</v>
       </c>
       <c r="Y117" s="1">
         <v>46338</v>
@@ -11690,7 +11690,7 @@
         <v>46269</v>
       </c>
       <c r="V185" s="2">
-        <v>0.2965277777777778</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="X185" t="str">
         <v>305 Ishan Jayathilaka</v>
@@ -11731,7 +11731,7 @@
         <v>46267</v>
       </c>
       <c r="U186" s="1">
-        <v>46269</v>
+        <v>46274</v>
       </c>
       <c r="X186" t="str">
         <v>305 Ishan Jayathilaka</v>
@@ -11799,7 +11799,7 @@
         <v>46279</v>
       </c>
       <c r="T187" s="2">
-        <v>0.2916666666666667</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="U187" s="1">
         <v>46280</v>
@@ -12619,7 +12619,7 @@
         <v>46289</v>
       </c>
       <c r="V198" s="2">
-        <v>0.3993055555555556</v>
+        <v>0.55625</v>
       </c>
       <c r="X198" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -12657,10 +12657,10 @@
         <v>46276</v>
       </c>
       <c r="S199" s="1">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="U199" s="1">
-        <v>46289</v>
+        <v>46284</v>
       </c>
       <c r="X199" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -12728,7 +12728,7 @@
         <v>46289</v>
       </c>
       <c r="T200" s="2">
-        <v>0.40902777777777777</v>
+        <v>0.5569444444444445</v>
       </c>
       <c r="U200" s="1">
         <v>46289</v>
@@ -12808,7 +12808,7 @@
         <v>46294</v>
       </c>
       <c r="V201" s="2">
-        <v>0.47291666666666665</v>
+        <v>0.6208333333333333</v>
       </c>
       <c r="X201" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -12846,10 +12846,10 @@
         <v>46287</v>
       </c>
       <c r="S202" s="1">
+        <v>46284</v>
+      </c>
+      <c r="U202" s="1">
         <v>46289</v>
-      </c>
-      <c r="U202" s="1">
-        <v>46294</v>
       </c>
       <c r="X202" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -12917,13 +12917,13 @@
         <v>46294</v>
       </c>
       <c r="T203" s="2">
-        <v>0.47708333333333336</v>
+        <v>0.6215277777777778</v>
       </c>
       <c r="U203" s="1">
         <v>46301</v>
       </c>
       <c r="V203" s="2">
-        <v>0.3527777777777778</v>
+        <v>0.49722222222222223</v>
       </c>
       <c r="X203" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -12961,10 +12961,10 @@
         <v>46291</v>
       </c>
       <c r="S204" s="1">
-        <v>46294</v>
+        <v>46289</v>
       </c>
       <c r="U204" s="1">
-        <v>46301</v>
+        <v>46296</v>
       </c>
       <c r="X204" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -13032,7 +13032,7 @@
         <v>46301</v>
       </c>
       <c r="T205" s="2">
-        <v>0.35347222222222224</v>
+        <v>0.4979166666666667</v>
       </c>
       <c r="U205" s="1">
         <v>46301</v>
@@ -13186,7 +13186,7 @@
         <v>46304</v>
       </c>
       <c r="V207" s="2">
-        <v>0.7041666666666667</v>
+        <v>0.36944444444444446</v>
       </c>
       <c r="X207" t="str">
         <v>1702 Piyumi Perera</v>
@@ -13224,10 +13224,10 @@
         <v>46293</v>
       </c>
       <c r="S208" s="1">
+        <v>46296</v>
+      </c>
+      <c r="U208" s="1">
         <v>46301</v>
-      </c>
-      <c r="U208" s="1">
-        <v>46304</v>
       </c>
       <c r="X208" t="str">
         <v>1702 Piyumi Perera</v>
@@ -13295,7 +13295,7 @@
         <v>46305</v>
       </c>
       <c r="T209" s="2">
-        <v>0.3326388888888889</v>
+        <v>0.3701388888888889</v>
       </c>
       <c r="U209" s="1">
         <v>46310</v>
@@ -13375,7 +13375,7 @@
         <v>46310</v>
       </c>
       <c r="V210" s="2">
-        <v>0.5486111111111112</v>
+        <v>0.5861111111111111</v>
       </c>
       <c r="X210" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -13413,10 +13413,10 @@
         <v>46303</v>
       </c>
       <c r="S211" s="1">
+        <v>46301</v>
+      </c>
+      <c r="U211" s="1">
         <v>46305</v>
-      </c>
-      <c r="U211" s="1">
-        <v>46310</v>
       </c>
       <c r="X211" t="str">
         <v>1675 Dinusha Guantillake</v>
@@ -13484,13 +13484,13 @@
         <v>46310</v>
       </c>
       <c r="T212" s="2">
-        <v>0.5493055555555556</v>
+        <v>0.5868055555555556</v>
       </c>
       <c r="U212" s="1">
         <v>46310</v>
       </c>
       <c r="V212" s="2">
-        <v>0.5527777777777778</v>
+        <v>0.5902777777777778</v>
       </c>
       <c r="Y212" s="1">
         <v>46338</v>
@@ -13525,10 +13525,10 @@
         <v>46308</v>
       </c>
       <c r="S213" s="1">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="U213" s="1">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="Y213" s="1">
         <v>46338</v>
@@ -13593,13 +13593,13 @@
         <v>46310</v>
       </c>
       <c r="T214" s="2">
-        <v>0.5534722222222223</v>
+        <v>0.5909722222222222</v>
       </c>
       <c r="U214" s="1">
         <v>46314</v>
       </c>
       <c r="V214" s="2">
-        <v>0.41805555555555557</v>
+        <v>0.45555555555555555</v>
       </c>
       <c r="Y214" s="1">
         <v>46338</v>
@@ -13634,10 +13634,10 @@
         <v>46308</v>
       </c>
       <c r="S215" s="1">
-        <v>46310</v>
+        <v>46305</v>
       </c>
       <c r="U215" s="1">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="Y215" s="1">
         <v>46338</v>
@@ -13702,13 +13702,13 @@
         <v>46314</v>
       </c>
       <c r="T216" s="2">
-        <v>0.41875</v>
+        <v>0.45625</v>
       </c>
       <c r="U216" s="1">
         <v>46314</v>
       </c>
       <c r="V216" s="2">
-        <v>0.6104166666666667</v>
+        <v>0.6479166666666667</v>
       </c>
       <c r="Y216" s="1">
         <v>46338</v>
@@ -13743,10 +13743,10 @@
         <v>46311</v>
       </c>
       <c r="S217" s="1">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="U217" s="1">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="Y217" s="1">
         <v>46338</v>
@@ -13811,13 +13811,13 @@
         <v>46314</v>
       </c>
       <c r="T218" s="2">
-        <v>0.6111111111111112</v>
+        <v>0.6486111111111111</v>
       </c>
       <c r="U218" s="1">
         <v>46315</v>
       </c>
       <c r="V218" s="2">
-        <v>0.29305555555555557</v>
+        <v>0.33055555555555555</v>
       </c>
       <c r="Y218" s="1">
         <v>46338</v>
@@ -13852,10 +13852,10 @@
         <v>46311</v>
       </c>
       <c r="S219" s="1">
-        <v>46314</v>
+        <v>46309</v>
       </c>
       <c r="U219" s="1">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="Y219" s="1">
         <v>46338</v>
@@ -13920,13 +13920,13 @@
         <v>46315</v>
       </c>
       <c r="T220" s="2">
-        <v>0.29375</v>
+        <v>0.33125</v>
       </c>
       <c r="U220" s="1">
         <v>46315</v>
       </c>
       <c r="V220" s="2">
-        <v>0.4465277777777778</v>
+        <v>0.4840277777777778</v>
       </c>
       <c r="Y220" s="1">
         <v>46338</v>
@@ -13961,10 +13961,10 @@
         <v>46312</v>
       </c>
       <c r="S221" s="1">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="U221" s="1">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="Y221" s="1">
         <v>46338</v>
@@ -14029,13 +14029,13 @@
         <v>46315</v>
       </c>
       <c r="T222" s="2">
-        <v>0.4486111111111111</v>
+        <v>0.4847222222222222</v>
       </c>
       <c r="U222" s="1">
         <v>46316</v>
       </c>
       <c r="V222" s="2">
-        <v>0.5493055555555556</v>
+        <v>0.5854166666666667</v>
       </c>
       <c r="Y222" s="1">
         <v>46338</v>
@@ -14070,10 +14070,10 @@
         <v>46312</v>
       </c>
       <c r="S223" s="1">
-        <v>46315</v>
+        <v>46310</v>
       </c>
       <c r="U223" s="1">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="Y223" s="1">
         <v>46338</v>
@@ -14138,7 +14138,7 @@
         <v>46316</v>
       </c>
       <c r="T224" s="2">
-        <v>0.55</v>
+        <v>0.5861111111111111</v>
       </c>
       <c r="U224" s="1">
         <v>46318</v>
@@ -14440,7 +14440,7 @@
         <v>46328</v>
       </c>
       <c r="V228" s="2">
-        <v>0.49583333333333335</v>
+        <v>0.5319444444444444</v>
       </c>
       <c r="X228" t="str">
         <v>762 Thesantha Hettiarachchi</v>
@@ -14478,10 +14478,10 @@
         <v>46314</v>
       </c>
       <c r="S229" s="1">
-        <v>46316</v>
+        <v>46311</v>
       </c>
       <c r="U229" s="1">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="X229" t="str">
         <v>762 Thesantha Hettiarachchi</v>
@@ -14549,7 +14549,7 @@
         <v>46328</v>
       </c>
       <c r="T230" s="2">
-        <v>0.4965277777777778</v>
+        <v>0.5326388888888889</v>
       </c>
       <c r="U230" s="1">
         <v>46329</v>
@@ -14777,7 +14777,7 @@
         <v>46335</v>
       </c>
       <c r="V233" s="2">
-        <v>0.43125</v>
+        <v>0.4673611111111111</v>
       </c>
       <c r="X233" t="str">
         <v>1654 Mali Karunarathna</v>
@@ -14815,10 +14815,10 @@
         <v>46325</v>
       </c>
       <c r="S234" s="1">
-        <v>46328</v>
+        <v>46323</v>
       </c>
       <c r="U234" s="1">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="X234" t="str">
         <v>1654 Mali Karunarathna</v>
@@ -14886,7 +14886,7 @@
         <v>46335</v>
       </c>
       <c r="T235" s="2">
-        <v>0.43194444444444446</v>
+        <v>0.46805555555555556</v>
       </c>
       <c r="U235" s="1">
         <v>46338</v>
@@ -15040,7 +15040,7 @@
         <v>46342</v>
       </c>
       <c r="V237" s="2">
-        <v>0.3173611111111111</v>
+        <v>0.35347222222222224</v>
       </c>
       <c r="X237" t="str">
         <v>762 Thesantha Hettiarachchi</v>
@@ -15078,10 +15078,10 @@
         <v>46332</v>
       </c>
       <c r="S238" s="1">
-        <v>46335</v>
+        <v>46330</v>
       </c>
       <c r="U238" s="1">
-        <v>46342</v>
+        <v>46337</v>
       </c>
       <c r="X238" t="str">
         <v>762 Thesantha Hettiarachchi</v>
@@ -15149,7 +15149,7 @@
         <v>46342</v>
       </c>
       <c r="T239" s="2">
-        <v>0.31805555555555554</v>
+        <v>0.3541666666666667</v>
       </c>
       <c r="U239" s="1">
         <v>46343</v>
@@ -15451,7 +15451,7 @@
         <v>46345</v>
       </c>
       <c r="V243" s="2">
-        <v>0.4125</v>
+        <v>0.4486111111111111</v>
       </c>
       <c r="X243" t="str">
         <v>1515 Sanjaya Mihiran</v>
@@ -15489,10 +15489,10 @@
         <v>46333</v>
       </c>
       <c r="S244" s="1">
-        <v>46342</v>
+        <v>46337</v>
       </c>
       <c r="U244" s="1">
-        <v>46345</v>
+        <v>46340</v>
       </c>
       <c r="X244" t="str">
         <v>1515 Sanjaya Mihiran</v>
@@ -15560,13 +15560,13 @@
         <v>46345</v>
       </c>
       <c r="T245" s="2">
-        <v>0.4131944444444444</v>
+        <v>0.44930555555555557</v>
       </c>
       <c r="U245" s="1">
         <v>46345</v>
       </c>
       <c r="V245" s="2">
-        <v>0.6472222222222223</v>
+        <v>0.6833333333333333</v>
       </c>
       <c r="Y245" s="1">
         <v>46377</v>
@@ -15601,10 +15601,10 @@
         <v>46343</v>
       </c>
       <c r="S246" s="1">
-        <v>46345</v>
+        <v>46340</v>
       </c>
       <c r="U246" s="1">
-        <v>46345</v>
+        <v>46340</v>
       </c>
       <c r="Y246" s="1">
         <v>46377</v>
@@ -15669,13 +15669,13 @@
         <v>46345</v>
       </c>
       <c r="T247" s="2">
-        <v>0.6479166666666667</v>
+        <v>0.6840277777777778</v>
       </c>
       <c r="U247" s="1">
         <v>46351</v>
       </c>
       <c r="V247" s="2">
-        <v>0.36527777777777776</v>
+        <v>0.4013888888888889</v>
       </c>
       <c r="Y247" s="1">
         <v>46377</v>
@@ -15710,10 +15710,10 @@
         <v>46343</v>
       </c>
       <c r="S248" s="1">
-        <v>46345</v>
+        <v>46340</v>
       </c>
       <c r="U248" s="1">
-        <v>46351</v>
+        <v>46346</v>
       </c>
       <c r="Y248" s="1">
         <v>46377</v>
@@ -15778,13 +15778,13 @@
         <v>46351</v>
       </c>
       <c r="T249" s="2">
-        <v>0.3659722222222222</v>
+        <v>0.40208333333333335</v>
       </c>
       <c r="U249" s="1">
         <v>46358</v>
       </c>
       <c r="V249" s="2">
-        <v>0.5777777777777777</v>
+        <v>0.6138888888888889</v>
       </c>
       <c r="Y249" s="1">
         <v>46377</v>
@@ -15819,10 +15819,10 @@
         <v>46349</v>
       </c>
       <c r="S250" s="1">
-        <v>46351</v>
+        <v>46346</v>
       </c>
       <c r="U250" s="1">
-        <v>46358</v>
+        <v>46353</v>
       </c>
       <c r="Y250" s="1">
         <v>46377</v>
